--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -1610,11 +1610,11 @@
       </c>
       <c r="F7" s="18">
         <f>Assumptions!D15*Assumptions!D22*(1+Assumptions!D23)^3</f>
-        <v>1758744.11</v>
+        <v>1758744.1065</v>
       </c>
       <c r="G7" s="18">
         <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
-        <v>1958385.33</v>
+        <v>1958385.3294</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -1635,11 +1635,11 @@
       </c>
       <c r="F8" s="18">
         <f>Assumptions!D15*Assumptions!D24*(1+Assumptions!D25)^3</f>
-        <v>101077.25</v>
+        <v>101077.2475</v>
       </c>
       <c r="G8" s="18">
         <f>Assumptions!D16*Assumptions!D24*(1+Assumptions!D25)^4</f>
-        <v>112550.88</v>
+        <v>112550.881</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -1685,11 +1685,11 @@
       </c>
       <c r="F10" s="20">
         <f>F6+F7+F8+F9</f>
-        <v>1934821.35</v>
+        <v>1934821.354</v>
       </c>
       <c r="G10" s="20">
         <f>G6+G7+G8+G9</f>
-        <v>2145936.21</v>
+        <v>2145936.2104</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="G13" s="18">
         <f>G12*Assumptions!D33*(1+Assumptions!D34)^4</f>
-        <v>855386.7</v>
+        <v>855386.6956</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -1760,11 +1760,11 @@
       </c>
       <c r="F14" s="18">
         <f>Assumptions!D38*Assumptions!D40*(1+Assumptions!D41)^3</f>
-        <v>288479.93</v>
+        <v>288479.928</v>
       </c>
       <c r="G14" s="18">
         <f>Assumptions!D39*Assumptions!D40*(1+Assumptions!D41)^4</f>
-        <v>297134.33</v>
+        <v>297134.32584</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C15" s="18">
         <f>(C13+C14)*Assumptions!D42</f>
-        <v>160466.67</v>
+        <v>160466.66666667</v>
       </c>
       <c r="D15" s="18">
         <f>(D13+D14)*Assumptions!D42</f>
@@ -1785,11 +1785,11 @@
       </c>
       <c r="F15" s="18">
         <f>(F13+F14)*Assumptions!D42</f>
-        <v>249287.45</v>
+        <v>249287.45293333</v>
       </c>
       <c r="G15" s="18">
         <f>(G13+G14)*Assumptions!D42</f>
-        <v>278525.91</v>
+        <v>278525.91351467</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="C16" s="20">
         <f>C13+C14+C15</f>
-        <v>824466.67</v>
+        <v>824466.66666667</v>
       </c>
       <c r="D16" s="20">
         <f>D13+D14+D15</f>
@@ -1810,11 +1810,11 @@
       </c>
       <c r="F16" s="20">
         <f>F13+F14+F15</f>
-        <v>1280821.74</v>
+        <v>1280821.74093333</v>
       </c>
       <c r="G16" s="20">
         <f>G13+G14+G15</f>
-        <v>1431046.93</v>
+        <v>1431046.93495467</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -1835,11 +1835,11 @@
       </c>
       <c r="F18" s="18">
         <f>Assumptions!D46*(1+Assumptions!D47)^3</f>
-        <v>111458.15</v>
+        <v>111458.154</v>
       </c>
       <c r="G18" s="18">
         <f>Assumptions!D46*(1+Assumptions!D47)^4</f>
-        <v>114801.9</v>
+        <v>114801.89862</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -1860,11 +1860,11 @@
       </c>
       <c r="F19" s="18">
         <f>Assumptions!D48*(1+Assumptions!D49)^3</f>
-        <v>37589.81</v>
+        <v>37589.8088</v>
       </c>
       <c r="G19" s="18">
         <f>Assumptions!D48*(1+Assumptions!D49)^4</f>
-        <v>38717.5</v>
+        <v>38717.503064</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -1881,15 +1881,15 @@
       </c>
       <c r="E20" s="18">
         <f>Assumptions!D14*Assumptions!D50*(1+Assumptions!D51)^2</f>
-        <v>172120.42</v>
+        <v>172120.416</v>
       </c>
       <c r="F20" s="18">
         <f>Assumptions!D15*Assumptions!D50*(1+Assumptions!D51)^3</f>
-        <v>266480.06</v>
+        <v>266480.055309</v>
       </c>
       <c r="G20" s="18">
         <f>Assumptions!D16*Assumptions!D50*(1+Assumptions!D51)^4</f>
-        <v>385747.89</v>
+        <v>385747.88546892</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
@@ -1906,15 +1906,15 @@
       </c>
       <c r="E21" s="18">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
-        <v>107066.03</v>
+        <v>107066.028</v>
       </c>
       <c r="F21" s="18">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
-        <v>127922.49</v>
+        <v>127922.4902544</v>
       </c>
       <c r="G21" s="18">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
-        <v>152841.79</v>
+        <v>152841.79135596</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -1931,15 +1931,15 @@
       </c>
       <c r="E22" s="20">
         <f>E18+E19+E20+E21</f>
-        <v>423893.2</v>
+        <v>423893.204</v>
       </c>
       <c r="F22" s="20">
         <f>F18+F19+F20+F21</f>
-        <v>543450.51</v>
+        <v>543450.5083634</v>
       </c>
       <c r="G22" s="20">
         <f>G18+G19+G20+G21</f>
-        <v>692109.08</v>
+        <v>692109.07850888</v>
       </c>
     </row>
   </sheetData>
@@ -2064,11 +2064,11 @@
       </c>
       <c r="F7" s="18">
         <f>Drivers!F7</f>
-        <v>1758744.11</v>
+        <v>1758744.1065</v>
       </c>
       <c r="G7" s="18">
         <f>Drivers!G7</f>
-        <v>1958385.33</v>
+        <v>1958385.3294</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2089,11 +2089,11 @@
       </c>
       <c r="F8" s="18">
         <f>Drivers!F8</f>
-        <v>101077.25</v>
+        <v>101077.2475</v>
       </c>
       <c r="G8" s="18">
         <f>Drivers!G8</f>
-        <v>112550.88</v>
+        <v>112550.881</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -2139,11 +2139,11 @@
       </c>
       <c r="F10" s="20">
         <f>Drivers!F10</f>
-        <v>1934821.35</v>
+        <v>1934821.354</v>
       </c>
       <c r="G10" s="20">
         <f>Drivers!G10</f>
-        <v>2145936.21</v>
+        <v>2145936.2104</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="C12" s="18">
         <f>Drivers!C16</f>
-        <v>824466.67</v>
+        <v>824466.66666667</v>
       </c>
       <c r="D12" s="18">
         <f>Drivers!D16</f>
@@ -2164,11 +2164,11 @@
       </c>
       <c r="F12" s="18">
         <f>Drivers!F16</f>
-        <v>1280821.74</v>
+        <v>1280821.74093333</v>
       </c>
       <c r="G12" s="18">
         <f>Drivers!G16</f>
-        <v>1431046.93</v>
+        <v>1431046.93495467</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -2185,15 +2185,15 @@
       </c>
       <c r="E13" s="18">
         <f>Drivers!E22</f>
-        <v>423893.2</v>
+        <v>423893.204</v>
       </c>
       <c r="F13" s="18">
         <f>Drivers!F22</f>
-        <v>543450.51</v>
+        <v>543450.5083634</v>
       </c>
       <c r="G13" s="18">
         <f>Drivers!G22</f>
-        <v>692109.08</v>
+        <v>692109.07850888</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="C15" s="20">
         <f>C12+C13</f>
-        <v>1095866.67</v>
+        <v>1095866.66666667</v>
       </c>
       <c r="D15" s="20">
         <f>D12+D13</f>
@@ -2210,15 +2210,15 @@
       </c>
       <c r="E15" s="20">
         <f>E12+E13</f>
-        <v>1562026.72</v>
+        <v>1562026.724</v>
       </c>
       <c r="F15" s="20">
         <f>F12+F13</f>
-        <v>1824272.25</v>
+        <v>1824272.24929673</v>
       </c>
       <c r="G15" s="20">
         <f>G12+G13</f>
-        <v>2123156.01</v>
+        <v>2123156.01346354</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="C16" s="21">
         <f>C10-C15</f>
-        <v>-100866.67</v>
+        <v>-100866.66666667</v>
       </c>
       <c r="D16" s="22">
         <f>D10-D15</f>
@@ -2235,15 +2235,15 @@
       </c>
       <c r="E16" s="22">
         <f>E10-E15</f>
-        <v>74618.08</v>
+        <v>74618.076</v>
       </c>
       <c r="F16" s="22">
         <f>F10-F15</f>
-        <v>110549.1</v>
+        <v>110549.10470327</v>
       </c>
       <c r="G16" s="22">
         <f>G10-G15</f>
-        <v>22780.2</v>
+        <v>22780.19693646</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2252,23 +2252,23 @@
       </c>
       <c r="C17" s="23">
         <f>IF(C10&gt;0,C16/C10,0)</f>
-        <v>-0.1</v>
+        <v>-0.10137353</v>
       </c>
       <c r="D17" s="23">
         <f>IF(D10&gt;0,D16/D10,0)</f>
-        <v>0.02</v>
+        <v>0.0159326</v>
       </c>
       <c r="E17" s="23">
         <f>IF(E10&gt;0,E16/E10,0)</f>
-        <v>0.05</v>
+        <v>0.0455921</v>
       </c>
       <c r="F17" s="23">
         <f>IF(F10&gt;0,F16/F10,0)</f>
-        <v>0.06</v>
+        <v>0.0571366</v>
       </c>
       <c r="G17" s="23">
         <f>IF(G10&gt;0,G16/G10,0)</f>
-        <v>0.01</v>
+        <v>0.01061551</v>
       </c>
     </row>
   </sheetData>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C4" s="18">
         <f>'5-Year P&amp;L'!C16</f>
-        <v>-100866.67</v>
+        <v>-100866.66666667</v>
       </c>
       <c r="D4" s="18">
         <f>'5-Year P&amp;L'!D16</f>
@@ -2339,15 +2339,15 @@
       </c>
       <c r="E4" s="18">
         <f>'5-Year P&amp;L'!E16</f>
-        <v>74618.08</v>
+        <v>74618.076</v>
       </c>
       <c r="F4" s="18">
         <f>'5-Year P&amp;L'!F16</f>
-        <v>110549.1</v>
+        <v>110549.10470327</v>
       </c>
       <c r="G4" s="18">
         <f>'5-Year P&amp;L'!G16</f>
-        <v>22780.2</v>
+        <v>22780.19693646</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -2381,23 +2381,23 @@
       </c>
       <c r="C7" s="18">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>34064.39</v>
+        <v>34064.39316601</v>
       </c>
       <c r="D7" s="18">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>34064.39</v>
+        <v>34064.39316601</v>
       </c>
       <c r="E7" s="18">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>34064.39</v>
+        <v>34064.39316601</v>
       </c>
       <c r="F7" s="18">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>34064.39</v>
+        <v>34064.39316601</v>
       </c>
       <c r="G7" s="18">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>34064.39</v>
+        <v>34064.39316601</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2406,23 +2406,23 @@
       </c>
       <c r="C8" s="20">
         <f>C6+C7</f>
-        <v>59064.39</v>
+        <v>59064.39316601</v>
       </c>
       <c r="D8" s="20">
         <f>D6+D7</f>
-        <v>59064.39</v>
+        <v>59064.39316601</v>
       </c>
       <c r="E8" s="20">
         <f>E6+E7</f>
-        <v>59064.39</v>
+        <v>59064.39316601</v>
       </c>
       <c r="F8" s="20">
         <f>F6+F7</f>
-        <v>59064.39</v>
+        <v>59064.39316601</v>
       </c>
       <c r="G8" s="20">
         <f>G6+G7</f>
-        <v>59064.39</v>
+        <v>59064.39316601</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -2431,23 +2431,23 @@
       </c>
       <c r="C10" s="24">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
-        <v>-1.71</v>
+        <v>-1.70774068</v>
       </c>
       <c r="D10" s="24">
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
-        <v>0.35</v>
+        <v>0.3525305</v>
       </c>
       <c r="E10" s="25">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
-        <v>1.26</v>
+        <v>1.26333434</v>
       </c>
       <c r="F10" s="25">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
-        <v>1.87</v>
+        <v>1.87167088</v>
       </c>
       <c r="G10" s="24">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
-        <v>0.39</v>
+        <v>0.38568409</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -2456,23 +2456,23 @@
       </c>
       <c r="C12" s="18">
         <f>C4-C8</f>
-        <v>-159931.06</v>
+        <v>-159931.05983267</v>
       </c>
       <c r="D12" s="18">
         <f>D4-D8</f>
-        <v>-38242.39</v>
+        <v>-38242.39316601</v>
       </c>
       <c r="E12" s="18">
         <f>E4-E8</f>
-        <v>15553.68</v>
+        <v>15553.68283399</v>
       </c>
       <c r="F12" s="18">
         <f>F4-F8</f>
-        <v>51484.71</v>
+        <v>51484.71153726</v>
       </c>
       <c r="G12" s="18">
         <f>G4-G8</f>
-        <v>-36284.2</v>
+        <v>-36284.19622955</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -2481,23 +2481,23 @@
       </c>
       <c r="C14" s="26">
         <f>Assumptions!D57+C12</f>
-        <v>-84931.06</v>
+        <v>-84931.05983267</v>
       </c>
       <c r="D14" s="26">
         <f>C14+D12</f>
-        <v>-123173.45</v>
+        <v>-123173.45299868</v>
       </c>
       <c r="E14" s="26">
         <f>D14+E12</f>
-        <v>-107619.77</v>
+        <v>-107619.77016469</v>
       </c>
       <c r="F14" s="26">
         <f>E14+F12</f>
-        <v>-56135.06</v>
+        <v>-56135.05862743</v>
       </c>
       <c r="G14" s="26">
         <f>F14+G12</f>
-        <v>-92419.25</v>
+        <v>-92419.25485698</v>
       </c>
     </row>
   </sheetData>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="C4" s="23">
         <f>Assumptions!D60</f>
-        <v>0.07</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C6" s="28">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>34064.39</v>
+        <v>34064.39316601</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="C8" s="24">
         <f>'Cash Flow &amp; DSCR'!C10</f>
-        <v>-1.71</v>
+        <v>-1.70774068</v>
       </c>
     </row>
   </sheetData>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="C9" s="18">
         <f>Drivers!G10</f>
-        <v>2145936.21</v>
+        <v>2145936.2104</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="C10" s="29">
         <f>'5-Year P&amp;L'!G16</f>
-        <v>22780.2</v>
+        <v>22780.19693646</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -53,7 +53,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 16, 2026</t>
+    <t>Generated March 17, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -412,13 +412,13 @@
     <font>
       <u/>
       <color rgb="FF0563C1"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
       <color rgb="FF6B7280"/>
-      <sz val="9"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -435,12 +435,12 @@
     </font>
     <font>
       <color rgb="FF374151"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF1E293B"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -59,7 +59,7 @@
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
   <si>
-    <t>SchoolStack Budget — Lender Pro Forma Assumptions</t>
+    <t>SchoolStack Budget - Lender Pro Forma Assumptions</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -143,19 +143,19 @@
     <t>Teacher Salary Growth %</t>
   </si>
   <si>
-    <t>Admin FTE — Year 1</t>
-  </si>
-  <si>
-    <t>Admin FTE — Year 2</t>
-  </si>
-  <si>
-    <t>Admin FTE — Year 3</t>
-  </si>
-  <si>
-    <t>Admin FTE — Year 4</t>
-  </si>
-  <si>
-    <t>Admin FTE — Year 5</t>
+    <t>Admin FTE - Year 1</t>
+  </si>
+  <si>
+    <t>Admin FTE - Year 2</t>
+  </si>
+  <si>
+    <t>Admin FTE - Year 3</t>
+  </si>
+  <si>
+    <t>Admin FTE - Year 4</t>
+  </si>
+  <si>
+    <t>Admin FTE - Year 5</t>
   </si>
   <si>
     <t>Avg Admin Salary (Year 1)</t>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -53,7 +53,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 17, 2026</t>
+    <t>Generated March 18, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -5,20 +5,22 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Cover" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Assumptions" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Drivers" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="5-Year P&amp;L" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Cash Flow &amp; DSCR" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Staffing" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Loan Snapshot" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Summary" state="visible" r:id="rId11"/>
+    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Assumptions" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Drivers" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="5-Year P&amp;L" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Cash Flow &amp; DSCR" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Staffing" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Loan Snapshot" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Summary" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Financial Health" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="177">
   <si>
     <t>SCHOOLSTACK BUDGET</t>
   </si>
@@ -53,12 +55,81 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 18, 2026</t>
+    <t>Generated March 26, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
   <si>
+    <t>How to Use This Workbook</t>
+  </si>
+  <si>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t>Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t>Green cells are key outputs and summary metrics.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>Assumptions &amp; Drivers: Model inputs and calculations</t>
+  </si>
+  <si>
+    <t>5-Year P&amp;L &amp; Cash Flow: Financial projections</t>
+  </si>
+  <si>
+    <t>Staffing &amp; Loan Snapshot: Personnel and debt detail</t>
+  </si>
+  <si>
+    <t>Summary &amp; Financial Health: Key metrics dashboard</t>
+  </si>
+  <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs.</t>
+  </si>
+  <si>
+    <t>Tips</t>
+  </si>
+  <si>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Disclaimer</t>
+  </si>
+  <si>
+    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
+  </si>
+  <si>
+    <t>user-provided assumptions and should be independently verified.</t>
+  </si>
+  <si>
     <t>SchoolStack Budget - Lender Pro Forma Assumptions</t>
   </si>
   <si>
@@ -366,6 +437,120 @@
   </si>
   <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
+  </si>
+  <si>
+    <t>Heritage Academy — Financial Health Dashboard</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Personnel</t>
+  </si>
+  <si>
+    <t>Operating Expenses</t>
+  </si>
+  <si>
+    <t>Debt Service</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>Ending Cash</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
+    <t>FINANCIAL HEALTH SIGNALS</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Watch Item</t>
+  </si>
+  <si>
+    <t>Viability</t>
+  </si>
+  <si>
+    <t>○ Needs attention</t>
+  </si>
+  <si>
+    <t>Year 5 margin of -2% signals the model is not yet on a sustainable path.</t>
+  </si>
+  <si>
+    <t>Revisit revenue assumptions and cost structure to build a clear path to break-even.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>Cash goes negative in month 5. The school will need outside funding to continue operating.</t>
+  </si>
+  <si>
+    <t>Secure a line of credit or bridge funding before operations begin.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
+    <t>Staffing at 67% of revenue is above the sustainable range. There's too little left for everything else.</t>
+  </si>
+  <si>
+    <t>Review staffing plan for phased hiring, shared roles, or adjusted ratios.</t>
+  </si>
+  <si>
+    <t>Facility Burden</t>
+  </si>
+  <si>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>Facility costs at 10% of revenue are well-managed and leave budget for programs.</t>
+  </si>
+  <si>
+    <t>Watch for rent escalation clauses that could push this higher over time.</t>
+  </si>
+  <si>
+    <t>Debt Affordability</t>
+  </si>
+  <si>
+    <t>DSCR of 0.39x means operating income does not cover debt payments. This must be resolved.</t>
+  </si>
+  <si>
+    <t>Reduce loan amounts, extend terms, or increase revenue before committing to this debt.</t>
+  </si>
+  <si>
+    <t>Revenue Concentration</t>
+  </si>
+  <si>
+    <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
+  </si>
+  <si>
+    <t>Continue to pressure-test enrollment assumptions: recruitment pipeline, waitlist depth, retention rates, and collection reliability.</t>
+  </si>
+  <si>
+    <t>Reserve Strength</t>
+  </si>
+  <si>
+    <t>Less than 1 month of reserves by Year 5. The school has no financial cushion.</t>
+  </si>
+  <si>
+    <t>Prioritize building reserves — even a small surplus each year compounds into meaningful protection.</t>
+  </si>
+  <si>
+    <t>2 Healthy  |  0 Watch  |  5 Needs Attention</t>
+  </si>
+  <si>
+    <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>
@@ -378,7 +563,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -422,6 +607,10 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF1E293B"/>
       <sz val="14"/>
@@ -444,16 +633,30 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF9CA3AF"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -478,6 +681,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EDF2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -541,7 +754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -549,32 +762,34 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -587,7 +802,7 @@
     <xf numFmtId="165" fontId="12" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="12" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -607,6 +822,32 @@
     </xf>
     <xf numFmtId="165" fontId="12" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1057,7 +1298,556 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G26"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="19">
+        <v>100</v>
+      </c>
+      <c r="D6" s="19">
+        <v>130</v>
+      </c>
+      <c r="E6" s="19">
+        <v>160</v>
+      </c>
+      <c r="F6" s="19">
+        <v>185</v>
+      </c>
+      <c r="G6" s="19">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="20">
+        <v>995000</v>
+      </c>
+      <c r="D7" s="20">
+        <v>1306880</v>
+      </c>
+      <c r="E7" s="20">
+        <v>1636644.8</v>
+      </c>
+      <c r="F7" s="20">
+        <v>1934821.354</v>
+      </c>
+      <c r="G7" s="20">
+        <v>2145936.2104</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="20">
+        <v>824466.6666666666</v>
+      </c>
+      <c r="D8" s="20">
+        <v>951514</v>
+      </c>
+      <c r="E8" s="20">
+        <v>1138133.52</v>
+      </c>
+      <c r="F8" s="20">
+        <v>1280821.7409333333</v>
+      </c>
+      <c r="G8" s="20">
+        <v>1431046.934954667</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="20">
+        <v>271400</v>
+      </c>
+      <c r="D9" s="20">
+        <v>334544</v>
+      </c>
+      <c r="E9" s="20">
+        <v>423893.20399999997</v>
+      </c>
+      <c r="F9" s="20">
+        <v>543450.5083634</v>
+      </c>
+      <c r="G9" s="20">
+        <v>692109.0785088772</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="20">
+        <v>59064.39316600799</v>
+      </c>
+      <c r="D10" s="20">
+        <v>59064.39316600799</v>
+      </c>
+      <c r="E10" s="20">
+        <v>59064.39316600799</v>
+      </c>
+      <c r="F10" s="20">
+        <v>59064.39316600799</v>
+      </c>
+      <c r="G10" s="20">
+        <v>59064.39316600799</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="C11" s="23">
+        <v>-159931.0598326745</v>
+      </c>
+      <c r="D11" s="23">
+        <v>-38242.39316600799</v>
+      </c>
+      <c r="E11" s="24">
+        <v>15553.682833992127</v>
+      </c>
+      <c r="F11" s="24">
+        <v>51484.71153725888</v>
+      </c>
+      <c r="G11" s="23">
+        <v>-36284.19622955197</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="23">
+        <v>-84931.05983267451</v>
+      </c>
+      <c r="D12" s="23">
+        <v>-123173.45299868251</v>
+      </c>
+      <c r="E12" s="23">
+        <v>-107619.77016469039</v>
+      </c>
+      <c r="F12" s="23">
+        <v>-56135.05862743151</v>
+      </c>
+      <c r="G12" s="23">
+        <v>-92419.25485698348</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="34">
+        <v>-0.1607347335001754</v>
+      </c>
+      <c r="D13" s="34">
+        <v>-0.029262360098867523</v>
+      </c>
+      <c r="E13" s="35">
+        <v>0.009503395504016587</v>
+      </c>
+      <c r="F13" s="35">
+        <v>0.026609542752265323</v>
+      </c>
+      <c r="G13" s="34">
+        <v>-0.016908329359328268</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="G15" s="32"/>
+    </row>
+    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="E16" s="38"/>
+      <c r="F16" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="G16" s="39"/>
+    </row>
+    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" s="38"/>
+      <c r="F17" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="G17" s="39"/>
+    </row>
+    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="E18" s="38"/>
+      <c r="F18" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="G18" s="39"/>
+    </row>
+    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="D19" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="E19" s="38"/>
+      <c r="F19" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="G19" s="39"/>
+    </row>
+    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="E20" s="38"/>
+      <c r="F20" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="G20" s="39"/>
+    </row>
+    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="E21" s="38"/>
+      <c r="F21" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="G21" s="39"/>
+    </row>
+    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="E22" s="38"/>
+      <c r="F22" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="G22" s="39"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B26:G26"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:B29"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFD97706"/>
@@ -1073,387 +1863,387 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="B1" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
+      <c r="B3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="10" t="s">
+      <c r="C5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>17</v>
+      <c r="C6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>19</v>
+      <c r="C7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="10">
+      <c r="C8" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="12">
         <v>2023</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="B10" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="11">
+      <c r="C12" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="13">
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="11">
+      <c r="C13" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="13">
         <v>130</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="11">
+      <c r="C14" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="13">
         <v>160</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="11">
+      <c r="C15" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="13">
         <v>185</v>
       </c>
     </row>
     <row r="16" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="11">
+      <c r="C16" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="13">
         <v>200</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
+      <c r="B18" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="12">
+      <c r="C20" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="13">
+      <c r="C21" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="15">
         <v>0.03</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="12">
+      <c r="C22" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="14">
         <v>8700</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="13">
+      <c r="C23" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="15">
         <v>0.03</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="12">
+      <c r="C24" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="14">
         <v>500</v>
       </c>
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="13">
+      <c r="C25" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="15">
         <v>0.03</v>
       </c>
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="13">
+      <c r="C26" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="15">
         <v>0.95</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="12">
+      <c r="C27" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="14">
         <v>75000</v>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="13">
+      <c r="C28" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
+      <c r="B30" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="11">
+      <c r="C32" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="13">
         <v>11</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="12">
+      <c r="C33" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="14">
         <v>40000</v>
       </c>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D34" s="13">
+      <c r="C34" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="15">
         <v>0.03</v>
       </c>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" s="11">
+      <c r="C35" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="13">
         <v>4</v>
       </c>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="11">
+      <c r="C36" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="13">
         <v>4</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="11">
+      <c r="C37" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" s="13">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" s="11">
+      <c r="C38" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="13">
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C39" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" s="11">
+      <c r="C39" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" s="13">
         <v>4</v>
       </c>
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C40" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" s="12">
+      <c r="C40" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" s="14">
         <v>66000</v>
       </c>
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C41" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D41" s="13">
+      <c r="C41" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="15">
         <v>0.03</v>
       </c>
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C42" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D42" s="13">
+      <c r="C42" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D42" s="15">
         <v>0.24166666666666667</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
+      <c r="B44" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D46" s="12">
+      <c r="C46" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" s="14">
         <v>102000</v>
       </c>
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D47" s="13">
+      <c r="C47" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D47" s="15">
         <v>0.03</v>
       </c>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" s="12">
+      <c r="C48" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48" s="14">
         <v>34400</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D49" s="13">
+      <c r="C49" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D49" s="15">
         <v>0.03</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D50" s="12">
+      <c r="C50" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D50" s="14">
         <v>600</v>
       </c>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D51" s="13">
+      <c r="C51" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D51" s="15">
         <v>0.339</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D52" s="12">
+      <c r="C52" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" s="14">
         <v>75000</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D53" s="13">
+      <c r="C53" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D53" s="15">
         <v>0.1948</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
+      <c r="B55" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C57" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D57" s="12">
+      <c r="C57" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57" s="14">
         <v>75000</v>
       </c>
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C58" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D58" s="12">
+      <c r="C58" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D58" s="14">
         <v>25000</v>
       </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C59" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D59" s="12">
+      <c r="C59" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D59" s="14">
         <v>250000</v>
       </c>
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C60" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D60" s="13">
+      <c r="C60" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D60" s="15">
         <v>0.065</v>
       </c>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C61" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D61" s="11">
+      <c r="C61" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D61" s="13">
         <v>10</v>
       </c>
     </row>
@@ -1475,7 +2265,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF0D9488"/>
@@ -1490,785 +2280,456 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="B1" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="14"/>
-      <c r="C3" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>69</v>
+      <c r="B3" s="16"/>
+      <c r="C3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="17">
+      <c r="B4" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="19">
         <f>Assumptions!D12</f>
         <v>100</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="19">
         <f>Assumptions!D13</f>
         <v>130</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="19">
         <f>Assumptions!D14</f>
         <v>160</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="19">
         <f>Assumptions!D15</f>
         <v>185</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="19">
         <f>Assumptions!D16</f>
         <v>200</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="18" t="str">
+      <c r="B5" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="20" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
         <v>0</v>
       </c>
-      <c r="D5" s="18" t="str">
+      <c r="D5" s="20" t="str">
         <f>Assumptions!D13*Assumptions!D20*(1+Assumptions!D21)^1</f>
         <v>0</v>
       </c>
-      <c r="E5" s="18" t="str">
+      <c r="E5" s="20" t="str">
         <f>Assumptions!D14*Assumptions!D20*(1+Assumptions!D21)^2</f>
         <v>0</v>
       </c>
-      <c r="F5" s="18" t="str">
+      <c r="F5" s="20" t="str">
         <f>Assumptions!D15*Assumptions!D20*(1+Assumptions!D21)^3</f>
         <v>0</v>
       </c>
-      <c r="G5" s="18" t="str">
+      <c r="G5" s="20" t="str">
         <f>Assumptions!D16*Assumptions!D20*(1+Assumptions!D21)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="18" t="str">
+      <c r="B6" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="20" t="str">
         <f>C5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="D6" s="18" t="str">
+      <c r="D6" s="20" t="str">
         <f>D5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="E6" s="18" t="str">
+      <c r="E6" s="20" t="str">
         <f>E5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="F6" s="18" t="str">
+      <c r="F6" s="20" t="str">
         <f>F5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="G6" s="18" t="str">
+      <c r="G6" s="20" t="str">
         <f>G5*Assumptions!D26</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="18">
+      <c r="B7" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="20">
         <f>Assumptions!D12*Assumptions!D22</f>
         <v>870000</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="20">
         <f>Assumptions!D13*Assumptions!D22*(1+Assumptions!D23)^1</f>
         <v>1164930</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="20">
         <f>Assumptions!D14*Assumptions!D22*(1+Assumptions!D23)^2</f>
         <v>1476772.8</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="20">
         <f>Assumptions!D15*Assumptions!D22*(1+Assumptions!D23)^3</f>
         <v>1758744.1065</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="20">
         <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
         <v>1958385.3294</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="18">
+      <c r="B8" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="20">
         <f>Assumptions!D12*Assumptions!D24</f>
         <v>50000</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="20">
         <f>Assumptions!D13*Assumptions!D24*(1+Assumptions!D25)^1</f>
         <v>66950</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="20">
         <f>Assumptions!D14*Assumptions!D24*(1+Assumptions!D25)^2</f>
         <v>84872</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="20">
         <f>Assumptions!D15*Assumptions!D24*(1+Assumptions!D25)^3</f>
         <v>101077.2475</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="20">
         <f>Assumptions!D16*Assumptions!D24*(1+Assumptions!D25)^4</f>
         <v>112550.881</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="18">
+      <c r="B9" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="20">
         <f>Assumptions!D27</f>
         <v>75000</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="20">
         <f>Assumptions!D27*(1+Assumptions!D28)^1</f>
         <v>75000</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="20">
         <f>Assumptions!D27*(1+Assumptions!D28)^2</f>
         <v>75000</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="20">
         <f>Assumptions!D27*(1+Assumptions!D28)^3</f>
         <v>75000</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="20">
         <f>Assumptions!D27*(1+Assumptions!D28)^4</f>
         <v>75000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="20">
+      <c r="B10" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="22">
         <f>C6+C7+C8+C9</f>
         <v>995000</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="22">
         <f>D6+D7+D8+D9</f>
         <v>1306880</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="22">
         <f>E6+E7+E8+E9</f>
         <v>1636644.8</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="22">
         <f>F6+F7+F8+F9</f>
         <v>1934821.354</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="22">
         <f>G6+G7+G8+G9</f>
         <v>2145936.2104</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="17">
+      <c r="B12" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="19">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
         <v>10</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="19">
         <f>CEILING(Assumptions!D13/Assumptions!D32,1)</f>
         <v>12</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="19">
         <f>CEILING(Assumptions!D14/Assumptions!D32,1)</f>
         <v>15</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="19">
         <f>CEILING(Assumptions!D15/Assumptions!D32,1)</f>
         <v>17</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="19">
         <f>CEILING(Assumptions!D16/Assumptions!D32,1)</f>
         <v>19</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="18">
+      <c r="B13" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="20">
         <f>C12*Assumptions!D33</f>
         <v>400000</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="20">
         <f>D12*Assumptions!D33*(1+Assumptions!D34)^1</f>
         <v>494400</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="20">
         <f>E12*Assumptions!D33*(1+Assumptions!D34)^2</f>
         <v>636540</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="20">
         <f>F12*Assumptions!D33*(1+Assumptions!D34)^3</f>
         <v>743054.36</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="20">
         <f>G12*Assumptions!D33*(1+Assumptions!D34)^4</f>
         <v>855386.6956</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="18">
+      <c r="B14" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="20">
         <f>Assumptions!D35*Assumptions!D40</f>
         <v>264000</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="20">
         <f>Assumptions!D36*Assumptions!D40*(1+Assumptions!D41)^1</f>
         <v>271920</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="20">
         <f>Assumptions!D37*Assumptions!D40*(1+Assumptions!D41)^2</f>
         <v>280077.6</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="20">
         <f>Assumptions!D38*Assumptions!D40*(1+Assumptions!D41)^3</f>
         <v>288479.928</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="20">
         <f>Assumptions!D39*Assumptions!D40*(1+Assumptions!D41)^4</f>
         <v>297134.32584</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="18">
+      <c r="B15" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="20">
         <f>(C13+C14)*Assumptions!D42</f>
         <v>160466.66666667</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="20">
         <f>(D13+D14)*Assumptions!D42</f>
         <v>185194</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="20">
         <f>(E13+E14)*Assumptions!D42</f>
         <v>221515.92</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="20">
         <f>(F13+F14)*Assumptions!D42</f>
         <v>249287.45293333</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="20">
         <f>(G13+G14)*Assumptions!D42</f>
         <v>278525.91351467</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" s="20">
+      <c r="B16" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="22">
         <f>C13+C14+C15</f>
         <v>824466.66666667</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="22">
         <f>D13+D14+D15</f>
         <v>951514</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="22">
         <f>E13+E14+E15</f>
         <v>1138133.52</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="22">
         <f>F13+F14+F15</f>
         <v>1280821.74093333</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="22">
         <f>G13+G14+G15</f>
         <v>1431046.93495467</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="18">
+      <c r="B18" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="20">
         <f>Assumptions!D46</f>
         <v>102000</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="20">
         <f>Assumptions!D46*(1+Assumptions!D47)^1</f>
         <v>105060</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="20">
         <f>Assumptions!D46*(1+Assumptions!D47)^2</f>
         <v>108211.8</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="20">
         <f>Assumptions!D46*(1+Assumptions!D47)^3</f>
         <v>111458.154</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="20">
         <f>Assumptions!D46*(1+Assumptions!D47)^4</f>
         <v>114801.89862</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" s="18">
+      <c r="B19" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="20">
         <f>Assumptions!D48</f>
         <v>34400</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="20">
         <f>Assumptions!D48*(1+Assumptions!D49)^1</f>
         <v>35432</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="20">
         <f>Assumptions!D48*(1+Assumptions!D49)^2</f>
         <v>36494.96</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="20">
         <f>Assumptions!D48*(1+Assumptions!D49)^3</f>
         <v>37589.8088</v>
       </c>
-      <c r="G19" s="18">
+      <c r="G19" s="20">
         <f>Assumptions!D48*(1+Assumptions!D49)^4</f>
         <v>38717.503064</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="18">
+      <c r="B20" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="20">
         <f>Assumptions!D12*Assumptions!D50</f>
         <v>60000</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="20">
         <f>Assumptions!D13*Assumptions!D50*(1+Assumptions!D51)^1</f>
         <v>104442</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="20">
         <f>Assumptions!D14*Assumptions!D50*(1+Assumptions!D51)^2</f>
         <v>172120.416</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="20">
         <f>Assumptions!D15*Assumptions!D50*(1+Assumptions!D51)^3</f>
         <v>266480.055309</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="20">
         <f>Assumptions!D16*Assumptions!D50*(1+Assumptions!D51)^4</f>
         <v>385747.88546892</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" s="18">
+      <c r="B21" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="20">
         <f>Assumptions!D52</f>
         <v>75000</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="20">
         <f>Assumptions!D52*(1+Assumptions!D53)^1</f>
         <v>89610</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="20">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
         <v>107066.028</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="20">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
         <v>127922.4902544</v>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="20">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
         <v>152841.79135596</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" s="20">
+      <c r="B22" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="22">
         <f>C18+C19+C20+C21</f>
         <v>271400</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="22">
         <f>D18+D19+D20+D21</f>
         <v>334544</v>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="22">
         <f>E18+E19+E20+E21</f>
         <v>423893.204</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="22">
         <f>F18+F19+F20+F21</f>
         <v>543450.5083634</v>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="22">
         <f>G18+G19+G20+G21</f>
         <v>692109.07850888</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF328555"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:G17"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="7" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="14"/>
-      <c r="C3" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="17">
-        <f>Drivers!C4</f>
-        <v>100</v>
-      </c>
-      <c r="D5" s="17">
-        <f>Drivers!D4</f>
-        <v>130</v>
-      </c>
-      <c r="E5" s="17">
-        <f>Drivers!E4</f>
-        <v>160</v>
-      </c>
-      <c r="F5" s="17">
-        <f>Drivers!F4</f>
-        <v>185</v>
-      </c>
-      <c r="G5" s="17">
-        <f>Drivers!G4</f>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="18" t="str">
-        <f>Drivers!C6</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="18" t="str">
-        <f>Drivers!D6</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="18" t="str">
-        <f>Drivers!E6</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="18" t="str">
-        <f>Drivers!F6</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="18" t="str">
-        <f>Drivers!G6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" s="18">
-        <f>Drivers!C7</f>
-        <v>870000</v>
-      </c>
-      <c r="D7" s="18">
-        <f>Drivers!D7</f>
-        <v>1164930</v>
-      </c>
-      <c r="E7" s="18">
-        <f>Drivers!E7</f>
-        <v>1476772.8</v>
-      </c>
-      <c r="F7" s="18">
-        <f>Drivers!F7</f>
-        <v>1758744.1065</v>
-      </c>
-      <c r="G7" s="18">
-        <f>Drivers!G7</f>
-        <v>1958385.3294</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="18">
-        <f>Drivers!C8</f>
-        <v>50000</v>
-      </c>
-      <c r="D8" s="18">
-        <f>Drivers!D8</f>
-        <v>66950</v>
-      </c>
-      <c r="E8" s="18">
-        <f>Drivers!E8</f>
-        <v>84872</v>
-      </c>
-      <c r="F8" s="18">
-        <f>Drivers!F8</f>
-        <v>101077.2475</v>
-      </c>
-      <c r="G8" s="18">
-        <f>Drivers!G8</f>
-        <v>112550.881</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="18">
-        <f>Drivers!C9</f>
-        <v>75000</v>
-      </c>
-      <c r="D9" s="18">
-        <f>Drivers!D9</f>
-        <v>75000</v>
-      </c>
-      <c r="E9" s="18">
-        <f>Drivers!E9</f>
-        <v>75000</v>
-      </c>
-      <c r="F9" s="18">
-        <f>Drivers!F9</f>
-        <v>75000</v>
-      </c>
-      <c r="G9" s="18">
-        <f>Drivers!G9</f>
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="20">
-        <f>Drivers!C10</f>
-        <v>995000</v>
-      </c>
-      <c r="D10" s="20">
-        <f>Drivers!D10</f>
-        <v>1306880</v>
-      </c>
-      <c r="E10" s="20">
-        <f>Drivers!E10</f>
-        <v>1636644.8</v>
-      </c>
-      <c r="F10" s="20">
-        <f>Drivers!F10</f>
-        <v>1934821.354</v>
-      </c>
-      <c r="G10" s="20">
-        <f>Drivers!G10</f>
-        <v>2145936.2104</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="18">
-        <f>Drivers!C16</f>
-        <v>824466.66666667</v>
-      </c>
-      <c r="D12" s="18">
-        <f>Drivers!D16</f>
-        <v>951514</v>
-      </c>
-      <c r="E12" s="18">
-        <f>Drivers!E16</f>
-        <v>1138133.52</v>
-      </c>
-      <c r="F12" s="18">
-        <f>Drivers!F16</f>
-        <v>1280821.74093333</v>
-      </c>
-      <c r="G12" s="18">
-        <f>Drivers!G16</f>
-        <v>1431046.93495467</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="18">
-        <f>Drivers!C22</f>
-        <v>271400</v>
-      </c>
-      <c r="D13" s="18">
-        <f>Drivers!D22</f>
-        <v>334544</v>
-      </c>
-      <c r="E13" s="18">
-        <f>Drivers!E22</f>
-        <v>423893.204</v>
-      </c>
-      <c r="F13" s="18">
-        <f>Drivers!F22</f>
-        <v>543450.5083634</v>
-      </c>
-      <c r="G13" s="18">
-        <f>Drivers!G22</f>
-        <v>692109.07850888</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="20">
-        <f>C12+C13</f>
-        <v>1095866.66666667</v>
-      </c>
-      <c r="D15" s="20">
-        <f>D12+D13</f>
-        <v>1286058</v>
-      </c>
-      <c r="E15" s="20">
-        <f>E12+E13</f>
-        <v>1562026.724</v>
-      </c>
-      <c r="F15" s="20">
-        <f>F12+F13</f>
-        <v>1824272.24929673</v>
-      </c>
-      <c r="G15" s="20">
-        <f>G12+G13</f>
-        <v>2123156.01346354</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" s="21">
-        <f>C10-C15</f>
-        <v>-100866.66666667</v>
-      </c>
-      <c r="D16" s="22">
-        <f>D10-D15</f>
-        <v>20822</v>
-      </c>
-      <c r="E16" s="22">
-        <f>E10-E15</f>
-        <v>74618.076</v>
-      </c>
-      <c r="F16" s="22">
-        <f>F10-F15</f>
-        <v>110549.10470327</v>
-      </c>
-      <c r="G16" s="22">
-        <f>G10-G15</f>
-        <v>22780.19693646</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="23">
-        <f>IF(C10&gt;0,C16/C10,0)</f>
-        <v>-0.10137353</v>
-      </c>
-      <c r="D17" s="23">
-        <f>IF(D10&gt;0,D16/D10,0)</f>
-        <v>0.0159326</v>
-      </c>
-      <c r="E17" s="23">
-        <f>IF(E10&gt;0,E16/E10,0)</f>
-        <v>0.0455921</v>
-      </c>
-      <c r="F17" s="23">
-        <f>IF(F10&gt;0,F16/F10,0)</f>
-        <v>0.0571366</v>
-      </c>
-      <c r="G17" s="23">
-        <f>IF(G10&gt;0,G16/G10,0)</f>
-        <v>0.01061551</v>
       </c>
     </row>
   </sheetData>
@@ -2286,10 +2747,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FFD97706"/>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G14"/>
+  <dimension ref="B1:G17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -2298,206 +2759,306 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="16"/>
+      <c r="C3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="19">
+        <f>Drivers!C4</f>
+        <v>100</v>
+      </c>
+      <c r="D5" s="19">
+        <f>Drivers!D4</f>
+        <v>130</v>
+      </c>
+      <c r="E5" s="19">
+        <f>Drivers!E4</f>
+        <v>160</v>
+      </c>
+      <c r="F5" s="19">
+        <f>Drivers!F4</f>
+        <v>185</v>
+      </c>
+      <c r="G5" s="19">
+        <f>Drivers!G4</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="14"/>
-      <c r="C3" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="18">
-        <f>'5-Year P&amp;L'!C16</f>
+      <c r="C6" s="20" t="str">
+        <f>Drivers!C6</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="20" t="str">
+        <f>Drivers!D6</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="20" t="str">
+        <f>Drivers!E6</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="20" t="str">
+        <f>Drivers!F6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="20" t="str">
+        <f>Drivers!G6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="20">
+        <f>Drivers!C7</f>
+        <v>870000</v>
+      </c>
+      <c r="D7" s="20">
+        <f>Drivers!D7</f>
+        <v>1164930</v>
+      </c>
+      <c r="E7" s="20">
+        <f>Drivers!E7</f>
+        <v>1476772.8</v>
+      </c>
+      <c r="F7" s="20">
+        <f>Drivers!F7</f>
+        <v>1758744.1065</v>
+      </c>
+      <c r="G7" s="20">
+        <f>Drivers!G7</f>
+        <v>1958385.3294</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="20">
+        <f>Drivers!C8</f>
+        <v>50000</v>
+      </c>
+      <c r="D8" s="20">
+        <f>Drivers!D8</f>
+        <v>66950</v>
+      </c>
+      <c r="E8" s="20">
+        <f>Drivers!E8</f>
+        <v>84872</v>
+      </c>
+      <c r="F8" s="20">
+        <f>Drivers!F8</f>
+        <v>101077.2475</v>
+      </c>
+      <c r="G8" s="20">
+        <f>Drivers!G8</f>
+        <v>112550.881</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="20">
+        <f>Drivers!C9</f>
+        <v>75000</v>
+      </c>
+      <c r="D9" s="20">
+        <f>Drivers!D9</f>
+        <v>75000</v>
+      </c>
+      <c r="E9" s="20">
+        <f>Drivers!E9</f>
+        <v>75000</v>
+      </c>
+      <c r="F9" s="20">
+        <f>Drivers!F9</f>
+        <v>75000</v>
+      </c>
+      <c r="G9" s="20">
+        <f>Drivers!G9</f>
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="22">
+        <f>Drivers!C10</f>
+        <v>995000</v>
+      </c>
+      <c r="D10" s="22">
+        <f>Drivers!D10</f>
+        <v>1306880</v>
+      </c>
+      <c r="E10" s="22">
+        <f>Drivers!E10</f>
+        <v>1636644.8</v>
+      </c>
+      <c r="F10" s="22">
+        <f>Drivers!F10</f>
+        <v>1934821.354</v>
+      </c>
+      <c r="G10" s="22">
+        <f>Drivers!G10</f>
+        <v>2145936.2104</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="20">
+        <f>Drivers!C16</f>
+        <v>824466.66666667</v>
+      </c>
+      <c r="D12" s="20">
+        <f>Drivers!D16</f>
+        <v>951514</v>
+      </c>
+      <c r="E12" s="20">
+        <f>Drivers!E16</f>
+        <v>1138133.52</v>
+      </c>
+      <c r="F12" s="20">
+        <f>Drivers!F16</f>
+        <v>1280821.74093333</v>
+      </c>
+      <c r="G12" s="20">
+        <f>Drivers!G16</f>
+        <v>1431046.93495467</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="20">
+        <f>Drivers!C22</f>
+        <v>271400</v>
+      </c>
+      <c r="D13" s="20">
+        <f>Drivers!D22</f>
+        <v>334544</v>
+      </c>
+      <c r="E13" s="20">
+        <f>Drivers!E22</f>
+        <v>423893.204</v>
+      </c>
+      <c r="F13" s="20">
+        <f>Drivers!F22</f>
+        <v>543450.5083634</v>
+      </c>
+      <c r="G13" s="20">
+        <f>Drivers!G22</f>
+        <v>692109.07850888</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="22">
+        <f>C12+C13</f>
+        <v>1095866.66666667</v>
+      </c>
+      <c r="D15" s="22">
+        <f>D12+D13</f>
+        <v>1286058</v>
+      </c>
+      <c r="E15" s="22">
+        <f>E12+E13</f>
+        <v>1562026.724</v>
+      </c>
+      <c r="F15" s="22">
+        <f>F12+F13</f>
+        <v>1824272.24929673</v>
+      </c>
+      <c r="G15" s="22">
+        <f>G12+G13</f>
+        <v>2123156.01346354</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="23">
+        <f>C10-C15</f>
         <v>-100866.66666667</v>
       </c>
-      <c r="D4" s="18">
-        <f>'5-Year P&amp;L'!D16</f>
+      <c r="D16" s="24">
+        <f>D10-D15</f>
         <v>20822</v>
       </c>
-      <c r="E4" s="18">
-        <f>'5-Year P&amp;L'!E16</f>
+      <c r="E16" s="24">
+        <f>E10-E15</f>
         <v>74618.076</v>
       </c>
-      <c r="F4" s="18">
-        <f>'5-Year P&amp;L'!F16</f>
+      <c r="F16" s="24">
+        <f>F10-F15</f>
         <v>110549.10470327</v>
       </c>
-      <c r="G4" s="18">
-        <f>'5-Year P&amp;L'!G16</f>
+      <c r="G16" s="24">
+        <f>G10-G15</f>
         <v>22780.19693646</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="18">
-        <f>Assumptions!D58</f>
-        <v>25000</v>
-      </c>
-      <c r="D6" s="18">
-        <f>Assumptions!D58</f>
-        <v>25000</v>
-      </c>
-      <c r="E6" s="18">
-        <f>Assumptions!D58</f>
-        <v>25000</v>
-      </c>
-      <c r="F6" s="18">
-        <f>Assumptions!D58</f>
-        <v>25000</v>
-      </c>
-      <c r="G6" s="18">
-        <f>Assumptions!D58</f>
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="18">
-        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>34064.39316601</v>
-      </c>
-      <c r="D7" s="18">
-        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>34064.39316601</v>
-      </c>
-      <c r="E7" s="18">
-        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>34064.39316601</v>
-      </c>
-      <c r="F7" s="18">
-        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>34064.39316601</v>
-      </c>
-      <c r="G7" s="18">
-        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>34064.39316601</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="20">
-        <f>C6+C7</f>
-        <v>59064.39316601</v>
-      </c>
-      <c r="D8" s="20">
-        <f>D6+D7</f>
-        <v>59064.39316601</v>
-      </c>
-      <c r="E8" s="20">
-        <f>E6+E7</f>
-        <v>59064.39316601</v>
-      </c>
-      <c r="F8" s="20">
-        <f>F6+F7</f>
-        <v>59064.39316601</v>
-      </c>
-      <c r="G8" s="20">
-        <f>G6+G7</f>
-        <v>59064.39316601</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="24">
-        <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
-        <v>-1.70774068</v>
-      </c>
-      <c r="D10" s="24">
-        <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
-        <v>0.3525305</v>
-      </c>
-      <c r="E10" s="25">
-        <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
-        <v>1.26333434</v>
-      </c>
-      <c r="F10" s="25">
-        <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
-        <v>1.87167088</v>
-      </c>
-      <c r="G10" s="24">
-        <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
-        <v>0.38568409</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="18">
-        <f>C4-C8</f>
-        <v>-159931.05983267</v>
-      </c>
-      <c r="D12" s="18">
-        <f>D4-D8</f>
-        <v>-38242.39316601</v>
-      </c>
-      <c r="E12" s="18">
-        <f>E4-E8</f>
-        <v>15553.68283399</v>
-      </c>
-      <c r="F12" s="18">
-        <f>F4-F8</f>
-        <v>51484.71153726</v>
-      </c>
-      <c r="G12" s="18">
-        <f>G4-G8</f>
-        <v>-36284.19622955</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="26">
-        <f>Assumptions!D57+C12</f>
-        <v>-84931.05983267</v>
-      </c>
-      <c r="D14" s="26">
-        <f>C14+D12</f>
-        <v>-123173.45299868</v>
-      </c>
-      <c r="E14" s="26">
-        <f>D14+E12</f>
-        <v>-107619.77016469</v>
-      </c>
-      <c r="F14" s="26">
-        <f>E14+F12</f>
-        <v>-56135.05862743</v>
-      </c>
-      <c r="G14" s="26">
-        <f>F14+G12</f>
-        <v>-92419.25485698</v>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="25">
+        <f>IF(C10&gt;0,C16/C10,0)</f>
+        <v>-0.10137353</v>
+      </c>
+      <c r="D17" s="25">
+        <f>IF(D10&gt;0,D16/D10,0)</f>
+        <v>0.0159326</v>
+      </c>
+      <c r="E17" s="25">
+        <f>IF(E10&gt;0,E16/E10,0)</f>
+        <v>0.0455921</v>
+      </c>
+      <c r="F17" s="25">
+        <f>IF(F10&gt;0,F16/F10,0)</f>
+        <v>0.0571366</v>
+      </c>
+      <c r="G17" s="25">
+        <f>IF(G10&gt;0,G16/G10,0)</f>
+        <v>0.01061551</v>
       </c>
     </row>
   </sheetData>
@@ -2515,10 +3076,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF0D9488"/>
+    <tabColor rgb="FFD97706"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G6"/>
+  <dimension ref="B1:G14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -2527,106 +3088,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="B1" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="14"/>
-      <c r="C3" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>69</v>
+      <c r="B3" s="16"/>
+      <c r="C3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" s="17">
-        <f>Drivers!C12</f>
-        <v>10</v>
-      </c>
-      <c r="D4" s="17">
-        <f>Drivers!D12</f>
-        <v>12</v>
-      </c>
-      <c r="E4" s="17">
-        <f>Drivers!E12</f>
-        <v>15</v>
-      </c>
-      <c r="F4" s="17">
-        <f>Drivers!F12</f>
-        <v>17</v>
-      </c>
-      <c r="G4" s="17">
-        <f>Drivers!G12</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="17">
-        <f>Assumptions!D35</f>
-        <v>4</v>
-      </c>
-      <c r="D5" s="17">
-        <f>Assumptions!D36</f>
-        <v>4</v>
-      </c>
-      <c r="E5" s="17">
-        <f>Assumptions!D37</f>
-        <v>4</v>
-      </c>
-      <c r="F5" s="17">
-        <f>Assumptions!D38</f>
-        <v>4</v>
-      </c>
-      <c r="G5" s="17">
-        <f>Assumptions!D39</f>
-        <v>4</v>
+      <c r="B4" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="20">
+        <f>'5-Year P&amp;L'!C16</f>
+        <v>-100866.66666667</v>
+      </c>
+      <c r="D4" s="20">
+        <f>'5-Year P&amp;L'!D16</f>
+        <v>20822</v>
+      </c>
+      <c r="E4" s="20">
+        <f>'5-Year P&amp;L'!E16</f>
+        <v>74618.076</v>
+      </c>
+      <c r="F4" s="20">
+        <f>'5-Year P&amp;L'!F16</f>
+        <v>110549.10470327</v>
+      </c>
+      <c r="G4" s="20">
+        <f>'5-Year P&amp;L'!G16</f>
+        <v>22780.19693646</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="27">
-        <f>C4+C5</f>
-        <v>14</v>
-      </c>
-      <c r="D6" s="27">
-        <f>D4+D5</f>
-        <v>16</v>
-      </c>
-      <c r="E6" s="27">
-        <f>E4+E5</f>
-        <v>19</v>
-      </c>
-      <c r="F6" s="27">
-        <f>F4+F5</f>
-        <v>21</v>
-      </c>
-      <c r="G6" s="27">
-        <f>G4+G5</f>
-        <v>23</v>
+      <c r="B6" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="20">
+        <f>Assumptions!D58</f>
+        <v>25000</v>
+      </c>
+      <c r="D6" s="20">
+        <f>Assumptions!D58</f>
+        <v>25000</v>
+      </c>
+      <c r="E6" s="20">
+        <f>Assumptions!D58</f>
+        <v>25000</v>
+      </c>
+      <c r="F6" s="20">
+        <f>Assumptions!D58</f>
+        <v>25000</v>
+      </c>
+      <c r="G6" s="20">
+        <f>Assumptions!D58</f>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="20">
+        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
+        <v>34064.39316601</v>
+      </c>
+      <c r="D7" s="20">
+        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
+        <v>34064.39316601</v>
+      </c>
+      <c r="E7" s="20">
+        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
+        <v>34064.39316601</v>
+      </c>
+      <c r="F7" s="20">
+        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
+        <v>34064.39316601</v>
+      </c>
+      <c r="G7" s="20">
+        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
+        <v>34064.39316601</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="22">
+        <f>C6+C7</f>
+        <v>59064.39316601</v>
+      </c>
+      <c r="D8" s="22">
+        <f>D6+D7</f>
+        <v>59064.39316601</v>
+      </c>
+      <c r="E8" s="22">
+        <f>E6+E7</f>
+        <v>59064.39316601</v>
+      </c>
+      <c r="F8" s="22">
+        <f>F6+F7</f>
+        <v>59064.39316601</v>
+      </c>
+      <c r="G8" s="22">
+        <f>G6+G7</f>
+        <v>59064.39316601</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="26">
+        <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
+        <v>-1.70774068</v>
+      </c>
+      <c r="D10" s="26">
+        <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
+        <v>0.3525305</v>
+      </c>
+      <c r="E10" s="27">
+        <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
+        <v>1.26333434</v>
+      </c>
+      <c r="F10" s="27">
+        <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
+        <v>1.87167088</v>
+      </c>
+      <c r="G10" s="26">
+        <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
+        <v>0.38568409</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="20">
+        <f>C4-C8</f>
+        <v>-159931.05983267</v>
+      </c>
+      <c r="D12" s="20">
+        <f>D4-D8</f>
+        <v>-38242.39316601</v>
+      </c>
+      <c r="E12" s="20">
+        <f>E4-E8</f>
+        <v>15553.68283399</v>
+      </c>
+      <c r="F12" s="20">
+        <f>F4-F8</f>
+        <v>51484.71153726</v>
+      </c>
+      <c r="G12" s="20">
+        <f>G4-G8</f>
+        <v>-36284.19622955</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="28">
+        <f>Assumptions!D57+C12</f>
+        <v>-84931.05983267</v>
+      </c>
+      <c r="D14" s="28">
+        <f>C14+D12</f>
+        <v>-123173.45299868</v>
+      </c>
+      <c r="E14" s="28">
+        <f>D14+E12</f>
+        <v>-107619.77016469</v>
+      </c>
+      <c r="F14" s="28">
+        <f>E14+F12</f>
+        <v>-56135.05862743</v>
+      </c>
+      <c r="G14" s="28">
+        <f>F14+G12</f>
+        <v>-92419.25485698</v>
       </c>
     </row>
   </sheetData>
@@ -2644,6 +3305,135 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF0D9488"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:G6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="16"/>
+      <c r="C3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="19">
+        <f>Drivers!C12</f>
+        <v>10</v>
+      </c>
+      <c r="D4" s="19">
+        <f>Drivers!D12</f>
+        <v>12</v>
+      </c>
+      <c r="E4" s="19">
+        <f>Drivers!E12</f>
+        <v>15</v>
+      </c>
+      <c r="F4" s="19">
+        <f>Drivers!F12</f>
+        <v>17</v>
+      </c>
+      <c r="G4" s="19">
+        <f>Drivers!G12</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="19">
+        <f>Assumptions!D35</f>
+        <v>4</v>
+      </c>
+      <c r="D5" s="19">
+        <f>Assumptions!D36</f>
+        <v>4</v>
+      </c>
+      <c r="E5" s="19">
+        <f>Assumptions!D37</f>
+        <v>4</v>
+      </c>
+      <c r="F5" s="19">
+        <f>Assumptions!D38</f>
+        <v>4</v>
+      </c>
+      <c r="G5" s="19">
+        <f>Assumptions!D39</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="29">
+        <f>C4+C5</f>
+        <v>14</v>
+      </c>
+      <c r="D6" s="29">
+        <f>D4+D5</f>
+        <v>16</v>
+      </c>
+      <c r="E6" s="29">
+        <f>E4+E5</f>
+        <v>19</v>
+      </c>
+      <c r="F6" s="29">
+        <f>F4+F5</f>
+        <v>21</v>
+      </c>
+      <c r="G6" s="29">
+        <f>G4+G5</f>
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor rgb="FFD97706"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2656,52 +3446,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" s="7"/>
+      <c r="B1" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="9"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="18">
+      <c r="B3" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" s="20">
         <f>Assumptions!D59</f>
         <v>250000</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="23">
+      <c r="B4" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="25">
         <f>Assumptions!D60</f>
         <v>0.065</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="17">
+      <c r="B5" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="19">
         <f>Assumptions!D61</f>
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="28">
+      <c r="B6" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" s="30">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" s="24">
+      <c r="B8" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="26">
         <f>'Cash Flow &amp; DSCR'!C10</f>
         <v>-1.70774068</v>
       </c>
@@ -2718,7 +3508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF328555"/>
@@ -2733,77 +3523,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C1" s="7"/>
+      <c r="B1" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="9"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="16" t="str">
+      <c r="B3" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="18" t="str">
         <f>Assumptions!D5</f>
         <v>Heritage Academy</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="16" t="str">
+      <c r="B4" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="18" t="str">
         <f>Assumptions!D7</f>
         <v>Private School</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="16" t="str">
+      <c r="B5" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="18" t="str">
         <f>Assumptions!D6</f>
         <v>FL</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="C6" s="16">
+      <c r="B6" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="18">
         <f>Assumptions!D8</f>
         <v>2023</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="17">
+      <c r="B8" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="19">
         <f>Assumptions!D16</f>
         <v>200</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="18">
+      <c r="B9" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="20">
         <f>Drivers!G10</f>
         <v>2145936.2104</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="C10" s="29">
+      <c r="B10" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="31">
         <f>'5-Year P&amp;L'!G16</f>
         <v>22780.19693646</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="C12" s="6"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="185">
   <si>
     <t>SCHOOLSTACK BUDGET</t>
   </si>
@@ -133,6 +133,9 @@
     <t>SchoolStack Budget - Lender Pro Forma Assumptions</t>
   </si>
   <si>
+    <t>Blue cells are editable inputs</t>
+  </si>
+  <si>
     <t>SCHOOL PROFILE</t>
   </si>
   <si>
@@ -464,6 +467,27 @@
   </si>
   <si>
     <t>Net Margin</t>
+  </si>
+  <si>
+    <t>Revenue per Student</t>
+  </si>
+  <si>
+    <t>Payroll %</t>
+  </si>
+  <si>
+    <t>Facility %</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
+    <t>Break-even Year</t>
+  </si>
+  <si>
+    <t>Cash Runway</t>
+  </si>
+  <si>
+    <t>5 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -563,7 +587,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -617,6 +641,12 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <color rgb="FF666666"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -628,7 +658,7 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF1E293B"/>
+      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -639,13 +669,13 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFDC2626"/>
+      <color rgb="FF16A34A"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF16A34A"/>
+      <color rgb="FFDC2626"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -665,12 +695,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE8"/>
+        <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
     <fill>
@@ -754,7 +784,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -765,24 +795,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -792,49 +824,60 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="166" fontId="13" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -846,7 +889,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1303,7 +1346,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G26"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1314,7 +1357,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -1333,355 +1376,481 @@
       <c r="G3" s="6"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="33" t="s">
+      <c r="B5" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="D5" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="E5" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="F5" s="35" t="s">
         <v>92</v>
       </c>
+      <c r="G5" s="35" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="19">
+      <c r="B6" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="21">
         <v>100</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="21">
         <v>130</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="21">
         <v>160</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="21">
         <v>185</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="21">
         <v>200</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="20">
+      <c r="B7" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="22">
         <v>995000</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="22">
         <v>1306880</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="22">
         <v>1636644.8</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="22">
         <v>1934821.354</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="22">
         <v>2145936.2104</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C8" s="20">
+      <c r="B8" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="22">
         <v>824466.6666666666</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="22">
         <v>951514</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="22">
         <v>1138133.52</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="22">
         <v>1280821.7409333333</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="22">
         <v>1431046.934954667</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C9" s="20">
+      <c r="B9" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" s="22">
         <v>271400</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="22">
         <v>334544</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="22">
         <v>423893.20399999997</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="22">
         <v>543450.5083634</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="22">
         <v>692109.0785088772</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="20">
+      <c r="B10" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="22">
         <v>59064.39316600799</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="22">
         <v>59064.39316600799</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="22">
         <v>59064.39316600799</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="22">
         <v>59064.39316600799</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="22">
         <v>59064.39316600799</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="C11" s="23">
+      <c r="B11" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" s="25">
         <v>-159931.0598326745</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="25">
         <v>-38242.39316600799</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="26">
         <v>15553.682833992127</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="26">
         <v>51484.71153725888</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="25">
         <v>-36284.19622955197</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="C12" s="23">
+      <c r="B12" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="25">
         <v>-84931.05983267451</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="25">
         <v>-123173.45299868251</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="25">
         <v>-107619.77016469039</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="25">
         <v>-56135.05862743151</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="25">
         <v>-92419.25485698348</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="C13" s="34">
+      <c r="B13" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="36">
         <v>-0.1607347335001754</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="36">
         <v>-0.029262360098867523</v>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="37">
         <v>0.009503395504016587</v>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="37">
         <v>0.026609542752265323</v>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="36">
         <v>-0.016908329359328268</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="C15" s="32" t="s">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="C14" s="22">
+        <v>9950</v>
+      </c>
+      <c r="D14" s="22">
+        <v>10052.923076923076</v>
+      </c>
+      <c r="E14" s="22">
+        <v>10229.03</v>
+      </c>
+      <c r="F14" s="22">
+        <v>10458.493805405406</v>
+      </c>
+      <c r="G14" s="22">
+        <v>10729.681052000002</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32" t="s">
+      <c r="C15" s="36">
+        <v>0.8286097152428811</v>
+      </c>
+      <c r="D15" s="36">
+        <v>0.7280806194906954</v>
+      </c>
+      <c r="E15" s="36">
+        <v>0.6954065537005952</v>
+      </c>
+      <c r="F15" s="36">
+        <v>0.6619844970624266</v>
+      </c>
+      <c r="G15" s="36">
+        <v>0.6668636877551553</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="G15" s="32"/>
-    </row>
-    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="36" t="s">
+      <c r="C16" s="38">
+        <v>0.08182914572864322</v>
+      </c>
+      <c r="D16" s="38">
+        <v>0.0767960333006856</v>
+      </c>
+      <c r="E16" s="38">
+        <v>0.07770040341068507</v>
+      </c>
+      <c r="F16" s="38">
+        <v>0.0842636722878654</v>
+      </c>
+      <c r="G16" s="38">
+        <v>0.09675624212238845</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="36">
+        <v>-0.10137353433835843</v>
+      </c>
+      <c r="D17" s="37">
+        <v>0.015932602840352597</v>
+      </c>
+      <c r="E17" s="37">
+        <v>0.04559210159712117</v>
+      </c>
+      <c r="F17" s="37">
+        <v>0.057136595311355426</v>
+      </c>
+      <c r="G17" s="37">
+        <v>0.010615505170216507</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C18" s="39">
+        <v>-1.7077406752181137</v>
+      </c>
+      <c r="D18" s="39">
+        <v>0.35253049906865414</v>
+      </c>
+      <c r="E18" s="40">
+        <v>1.2633343373269994</v>
+      </c>
+      <c r="F18" s="40">
+        <v>1.871670879484945</v>
+      </c>
+      <c r="G18" s="39">
+        <v>0.38568409350163607</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="C19" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="E16" s="38"/>
-      <c r="F16" s="39" t="s">
+      <c r="C20" s="42" t="s">
         <v>155</v>
       </c>
-      <c r="G16" s="39"/>
-    </row>
-    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="36" t="s">
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="C17" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="D17" s="38" t="s">
+      <c r="C22" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="E17" s="38"/>
-      <c r="F17" s="39" t="s">
+      <c r="D22" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="G17" s="39"/>
-    </row>
-    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="36" t="s">
+      <c r="E22" s="34"/>
+      <c r="F22" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="C18" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="D18" s="38" t="s">
+      <c r="G22" s="34"/>
+    </row>
+    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="43" t="s">
         <v>160</v>
       </c>
-      <c r="E18" s="38"/>
-      <c r="F18" s="39" t="s">
+      <c r="C23" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="G18" s="39"/>
-    </row>
-    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="36" t="s">
+      <c r="D23" s="45" t="s">
         <v>162</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="E23" s="45"/>
+      <c r="F23" s="46" t="s">
         <v>163</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="G23" s="46"/>
+    </row>
+    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="43" t="s">
         <v>164</v>
       </c>
-      <c r="E19" s="38"/>
-      <c r="F19" s="39" t="s">
+      <c r="C24" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24" s="45" t="s">
         <v>165</v>
       </c>
-      <c r="G19" s="39"/>
-    </row>
-    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="36" t="s">
+      <c r="E24" s="45"/>
+      <c r="F24" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="C20" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="D20" s="38" t="s">
+      <c r="G24" s="46"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="43" t="s">
         <v>167</v>
       </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="39" t="s">
+      <c r="C25" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="D25" s="45" t="s">
         <v>168</v>
       </c>
-      <c r="G20" s="39"/>
-    </row>
-    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="36" t="s">
+      <c r="E25" s="45"/>
+      <c r="F25" s="46" t="s">
         <v>169</v>
       </c>
-      <c r="C21" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D21" s="38" t="s">
+      <c r="G25" s="46"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="43" t="s">
         <v>170</v>
       </c>
-      <c r="E21" s="38"/>
-      <c r="F21" s="39" t="s">
+      <c r="C26" s="47" t="s">
         <v>171</v>
       </c>
-      <c r="G21" s="39"/>
-    </row>
-    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="36" t="s">
+      <c r="D26" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C22" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="D22" s="38" t="s">
+      <c r="E26" s="45"/>
+      <c r="F26" s="46" t="s">
         <v>173</v>
       </c>
-      <c r="E22" s="38"/>
-      <c r="F22" s="39" t="s">
+      <c r="G26" s="46"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="43" t="s">
         <v>174</v>
       </c>
-      <c r="G22" s="39"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="36" t="s">
+      <c r="C27" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="D27" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="E27" s="45"/>
+      <c r="F27" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="G27" s="46"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="D28" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="E28" s="45"/>
+      <c r="F28" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="G28" s="46"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="C29" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="E29" s="45"/>
+      <c r="F29" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="G29" s="46"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
+      <c r="C31" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="48" t="s">
+        <v>184</v>
+      </c>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="B33:G33"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -1869,381 +2038,389 @@
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
     </row>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
     <row r="3" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
+      <c r="B3" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="12" t="s">
+      <c r="C5" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>40</v>
       </c>
+      <c r="D6" s="14" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="12" t="s">
+      <c r="C7" s="13" t="s">
         <v>42</v>
       </c>
+      <c r="D7" s="14" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="12">
+      <c r="C8" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="14">
         <v>2023</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
+      <c r="B10" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="13">
+      <c r="C12" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="15">
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="13">
+      <c r="C13" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="15">
         <v>130</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="13">
+      <c r="C14" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="15">
         <v>160</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="13">
+      <c r="C15" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="15">
         <v>185</v>
       </c>
     </row>
     <row r="16" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="13">
+      <c r="C16" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="15">
         <v>200</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
+      <c r="B18" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="15">
+      <c r="C21" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="16">
         <v>8700</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="C23" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="14">
+      <c r="C24" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="16">
         <v>500</v>
       </c>
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="15">
+      <c r="C25" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="15">
+      <c r="C26" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="17">
         <v>0.95</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="16">
         <v>75000</v>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
+      <c r="B30" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D32" s="13">
+      <c r="C32" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="15">
         <v>11</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33" s="14">
+      <c r="C33" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="16">
         <v>40000</v>
       </c>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D34" s="15">
+      <c r="C34" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" s="13">
+      <c r="C35" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="15">
         <v>4</v>
       </c>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D36" s="13">
+      <c r="C36" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="15">
         <v>4</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D37" s="13">
+      <c r="C37" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="15">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D38" s="13">
+      <c r="C38" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="15">
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C39" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D39" s="13">
+      <c r="C39" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" s="15">
         <v>4</v>
       </c>
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C40" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D40" s="14">
+      <c r="C40" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" s="16">
         <v>66000</v>
       </c>
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C41" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D41" s="15">
+      <c r="C41" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D41" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C42" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D42" s="15">
+      <c r="C42" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" s="17">
         <v>0.24166666666666667</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
+      <c r="B44" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D46" s="14">
+      <c r="C46" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D46" s="16">
         <v>102000</v>
       </c>
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D47" s="15">
+      <c r="C47" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48" s="14">
+      <c r="C48" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D48" s="16">
         <v>34400</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D49" s="15">
+      <c r="C49" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D49" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D50" s="14">
+      <c r="C50" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D50" s="16">
         <v>600</v>
       </c>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D51" s="15">
+      <c r="C51" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D51" s="17">
         <v>0.339</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D52" s="14">
+      <c r="C52" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" s="16">
         <v>75000</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D53" s="15">
+      <c r="C53" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D53" s="17">
         <v>0.1948</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
+      <c r="B55" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C57" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D57" s="14">
+      <c r="C57" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D57" s="16">
         <v>75000</v>
       </c>
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C58" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D58" s="14">
+      <c r="C58" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D58" s="16">
         <v>25000</v>
       </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C59" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D59" s="14">
+      <c r="C59" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D59" s="16">
         <v>250000</v>
       </c>
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C60" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D60" s="15">
+      <c r="C60" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" s="17">
         <v>0.065</v>
       </c>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C61" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D61" s="13">
+      <c r="C61" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D61" s="15">
         <v>10</v>
       </c>
     </row>
@@ -2281,7 +2458,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -2290,444 +2467,444 @@
       <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="19" t="s">
         <v>92</v>
       </c>
+      <c r="G3" s="19" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="19">
+      <c r="B4" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="21">
         <f>Assumptions!D12</f>
         <v>100</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="21">
         <f>Assumptions!D13</f>
         <v>130</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="21">
         <f>Assumptions!D14</f>
         <v>160</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="21">
         <f>Assumptions!D15</f>
         <v>185</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="21">
         <f>Assumptions!D16</f>
         <v>200</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="20" t="str">
+      <c r="B5" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="22" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
         <v>0</v>
       </c>
-      <c r="D5" s="20" t="str">
+      <c r="D5" s="22" t="str">
         <f>Assumptions!D13*Assumptions!D20*(1+Assumptions!D21)^1</f>
         <v>0</v>
       </c>
-      <c r="E5" s="20" t="str">
+      <c r="E5" s="22" t="str">
         <f>Assumptions!D14*Assumptions!D20*(1+Assumptions!D21)^2</f>
         <v>0</v>
       </c>
-      <c r="F5" s="20" t="str">
+      <c r="F5" s="22" t="str">
         <f>Assumptions!D15*Assumptions!D20*(1+Assumptions!D21)^3</f>
         <v>0</v>
       </c>
-      <c r="G5" s="20" t="str">
+      <c r="G5" s="22" t="str">
         <f>Assumptions!D16*Assumptions!D20*(1+Assumptions!D21)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="20" t="str">
+      <c r="B6" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="22" t="str">
         <f>C5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="D6" s="20" t="str">
+      <c r="D6" s="22" t="str">
         <f>D5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="E6" s="20" t="str">
+      <c r="E6" s="22" t="str">
         <f>E5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="F6" s="20" t="str">
+      <c r="F6" s="22" t="str">
         <f>F5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="G6" s="20" t="str">
+      <c r="G6" s="22" t="str">
         <f>G5*Assumptions!D26</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="C7" s="20">
+      <c r="B7" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="22">
         <f>Assumptions!D12*Assumptions!D22</f>
         <v>870000</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="22">
         <f>Assumptions!D13*Assumptions!D22*(1+Assumptions!D23)^1</f>
         <v>1164930</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="22">
         <f>Assumptions!D14*Assumptions!D22*(1+Assumptions!D23)^2</f>
         <v>1476772.8</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="22">
         <f>Assumptions!D15*Assumptions!D22*(1+Assumptions!D23)^3</f>
         <v>1758744.1065</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="22">
         <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
         <v>1958385.3294</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="20">
+      <c r="B8" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="22">
         <f>Assumptions!D12*Assumptions!D24</f>
         <v>50000</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="22">
         <f>Assumptions!D13*Assumptions!D24*(1+Assumptions!D25)^1</f>
         <v>66950</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="22">
         <f>Assumptions!D14*Assumptions!D24*(1+Assumptions!D25)^2</f>
         <v>84872</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="22">
         <f>Assumptions!D15*Assumptions!D24*(1+Assumptions!D25)^3</f>
         <v>101077.2475</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="22">
         <f>Assumptions!D16*Assumptions!D24*(1+Assumptions!D25)^4</f>
         <v>112550.881</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="20">
+      <c r="B9" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="22">
         <f>Assumptions!D27</f>
         <v>75000</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="22">
         <f>Assumptions!D27*(1+Assumptions!D28)^1</f>
         <v>75000</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="22">
         <f>Assumptions!D27*(1+Assumptions!D28)^2</f>
         <v>75000</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="22">
         <f>Assumptions!D27*(1+Assumptions!D28)^3</f>
         <v>75000</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="22">
         <f>Assumptions!D27*(1+Assumptions!D28)^4</f>
         <v>75000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="22">
+      <c r="B10" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="24">
         <f>C6+C7+C8+C9</f>
         <v>995000</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="24">
         <f>D6+D7+D8+D9</f>
         <v>1306880</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="24">
         <f>E6+E7+E8+E9</f>
         <v>1636644.8</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="24">
         <f>F6+F7+F8+F9</f>
         <v>1934821.354</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="24">
         <f>G6+G7+G8+G9</f>
         <v>2145936.2104</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="19">
+      <c r="B12" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="21">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
         <v>10</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="21">
         <f>CEILING(Assumptions!D13/Assumptions!D32,1)</f>
         <v>12</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="21">
         <f>CEILING(Assumptions!D14/Assumptions!D32,1)</f>
         <v>15</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="21">
         <f>CEILING(Assumptions!D15/Assumptions!D32,1)</f>
         <v>17</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="21">
         <f>CEILING(Assumptions!D16/Assumptions!D32,1)</f>
         <v>19</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="20">
+      <c r="B13" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="22">
         <f>C12*Assumptions!D33</f>
         <v>400000</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="22">
         <f>D12*Assumptions!D33*(1+Assumptions!D34)^1</f>
         <v>494400</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="22">
         <f>E12*Assumptions!D33*(1+Assumptions!D34)^2</f>
         <v>636540</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="22">
         <f>F12*Assumptions!D33*(1+Assumptions!D34)^3</f>
         <v>743054.36</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="22">
         <f>G12*Assumptions!D33*(1+Assumptions!D34)^4</f>
         <v>855386.6956</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="20">
+      <c r="B14" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="22">
         <f>Assumptions!D35*Assumptions!D40</f>
         <v>264000</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="22">
         <f>Assumptions!D36*Assumptions!D40*(1+Assumptions!D41)^1</f>
         <v>271920</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="22">
         <f>Assumptions!D37*Assumptions!D40*(1+Assumptions!D41)^2</f>
         <v>280077.6</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="22">
         <f>Assumptions!D38*Assumptions!D40*(1+Assumptions!D41)^3</f>
         <v>288479.928</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="22">
         <f>Assumptions!D39*Assumptions!D40*(1+Assumptions!D41)^4</f>
         <v>297134.32584</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="20">
+      <c r="B15" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="22">
         <f>(C13+C14)*Assumptions!D42</f>
         <v>160466.66666667</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="22">
         <f>(D13+D14)*Assumptions!D42</f>
         <v>185194</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="22">
         <f>(E13+E14)*Assumptions!D42</f>
         <v>221515.92</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="22">
         <f>(F13+F14)*Assumptions!D42</f>
         <v>249287.45293333</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="22">
         <f>(G13+G14)*Assumptions!D42</f>
         <v>278525.91351467</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="22">
+      <c r="B16" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="24">
         <f>C13+C14+C15</f>
         <v>824466.66666667</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="24">
         <f>D13+D14+D15</f>
         <v>951514</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="24">
         <f>E13+E14+E15</f>
         <v>1138133.52</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="24">
         <f>F13+F14+F15</f>
         <v>1280821.74093333</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="24">
         <f>G13+G14+G15</f>
         <v>1431046.93495467</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="20">
+      <c r="B18" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="22">
         <f>Assumptions!D46</f>
         <v>102000</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="22">
         <f>Assumptions!D46*(1+Assumptions!D47)^1</f>
         <v>105060</v>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="22">
         <f>Assumptions!D46*(1+Assumptions!D47)^2</f>
         <v>108211.8</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="22">
         <f>Assumptions!D46*(1+Assumptions!D47)^3</f>
         <v>111458.154</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="22">
         <f>Assumptions!D46*(1+Assumptions!D47)^4</f>
         <v>114801.89862</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19" s="20">
+      <c r="B19" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="22">
         <f>Assumptions!D48</f>
         <v>34400</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="22">
         <f>Assumptions!D48*(1+Assumptions!D49)^1</f>
         <v>35432</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="22">
         <f>Assumptions!D48*(1+Assumptions!D49)^2</f>
         <v>36494.96</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="22">
         <f>Assumptions!D48*(1+Assumptions!D49)^3</f>
         <v>37589.8088</v>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="22">
         <f>Assumptions!D48*(1+Assumptions!D49)^4</f>
         <v>38717.503064</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" s="20">
+      <c r="B20" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="22">
         <f>Assumptions!D12*Assumptions!D50</f>
         <v>60000</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="22">
         <f>Assumptions!D13*Assumptions!D50*(1+Assumptions!D51)^1</f>
         <v>104442</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="22">
         <f>Assumptions!D14*Assumptions!D50*(1+Assumptions!D51)^2</f>
         <v>172120.416</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="22">
         <f>Assumptions!D15*Assumptions!D50*(1+Assumptions!D51)^3</f>
         <v>266480.055309</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="22">
         <f>Assumptions!D16*Assumptions!D50*(1+Assumptions!D51)^4</f>
         <v>385747.88546892</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="20">
+      <c r="B21" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="22">
         <f>Assumptions!D52</f>
         <v>75000</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="22">
         <f>Assumptions!D52*(1+Assumptions!D53)^1</f>
         <v>89610</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="22">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
         <v>107066.028</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="22">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
         <v>127922.4902544</v>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="22">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
         <v>152841.79135596</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" s="22">
+      <c r="B22" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" s="24">
         <f>C18+C19+C20+C21</f>
         <v>271400</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="24">
         <f>D18+D19+D20+D21</f>
         <v>334544</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="24">
         <f>E18+E19+E20+E21</f>
         <v>423893.204</v>
       </c>
-      <c r="F22" s="22">
+      <c r="F22" s="24">
         <f>F18+F19+F20+F21</f>
         <v>543450.5083634</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="24">
         <f>G18+G19+G20+G21</f>
         <v>692109.07850888</v>
       </c>
@@ -2760,7 +2937,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -2769,294 +2946,294 @@
       <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="19" t="s">
         <v>92</v>
       </c>
+      <c r="G3" s="19" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="19">
+      <c r="B5" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="21">
         <f>Drivers!C4</f>
         <v>100</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="21">
         <f>Drivers!D4</f>
         <v>130</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="21">
         <f>Drivers!E4</f>
         <v>160</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="21">
         <f>Drivers!F4</f>
         <v>185</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="21">
         <f>Drivers!G4</f>
         <v>200</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="20" t="str">
+      <c r="B6" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="22" t="str">
         <f>Drivers!C6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="20" t="str">
+      <c r="D6" s="22" t="str">
         <f>Drivers!D6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="20" t="str">
+      <c r="E6" s="22" t="str">
         <f>Drivers!E6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="20" t="str">
+      <c r="F6" s="22" t="str">
         <f>Drivers!F6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="20" t="str">
+      <c r="G6" s="22" t="str">
         <f>Drivers!G6</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="20">
+      <c r="B7" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="22">
         <f>Drivers!C7</f>
         <v>870000</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="22">
         <f>Drivers!D7</f>
         <v>1164930</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="22">
         <f>Drivers!E7</f>
         <v>1476772.8</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="22">
         <f>Drivers!F7</f>
         <v>1758744.1065</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="22">
         <f>Drivers!G7</f>
         <v>1958385.3294</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="20">
+      <c r="B8" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="22">
         <f>Drivers!C8</f>
         <v>50000</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="22">
         <f>Drivers!D8</f>
         <v>66950</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="22">
         <f>Drivers!E8</f>
         <v>84872</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="22">
         <f>Drivers!F8</f>
         <v>101077.2475</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="22">
         <f>Drivers!G8</f>
         <v>112550.881</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="20">
+      <c r="B9" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="22">
         <f>Drivers!C9</f>
         <v>75000</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="22">
         <f>Drivers!D9</f>
         <v>75000</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="22">
         <f>Drivers!E9</f>
         <v>75000</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="22">
         <f>Drivers!F9</f>
         <v>75000</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="22">
         <f>Drivers!G9</f>
         <v>75000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="22">
+      <c r="B10" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="24">
         <f>Drivers!C10</f>
         <v>995000</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="24">
         <f>Drivers!D10</f>
         <v>1306880</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="24">
         <f>Drivers!E10</f>
         <v>1636644.8</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="24">
         <f>Drivers!F10</f>
         <v>1934821.354</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="24">
         <f>Drivers!G10</f>
         <v>2145936.2104</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="20">
+      <c r="B12" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="22">
         <f>Drivers!C16</f>
         <v>824466.66666667</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="22">
         <f>Drivers!D16</f>
         <v>951514</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="22">
         <f>Drivers!E16</f>
         <v>1138133.52</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="22">
         <f>Drivers!F16</f>
         <v>1280821.74093333</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="22">
         <f>Drivers!G16</f>
         <v>1431046.93495467</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="20">
+      <c r="B13" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="22">
         <f>Drivers!C22</f>
         <v>271400</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="22">
         <f>Drivers!D22</f>
         <v>334544</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="22">
         <f>Drivers!E22</f>
         <v>423893.204</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="22">
         <f>Drivers!F22</f>
         <v>543450.5083634</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="22">
         <f>Drivers!G22</f>
         <v>692109.07850888</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="22">
+      <c r="B15" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="24">
         <f>C12+C13</f>
         <v>1095866.66666667</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="24">
         <f>D12+D13</f>
         <v>1286058</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="24">
         <f>E12+E13</f>
         <v>1562026.724</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="24">
         <f>F12+F13</f>
         <v>1824272.24929673</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="24">
         <f>G12+G13</f>
         <v>2123156.01346354</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="C16" s="23">
+      <c r="B16" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="25">
         <f>C10-C15</f>
         <v>-100866.66666667</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="26">
         <f>D10-D15</f>
         <v>20822</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="26">
         <f>E10-E15</f>
         <v>74618.076</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="26">
         <f>F10-F15</f>
         <v>110549.10470327</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="26">
         <f>G10-G15</f>
         <v>22780.19693646</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="C17" s="25">
+      <c r="B17" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="27">
         <f>IF(C10&gt;0,C16/C10,0)</f>
         <v>-0.10137353</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="27">
         <f>IF(D10&gt;0,D16/D10,0)</f>
         <v>0.0159326</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="27">
         <f>IF(E10&gt;0,E16/E10,0)</f>
         <v>0.0455921</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="27">
         <f>IF(F10&gt;0,F16/F10,0)</f>
         <v>0.0571366</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="27">
         <f>IF(G10&gt;0,G16/G10,0)</f>
         <v>0.01061551</v>
       </c>
@@ -3089,7 +3266,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -3098,194 +3275,194 @@
       <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="19" t="s">
         <v>92</v>
       </c>
+      <c r="G3" s="19" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" s="20">
+      <c r="B4" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="22">
         <f>'5-Year P&amp;L'!C16</f>
         <v>-100866.66666667</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="22">
         <f>'5-Year P&amp;L'!D16</f>
         <v>20822</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="22">
         <f>'5-Year P&amp;L'!E16</f>
         <v>74618.076</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="22">
         <f>'5-Year P&amp;L'!F16</f>
         <v>110549.10470327</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="22">
         <f>'5-Year P&amp;L'!G16</f>
         <v>22780.19693646</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="C6" s="20">
+      <c r="B6" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="22">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="22">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="22">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="22">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="22">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="C7" s="20">
+      <c r="B7" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="22">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="22">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="22">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="22">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="22">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="C8" s="22">
+      <c r="B8" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="24">
         <f>C6+C7</f>
         <v>59064.39316601</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="24">
         <f>D6+D7</f>
         <v>59064.39316601</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="24">
         <f>E6+E7</f>
         <v>59064.39316601</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="24">
         <f>F6+F7</f>
         <v>59064.39316601</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="24">
         <f>G6+G7</f>
         <v>59064.39316601</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="26">
+      <c r="B10" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="28">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
         <v>-1.70774068</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="28">
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
         <v>0.3525305</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="29">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
         <v>1.26333434</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="29">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
         <v>1.87167088</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="28">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
         <v>0.38568409</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="20">
+      <c r="B12" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="22">
         <f>C4-C8</f>
         <v>-159931.05983267</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="22">
         <f>D4-D8</f>
         <v>-38242.39316601</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="22">
         <f>E4-E8</f>
         <v>15553.68283399</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="22">
         <f>F4-F8</f>
         <v>51484.71153726</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="22">
         <f>G4-G8</f>
         <v>-36284.19622955</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C14" s="28">
+      <c r="B14" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="30">
         <f>Assumptions!D57+C12</f>
         <v>-84931.05983267</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="30">
         <f>C14+D12</f>
         <v>-123173.45299868</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="30">
         <f>D14+E12</f>
         <v>-107619.77016469</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="30">
         <f>E14+F12</f>
         <v>-56135.05862743</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="30">
         <f>F14+G12</f>
         <v>-92419.25485698</v>
       </c>
@@ -3318,7 +3495,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -3327,94 +3504,94 @@
       <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="19" t="s">
         <v>92</v>
       </c>
+      <c r="G3" s="19" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4" s="19">
+      <c r="B4" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="21">
         <f>Drivers!C12</f>
         <v>10</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="21">
         <f>Drivers!D12</f>
         <v>12</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="21">
         <f>Drivers!E12</f>
         <v>15</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="21">
         <f>Drivers!F12</f>
         <v>17</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="21">
         <f>Drivers!G12</f>
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="19">
+      <c r="B5" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="21">
         <f>Assumptions!D35</f>
         <v>4</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="21">
         <f>Assumptions!D36</f>
         <v>4</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="21">
         <f>Assumptions!D37</f>
         <v>4</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="21">
         <f>Assumptions!D38</f>
         <v>4</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="21">
         <f>Assumptions!D39</f>
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="C6" s="29">
+      <c r="B6" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="31">
         <f>C4+C5</f>
         <v>14</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="31">
         <f>D4+D5</f>
         <v>16</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="31">
         <f>E4+E5</f>
         <v>19</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="31">
         <f>F4+F5</f>
         <v>21</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="31">
         <f>G4+G5</f>
         <v>23</v>
       </c>
@@ -3447,51 +3624,51 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C1" s="9"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="C3" s="20">
+      <c r="B3" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="22">
         <f>Assumptions!D59</f>
         <v>250000</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="25">
+      <c r="B4" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="27">
         <f>Assumptions!D60</f>
         <v>0.065</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="19">
+      <c r="B5" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="21">
         <f>Assumptions!D61</f>
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="30">
+      <c r="B6" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="32">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="26">
+      <c r="B8" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="28">
         <f>'Cash Flow &amp; DSCR'!C10</f>
         <v>-1.70774068</v>
       </c>
@@ -3524,76 +3701,76 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C1" s="9"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="18" t="str">
+      <c r="B3" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="20" t="str">
         <f>Assumptions!D5</f>
         <v>Heritage Academy</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="18" t="str">
+      <c r="B4" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="20" t="str">
         <f>Assumptions!D7</f>
         <v>Private School</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="18" t="str">
+      <c r="B5" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="20" t="str">
         <f>Assumptions!D6</f>
         <v>FL</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="18">
+      <c r="B6" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="20">
         <f>Assumptions!D8</f>
         <v>2023</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="19">
+      <c r="B8" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="21">
         <f>Assumptions!D16</f>
         <v>200</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" s="20">
+      <c r="B9" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="C9" s="22">
         <f>Drivers!G10</f>
         <v>2145936.2104</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="C10" s="31">
+      <c r="B10" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="33">
         <f>'5-Year P&amp;L'!G16</f>
         <v>22780.19693646</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C12" s="6"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="190">
   <si>
     <t>SCHOOLSTACK BUDGET</t>
   </si>
@@ -67,13 +67,13 @@
     <t>Cell Color Legend</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
-  </si>
-  <si>
-    <t>Green cells are key outputs and summary metrics.</t>
+    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
   </si>
   <si>
     <t/>
@@ -119,6 +119,21 @@
   </si>
   <si>
     <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Next Steps</t>
+  </si>
+  <si>
+    <t>2. Verify enrollment and revenue projections match your plan.</t>
+  </si>
+  <si>
+    <t>3. Check the Financial Health dashboard for risk signals.</t>
+  </si>
+  <si>
+    <t>4. Share this workbook with your lender or financial advisor.</t>
+  </si>
+  <si>
+    <t>5. Update inputs as your school's plan evolves.</t>
   </si>
   <si>
     <t>Disclaimer</t>
@@ -587,7 +602,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -631,6 +646,22 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1E293B"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1E3A5F"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -654,11 +685,6 @@
     </font>
     <font>
       <color rgb="FF374151"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -700,17 +726,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -784,7 +810,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -792,111 +818,263 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="15" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="15" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="21">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1344,6 +1522,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF0D9488"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:G33"/>
@@ -1357,7 +1536,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -1376,456 +1555,456 @@
       <c r="G3" s="6"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="F5" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" s="35" t="s">
-        <v>93</v>
+      <c r="B5" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="39" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="21">
+      <c r="B6" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="25">
         <v>100</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="25">
         <v>130</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="25">
         <v>160</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="25">
         <v>185</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="25">
         <v>200</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="22">
+      <c r="B7" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="26">
         <v>995000</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="26">
         <v>1306880</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="26">
         <v>1636644.8</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="26">
         <v>1934821.354</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="26">
         <v>2145936.2104</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="C8" s="22">
+      <c r="B8" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="26">
         <v>824466.6666666666</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="26">
         <v>951514</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="26">
         <v>1138133.52</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="26">
         <v>1280821.7409333333</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="26">
         <v>1431046.934954667</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" s="22">
+      <c r="B9" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="26">
         <v>271400</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="26">
         <v>334544</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="26">
         <v>423893.20399999997</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="26">
         <v>543450.5083634</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="26">
         <v>692109.0785088772</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" s="22">
+      <c r="B10" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" s="26">
         <v>59064.39316600799</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="26">
         <v>59064.39316600799</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="26">
         <v>59064.39316600799</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="26">
         <v>59064.39316600799</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="26">
         <v>59064.39316600799</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="C11" s="25">
+      <c r="B11" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="29">
         <v>-159931.0598326745</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="29">
         <v>-38242.39316600799</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="30">
         <v>15553.682833992127</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="30">
         <v>51484.71153725888</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="29">
         <v>-36284.19622955197</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12" s="25">
+      <c r="B12" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="29">
         <v>-84931.05983267451</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="29">
         <v>-123173.45299868251</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="29">
         <v>-107619.77016469039</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="29">
         <v>-56135.05862743151</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="29">
         <v>-92419.25485698348</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="C13" s="36">
+      <c r="B13" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="40">
         <v>-0.1607347335001754</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="40">
         <v>-0.029262360098867523</v>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="41">
         <v>0.009503395504016587</v>
       </c>
-      <c r="F13" s="37">
+      <c r="F13" s="41">
         <v>0.026609542752265323</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="40">
         <v>-0.016908329359328268</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="C14" s="22">
+      <c r="B14" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" s="26">
         <v>9950</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="26">
         <v>10052.923076923076</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="26">
         <v>10229.03</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="26">
         <v>10458.493805405406</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="26">
         <v>10729.681052000002</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="36">
+      <c r="B15" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" s="40">
         <v>0.8286097152428811</v>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="40">
         <v>0.7280806194906954</v>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="40">
         <v>0.6954065537005952</v>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="40">
         <v>0.6619844970624266</v>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="40">
         <v>0.6668636877551553</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="C16" s="38">
+      <c r="B16" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="42">
         <v>0.08182914572864322</v>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="42">
         <v>0.0767960333006856</v>
       </c>
-      <c r="E16" s="38">
+      <c r="E16" s="42">
         <v>0.07770040341068507</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="42">
         <v>0.0842636722878654</v>
       </c>
-      <c r="G16" s="38">
+      <c r="G16" s="42">
         <v>0.09675624212238845</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="36">
+      <c r="B17" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="40">
         <v>-0.10137353433835843</v>
       </c>
-      <c r="D17" s="37">
+      <c r="D17" s="41">
         <v>0.015932602840352597</v>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="41">
         <v>0.04559210159712117</v>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="41">
         <v>0.057136595311355426</v>
       </c>
-      <c r="G17" s="37">
+      <c r="G17" s="41">
         <v>0.010615505170216507</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="C18" s="39">
+      <c r="B18" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="C18" s="43">
         <v>-1.7077406752181137</v>
       </c>
-      <c r="D18" s="39">
+      <c r="D18" s="43">
         <v>0.35253049906865414</v>
       </c>
-      <c r="E18" s="40">
+      <c r="E18" s="44">
         <v>1.2633343373269994</v>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="44">
         <v>1.871670879484945</v>
       </c>
-      <c r="G18" s="39">
+      <c r="G18" s="43">
         <v>0.38568409350163607</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="C19" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
+      <c r="B19" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="C20" s="42" t="s">
-        <v>155</v>
-      </c>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
+      <c r="B20" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="C22" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="D22" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="G22" s="34"/>
+      <c r="B22" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="G22" s="38"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="43" t="s">
-        <v>160</v>
-      </c>
-      <c r="C23" s="44" t="s">
-        <v>161</v>
-      </c>
-      <c r="D23" s="45" t="s">
-        <v>162</v>
-      </c>
-      <c r="E23" s="45"/>
-      <c r="F23" s="46" t="s">
-        <v>163</v>
-      </c>
-      <c r="G23" s="46"/>
+      <c r="B23" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" s="48" t="s">
+        <v>166</v>
+      </c>
+      <c r="D23" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="E23" s="49"/>
+      <c r="F23" s="50" t="s">
+        <v>168</v>
+      </c>
+      <c r="G23" s="50"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="43" t="s">
-        <v>164</v>
-      </c>
-      <c r="C24" s="44" t="s">
-        <v>161</v>
-      </c>
-      <c r="D24" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="E24" s="45"/>
-      <c r="F24" s="46" t="s">
+      <c r="B24" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" s="48" t="s">
         <v>166</v>
       </c>
-      <c r="G24" s="46"/>
+      <c r="D24" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="E24" s="49"/>
+      <c r="F24" s="50" t="s">
+        <v>171</v>
+      </c>
+      <c r="G24" s="50"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="C25" s="44" t="s">
-        <v>161</v>
-      </c>
-      <c r="D25" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="E25" s="45"/>
-      <c r="F25" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="G25" s="46"/>
+      <c r="B25" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>166</v>
+      </c>
+      <c r="D25" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="E25" s="49"/>
+      <c r="F25" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="G25" s="50"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="43" t="s">
-        <v>170</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>171</v>
-      </c>
-      <c r="D26" s="45" t="s">
-        <v>172</v>
-      </c>
-      <c r="E26" s="45"/>
-      <c r="F26" s="46" t="s">
-        <v>173</v>
-      </c>
-      <c r="G26" s="46"/>
+      <c r="B26" s="47" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="D26" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="E26" s="49"/>
+      <c r="F26" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="G26" s="50"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="43" t="s">
-        <v>174</v>
-      </c>
-      <c r="C27" s="44" t="s">
-        <v>161</v>
-      </c>
-      <c r="D27" s="45" t="s">
-        <v>175</v>
-      </c>
-      <c r="E27" s="45"/>
-      <c r="F27" s="46" t="s">
+      <c r="B27" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="C27" s="48" t="s">
+        <v>166</v>
+      </c>
+      <c r="D27" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="E27" s="49"/>
+      <c r="F27" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="G27" s="50"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="47" t="s">
+        <v>182</v>
+      </c>
+      <c r="C28" s="51" t="s">
         <v>176</v>
       </c>
-      <c r="G27" s="46"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="C28" s="47" t="s">
-        <v>171</v>
-      </c>
-      <c r="D28" s="45" t="s">
-        <v>178</v>
-      </c>
-      <c r="E28" s="45"/>
-      <c r="F28" s="46" t="s">
-        <v>179</v>
-      </c>
-      <c r="G28" s="46"/>
+      <c r="D28" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="E28" s="49"/>
+      <c r="F28" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="G28" s="50"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="C29" s="44" t="s">
-        <v>161</v>
-      </c>
-      <c r="D29" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="E29" s="45"/>
-      <c r="F29" s="46" t="s">
-        <v>182</v>
-      </c>
-      <c r="G29" s="46"/>
+      <c r="B29" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" s="48" t="s">
+        <v>166</v>
+      </c>
+      <c r="D29" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="E29" s="49"/>
+      <c r="F29" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="G29" s="50"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="43" t="s">
+      <c r="B31" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
+      <c r="C31" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
+      <c r="B33" s="52" t="s">
+        <v>189</v>
+      </c>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -1852,6 +2031,83 @@
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="B33:G33"/>
   </mergeCells>
+  <conditionalFormatting sqref="C11:G11">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>C11&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>C11&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>C11&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12:G12">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C12&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C12&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C12&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C13&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C13&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>C15&lt;=0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>C15&lt;=0.65</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>C15&gt;0.65</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C16&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C16&lt;=0.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C16&gt;0.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:G17">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C17&gt;=0.10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C17&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C17&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:G18">
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>C18&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>C18&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="3">
+      <formula>C18&lt;1.0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -1863,9 +2119,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B29"/>
+  <dimension ref="B2:B37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1877,134 +2134,174 @@
         <v>13</v>
       </c>
     </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="8" t="s">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="8" t="s">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="8" t="s">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="8" t="s">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="8" t="s">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="8" t="s">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="8" t="s">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="8" t="s">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="8" t="s">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="8" t="s">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="8" t="s">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="8" t="s">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="7" t="s">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="8" t="s">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="8" t="s">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="s">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="8" t="s">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="11" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2032,395 +2329,395 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>37</v>
+      <c r="C2" s="15" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
+      <c r="B3" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="14" t="s">
+      <c r="C5" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>41</v>
+      <c r="C6" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>43</v>
+      <c r="C7" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="14">
+      <c r="C8" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="18">
         <v>2023</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
+      <c r="B10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="15">
+      <c r="C12" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="19">
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="15">
+      <c r="C13" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="19">
         <v>130</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="15">
+      <c r="C14" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="19">
         <v>160</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="15">
+      <c r="C15" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="19">
         <v>185</v>
       </c>
     </row>
     <row r="16" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="19">
         <v>200</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
+      <c r="B18" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="16">
+      <c r="C20" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="17">
+      <c r="C21" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="16">
+      <c r="C22" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="20">
         <v>8700</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="17">
+      <c r="C23" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="16">
+      <c r="C24" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="20">
         <v>500</v>
       </c>
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="17">
+      <c r="C25" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="17">
+      <c r="C26" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="21">
         <v>0.95</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="16">
+      <c r="C27" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="20">
         <v>75000</v>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D28" s="17">
+      <c r="C28" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
+      <c r="B30" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="15">
+      <c r="C32" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="19">
         <v>11</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D33" s="16">
+      <c r="C33" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="20">
         <v>40000</v>
       </c>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" s="17">
+      <c r="C34" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D35" s="15">
+      <c r="C35" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="19">
         <v>4</v>
       </c>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D36" s="15">
+      <c r="C36" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" s="19">
         <v>4</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D37" s="15">
+      <c r="C37" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="19">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" s="15">
+      <c r="C38" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="19">
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C39" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D39" s="15">
+      <c r="C39" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D39" s="19">
         <v>4</v>
       </c>
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C40" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" s="16">
+      <c r="C40" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="20">
         <v>66000</v>
       </c>
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C41" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D41" s="17">
+      <c r="C41" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C42" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" s="17">
+      <c r="C42" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" s="21">
         <v>0.24166666666666667</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
+      <c r="B44" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D46" s="16">
+      <c r="C46" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" s="20">
         <v>102000</v>
       </c>
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47" s="17">
+      <c r="C47" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D48" s="16">
+      <c r="C48" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="20">
         <v>34400</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D49" s="17">
+      <c r="C49" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D50" s="16">
+      <c r="C50" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" s="20">
         <v>600</v>
       </c>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D51" s="17">
+      <c r="C51" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D51" s="21">
         <v>0.339</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D52" s="16">
+      <c r="C52" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52" s="20">
         <v>75000</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D53" s="17">
+      <c r="C53" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D53" s="21">
         <v>0.1948</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
+      <c r="B55" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C57" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D57" s="16">
+      <c r="C57" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D57" s="20">
         <v>75000</v>
       </c>
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C58" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D58" s="16">
+      <c r="C58" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D58" s="20">
         <v>25000</v>
       </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C59" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D59" s="16">
+      <c r="C59" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D59" s="20">
         <v>250000</v>
       </c>
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C60" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D60" s="17">
+      <c r="C60" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D60" s="21">
         <v>0.065</v>
       </c>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C61" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D61" s="15">
+      <c r="C61" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D61" s="19">
         <v>10</v>
       </c>
     </row>
@@ -2457,454 +2754,454 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="18"/>
-      <c r="C3" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>93</v>
+      <c r="B3" s="22"/>
+      <c r="C3" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="21">
+      <c r="B4" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="25">
         <f>Assumptions!D12</f>
         <v>100</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="25">
         <f>Assumptions!D13</f>
         <v>130</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="25">
         <f>Assumptions!D14</f>
         <v>160</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="25">
         <f>Assumptions!D15</f>
         <v>185</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="25">
         <f>Assumptions!D16</f>
         <v>200</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" s="22" t="str">
+      <c r="B5" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="26" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
         <v>0</v>
       </c>
-      <c r="D5" s="22" t="str">
+      <c r="D5" s="26" t="str">
         <f>Assumptions!D13*Assumptions!D20*(1+Assumptions!D21)^1</f>
         <v>0</v>
       </c>
-      <c r="E5" s="22" t="str">
+      <c r="E5" s="26" t="str">
         <f>Assumptions!D14*Assumptions!D20*(1+Assumptions!D21)^2</f>
         <v>0</v>
       </c>
-      <c r="F5" s="22" t="str">
+      <c r="F5" s="26" t="str">
         <f>Assumptions!D15*Assumptions!D20*(1+Assumptions!D21)^3</f>
         <v>0</v>
       </c>
-      <c r="G5" s="22" t="str">
+      <c r="G5" s="26" t="str">
         <f>Assumptions!D16*Assumptions!D20*(1+Assumptions!D21)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="22" t="str">
+      <c r="B6" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="26" t="str">
         <f>C5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="D6" s="22" t="str">
+      <c r="D6" s="26" t="str">
         <f>D5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="E6" s="22" t="str">
+      <c r="E6" s="26" t="str">
         <f>E5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="F6" s="22" t="str">
+      <c r="F6" s="26" t="str">
         <f>F5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="G6" s="22" t="str">
+      <c r="G6" s="26" t="str">
         <f>G5*Assumptions!D26</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="22">
+      <c r="B7" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="26">
         <f>Assumptions!D12*Assumptions!D22</f>
         <v>870000</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="26">
         <f>Assumptions!D13*Assumptions!D22*(1+Assumptions!D23)^1</f>
         <v>1164930</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="26">
         <f>Assumptions!D14*Assumptions!D22*(1+Assumptions!D23)^2</f>
         <v>1476772.8</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="26">
         <f>Assumptions!D15*Assumptions!D22*(1+Assumptions!D23)^3</f>
         <v>1758744.1065</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="26">
         <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
         <v>1958385.3294</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="22">
+      <c r="B8" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="26">
         <f>Assumptions!D12*Assumptions!D24</f>
         <v>50000</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="26">
         <f>Assumptions!D13*Assumptions!D24*(1+Assumptions!D25)^1</f>
         <v>66950</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="26">
         <f>Assumptions!D14*Assumptions!D24*(1+Assumptions!D25)^2</f>
         <v>84872</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="26">
         <f>Assumptions!D15*Assumptions!D24*(1+Assumptions!D25)^3</f>
         <v>101077.2475</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="26">
         <f>Assumptions!D16*Assumptions!D24*(1+Assumptions!D25)^4</f>
         <v>112550.881</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="22">
+      <c r="B9" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="26">
         <f>Assumptions!D27</f>
         <v>75000</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="26">
         <f>Assumptions!D27*(1+Assumptions!D28)^1</f>
         <v>75000</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="26">
         <f>Assumptions!D27*(1+Assumptions!D28)^2</f>
         <v>75000</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="26">
         <f>Assumptions!D27*(1+Assumptions!D28)^3</f>
         <v>75000</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="26">
         <f>Assumptions!D27*(1+Assumptions!D28)^4</f>
         <v>75000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="24">
+      <c r="B10" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="28">
         <f>C6+C7+C8+C9</f>
         <v>995000</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="28">
         <f>D6+D7+D8+D9</f>
         <v>1306880</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="28">
         <f>E6+E7+E8+E9</f>
         <v>1636644.8</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="28">
         <f>F6+F7+F8+F9</f>
         <v>1934821.354</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="28">
         <f>G6+G7+G8+G9</f>
         <v>2145936.2104</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="21">
+      <c r="B12" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="25">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
         <v>10</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="25">
         <f>CEILING(Assumptions!D13/Assumptions!D32,1)</f>
         <v>12</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="25">
         <f>CEILING(Assumptions!D14/Assumptions!D32,1)</f>
         <v>15</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="25">
         <f>CEILING(Assumptions!D15/Assumptions!D32,1)</f>
         <v>17</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="25">
         <f>CEILING(Assumptions!D16/Assumptions!D32,1)</f>
         <v>19</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" s="22">
+      <c r="B13" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="26">
         <f>C12*Assumptions!D33</f>
         <v>400000</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="26">
         <f>D12*Assumptions!D33*(1+Assumptions!D34)^1</f>
         <v>494400</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="26">
         <f>E12*Assumptions!D33*(1+Assumptions!D34)^2</f>
         <v>636540</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="26">
         <f>F12*Assumptions!D33*(1+Assumptions!D34)^3</f>
         <v>743054.36</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="26">
         <f>G12*Assumptions!D33*(1+Assumptions!D34)^4</f>
         <v>855386.6956</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="22">
+      <c r="B14" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="26">
         <f>Assumptions!D35*Assumptions!D40</f>
         <v>264000</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="26">
         <f>Assumptions!D36*Assumptions!D40*(1+Assumptions!D41)^1</f>
         <v>271920</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="26">
         <f>Assumptions!D37*Assumptions!D40*(1+Assumptions!D41)^2</f>
         <v>280077.6</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="26">
         <f>Assumptions!D38*Assumptions!D40*(1+Assumptions!D41)^3</f>
         <v>288479.928</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="26">
         <f>Assumptions!D39*Assumptions!D40*(1+Assumptions!D41)^4</f>
         <v>297134.32584</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="22">
+      <c r="B15" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="26">
         <f>(C13+C14)*Assumptions!D42</f>
         <v>160466.66666667</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="26">
         <f>(D13+D14)*Assumptions!D42</f>
         <v>185194</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="26">
         <f>(E13+E14)*Assumptions!D42</f>
         <v>221515.92</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="26">
         <f>(F13+F14)*Assumptions!D42</f>
         <v>249287.45293333</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="26">
         <f>(G13+G14)*Assumptions!D42</f>
         <v>278525.91351467</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="24">
+      <c r="B16" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="28">
         <f>C13+C14+C15</f>
         <v>824466.66666667</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="28">
         <f>D13+D14+D15</f>
         <v>951514</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="28">
         <f>E13+E14+E15</f>
         <v>1138133.52</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="28">
         <f>F13+F14+F15</f>
         <v>1280821.74093333</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="28">
         <f>G13+G14+G15</f>
         <v>1431046.93495467</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" s="22">
+      <c r="B18" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="26">
         <f>Assumptions!D46</f>
         <v>102000</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="26">
         <f>Assumptions!D46*(1+Assumptions!D47)^1</f>
         <v>105060</v>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="26">
         <f>Assumptions!D46*(1+Assumptions!D47)^2</f>
         <v>108211.8</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="26">
         <f>Assumptions!D46*(1+Assumptions!D47)^3</f>
         <v>111458.154</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="26">
         <f>Assumptions!D46*(1+Assumptions!D47)^4</f>
         <v>114801.89862</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="C19" s="22">
+      <c r="B19" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="26">
         <f>Assumptions!D48</f>
         <v>34400</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="26">
         <f>Assumptions!D48*(1+Assumptions!D49)^1</f>
         <v>35432</v>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="26">
         <f>Assumptions!D48*(1+Assumptions!D49)^2</f>
         <v>36494.96</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="26">
         <f>Assumptions!D48*(1+Assumptions!D49)^3</f>
         <v>37589.8088</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="26">
         <f>Assumptions!D48*(1+Assumptions!D49)^4</f>
         <v>38717.503064</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="22">
+      <c r="B20" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="26">
         <f>Assumptions!D12*Assumptions!D50</f>
         <v>60000</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="26">
         <f>Assumptions!D13*Assumptions!D50*(1+Assumptions!D51)^1</f>
         <v>104442</v>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="26">
         <f>Assumptions!D14*Assumptions!D50*(1+Assumptions!D51)^2</f>
         <v>172120.416</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="26">
         <f>Assumptions!D15*Assumptions!D50*(1+Assumptions!D51)^3</f>
         <v>266480.055309</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="26">
         <f>Assumptions!D16*Assumptions!D50*(1+Assumptions!D51)^4</f>
         <v>385747.88546892</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C21" s="22">
+      <c r="B21" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="26">
         <f>Assumptions!D52</f>
         <v>75000</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="26">
         <f>Assumptions!D52*(1+Assumptions!D53)^1</f>
         <v>89610</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="26">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
         <v>107066.028</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="26">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
         <v>127922.4902544</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="26">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
         <v>152841.79135596</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="C22" s="24">
+      <c r="B22" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="28">
         <f>C18+C19+C20+C21</f>
         <v>271400</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="28">
         <f>D18+D19+D20+D21</f>
         <v>334544</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="28">
         <f>E18+E19+E20+E21</f>
         <v>423893.204</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="28">
         <f>F18+F19+F20+F21</f>
         <v>543450.5083634</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="28">
         <f>G18+G19+G20+G21</f>
         <v>692109.07850888</v>
       </c>
@@ -2936,304 +3233,304 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="18"/>
-      <c r="C3" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>93</v>
+      <c r="B3" s="22"/>
+      <c r="C3" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="21">
+      <c r="B5" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="25">
         <f>Drivers!C4</f>
         <v>100</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="25">
         <f>Drivers!D4</f>
         <v>130</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="25">
         <f>Drivers!E4</f>
         <v>160</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="25">
         <f>Drivers!F4</f>
         <v>185</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="25">
         <f>Drivers!G4</f>
         <v>200</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="22" t="str">
+      <c r="B6" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="26" t="str">
         <f>Drivers!C6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="22" t="str">
+      <c r="D6" s="26" t="str">
         <f>Drivers!D6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="22" t="str">
+      <c r="E6" s="26" t="str">
         <f>Drivers!E6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="22" t="str">
+      <c r="F6" s="26" t="str">
         <f>Drivers!F6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="22" t="str">
+      <c r="G6" s="26" t="str">
         <f>Drivers!G6</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="22">
+      <c r="B7" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="26">
         <f>Drivers!C7</f>
         <v>870000</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="26">
         <f>Drivers!D7</f>
         <v>1164930</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="26">
         <f>Drivers!E7</f>
         <v>1476772.8</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="26">
         <f>Drivers!F7</f>
         <v>1758744.1065</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="26">
         <f>Drivers!G7</f>
         <v>1958385.3294</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="C8" s="22">
+      <c r="B8" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="26">
         <f>Drivers!C8</f>
         <v>50000</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="26">
         <f>Drivers!D8</f>
         <v>66950</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="26">
         <f>Drivers!E8</f>
         <v>84872</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="26">
         <f>Drivers!F8</f>
         <v>101077.2475</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="26">
         <f>Drivers!G8</f>
         <v>112550.881</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="22">
+      <c r="B9" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="26">
         <f>Drivers!C9</f>
         <v>75000</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="26">
         <f>Drivers!D9</f>
         <v>75000</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="26">
         <f>Drivers!E9</f>
         <v>75000</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="26">
         <f>Drivers!F9</f>
         <v>75000</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="26">
         <f>Drivers!G9</f>
         <v>75000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="24">
+      <c r="B10" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="28">
         <f>Drivers!C10</f>
         <v>995000</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="28">
         <f>Drivers!D10</f>
         <v>1306880</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="28">
         <f>Drivers!E10</f>
         <v>1636644.8</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="28">
         <f>Drivers!F10</f>
         <v>1934821.354</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="28">
         <f>Drivers!G10</f>
         <v>2145936.2104</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="22">
+      <c r="B12" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="26">
         <f>Drivers!C16</f>
         <v>824466.66666667</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="26">
         <f>Drivers!D16</f>
         <v>951514</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="26">
         <f>Drivers!E16</f>
         <v>1138133.52</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="26">
         <f>Drivers!F16</f>
         <v>1280821.74093333</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="26">
         <f>Drivers!G16</f>
         <v>1431046.93495467</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13" s="22">
+      <c r="B13" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="26">
         <f>Drivers!C22</f>
         <v>271400</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="26">
         <f>Drivers!D22</f>
         <v>334544</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="26">
         <f>Drivers!E22</f>
         <v>423893.204</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="26">
         <f>Drivers!F22</f>
         <v>543450.5083634</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="26">
         <f>Drivers!G22</f>
         <v>692109.07850888</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" s="24">
+      <c r="B15" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="28">
         <f>C12+C13</f>
         <v>1095866.66666667</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="28">
         <f>D12+D13</f>
         <v>1286058</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="28">
         <f>E12+E13</f>
         <v>1562026.724</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="28">
         <f>F12+F13</f>
         <v>1824272.24929673</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="28">
         <f>G12+G13</f>
         <v>2123156.01346354</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="25">
+      <c r="B16" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="29">
         <f>C10-C15</f>
         <v>-100866.66666667</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="30">
         <f>D10-D15</f>
         <v>20822</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="30">
         <f>E10-E15</f>
         <v>74618.076</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="30">
         <f>F10-F15</f>
         <v>110549.10470327</v>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="30">
         <f>G10-G15</f>
         <v>22780.19693646</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="27">
+      <c r="B17" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="31">
         <f>IF(C10&gt;0,C16/C10,0)</f>
         <v>-0.10137353</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="31">
         <f>IF(D10&gt;0,D16/D10,0)</f>
         <v>0.0159326</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="31">
         <f>IF(E10&gt;0,E16/E10,0)</f>
         <v>0.0455921</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="31">
         <f>IF(F10&gt;0,F16/F10,0)</f>
         <v>0.0571366</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="31">
         <f>IF(G10&gt;0,G16/G10,0)</f>
         <v>0.01061551</v>
       </c>
@@ -3265,204 +3562,204 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="18"/>
-      <c r="C3" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>93</v>
+      <c r="B3" s="22"/>
+      <c r="C3" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" s="22">
+      <c r="B4" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="26">
         <f>'5-Year P&amp;L'!C16</f>
         <v>-100866.66666667</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="26">
         <f>'5-Year P&amp;L'!D16</f>
         <v>20822</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="26">
         <f>'5-Year P&amp;L'!E16</f>
         <v>74618.076</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="26">
         <f>'5-Year P&amp;L'!F16</f>
         <v>110549.10470327</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="26">
         <f>'5-Year P&amp;L'!G16</f>
         <v>22780.19693646</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" s="22">
+      <c r="B6" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="26">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="26">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="26">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="26">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="26">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="22">
+      <c r="B7" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="26">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="26">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="26">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="26">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="26">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" s="24">
+      <c r="B8" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="28">
         <f>C6+C7</f>
         <v>59064.39316601</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="28">
         <f>D6+D7</f>
         <v>59064.39316601</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="28">
         <f>E6+E7</f>
         <v>59064.39316601</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="28">
         <f>F6+F7</f>
         <v>59064.39316601</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="28">
         <f>G6+G7</f>
         <v>59064.39316601</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="28">
+      <c r="B10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="32">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
         <v>-1.70774068</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="32">
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
         <v>0.3525305</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="33">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
         <v>1.26333434</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="33">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
         <v>1.87167088</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="32">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
         <v>0.38568409</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="22">
+      <c r="B12" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="26">
         <f>C4-C8</f>
         <v>-159931.05983267</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="26">
         <f>D4-D8</f>
         <v>-38242.39316601</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="26">
         <f>E4-E8</f>
         <v>15553.68283399</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="26">
         <f>F4-F8</f>
         <v>51484.71153726</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="26">
         <f>G4-G8</f>
         <v>-36284.19622955</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" s="30">
+      <c r="B14" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" s="34">
         <f>Assumptions!D57+C12</f>
         <v>-84931.05983267</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="34">
         <f>C14+D12</f>
         <v>-123173.45299868</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="34">
         <f>D14+E12</f>
         <v>-107619.77016469</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="34">
         <f>E14+F12</f>
         <v>-56135.05862743</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="34">
         <f>F14+G12</f>
         <v>-92419.25485698</v>
       </c>
@@ -3494,104 +3791,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="18"/>
-      <c r="C3" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>93</v>
+      <c r="B3" s="22"/>
+      <c r="C3" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="C4" s="21">
+      <c r="B4" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="25">
         <f>Drivers!C12</f>
         <v>10</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="25">
         <f>Drivers!D12</f>
         <v>12</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="25">
         <f>Drivers!E12</f>
         <v>15</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="25">
         <f>Drivers!F12</f>
         <v>17</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="25">
         <f>Drivers!G12</f>
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="C5" s="21">
+      <c r="B5" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="25">
         <f>Assumptions!D35</f>
         <v>4</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="25">
         <f>Assumptions!D36</f>
         <v>4</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="25">
         <f>Assumptions!D37</f>
         <v>4</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="25">
         <f>Assumptions!D38</f>
         <v>4</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="25">
         <f>Assumptions!D39</f>
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="C6" s="31">
+      <c r="B6" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="35">
         <f>C4+C5</f>
         <v>14</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="35">
         <f>D4+D5</f>
         <v>16</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="35">
         <f>E4+E5</f>
         <v>19</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="35">
         <f>F4+F5</f>
         <v>21</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="35">
         <f>G4+G5</f>
         <v>23</v>
       </c>
@@ -3623,52 +3920,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="22">
+      <c r="B3" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="26">
         <f>Assumptions!D59</f>
         <v>250000</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C4" s="27">
+      <c r="B4" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="31">
         <f>Assumptions!D60</f>
         <v>0.065</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="21">
+      <c r="B5" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="25">
         <f>Assumptions!D61</f>
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="C6" s="32">
+      <c r="B6" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="36">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="28">
+      <c r="B8" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="32">
         <f>'Cash Flow &amp; DSCR'!C10</f>
         <v>-1.70774068</v>
       </c>
@@ -3700,77 +3997,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="20" t="str">
+      <c r="B3" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="24" t="str">
         <f>Assumptions!D5</f>
         <v>Heritage Academy</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="20" t="str">
+      <c r="B4" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="24" t="str">
         <f>Assumptions!D7</f>
         <v>Private School</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="20" t="str">
+      <c r="B5" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="24" t="str">
         <f>Assumptions!D6</f>
         <v>FL</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="20">
+      <c r="B6" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="24">
         <f>Assumptions!D8</f>
         <v>2023</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="21">
+      <c r="B8" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="25">
         <f>Assumptions!D16</f>
         <v>200</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" s="22">
+      <c r="B9" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" s="26">
         <f>Drivers!G10</f>
         <v>2145936.2104</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="C10" s="33">
+      <c r="B10" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" s="37">
         <f>'5-Year P&amp;L'!G16</f>
         <v>22780.19693646</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C12" s="6"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -4,8 +4,8 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Cover" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+    <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Cover" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Assumptions" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Drivers" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="5-Year P&amp;L" state="visible" r:id="rId8"/>
@@ -22,15 +22,102 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="190">
   <si>
+    <t>How to Use This Workbook</t>
+  </si>
+  <si>
+    <t>Heritage Academy</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026</t>
+  </si>
+  <si>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>Assumptions &amp; Drivers: Model inputs and calculations</t>
+  </si>
+  <si>
+    <t>5-Year P&amp;L &amp; Cash Flow: Financial projections</t>
+  </si>
+  <si>
+    <t>Staffing &amp; Loan Snapshot: Personnel and debt detail</t>
+  </si>
+  <si>
+    <t>Summary &amp; Financial Health: Key metrics dashboard</t>
+  </si>
+  <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs.</t>
+  </si>
+  <si>
+    <t>Tips</t>
+  </si>
+  <si>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Next Steps</t>
+  </si>
+  <si>
+    <t>2. Verify enrollment and revenue projections match your plan.</t>
+  </si>
+  <si>
+    <t>3. Check the Financial Health dashboard for risk signals.</t>
+  </si>
+  <si>
+    <t>4. Share this workbook with your lender or financial advisor.</t>
+  </si>
+  <si>
+    <t>5. Update inputs as your school's plan evolves.</t>
+  </si>
+  <si>
+    <t>Disclaimer</t>
+  </si>
+  <si>
+    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
+  </si>
+  <si>
+    <t>user-provided assumptions and should be independently verified.</t>
+  </si>
+  <si>
     <t>SCHOOLSTACK BUDGET</t>
   </si>
   <si>
     <t>Lender-Ready Pro Forma</t>
   </si>
   <si>
-    <t>Heritage Academy</t>
-  </si>
-  <si>
     <t>TABLE OF CONTENTS</t>
   </si>
   <si>
@@ -55,94 +142,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
-  </si>
-  <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
-  </si>
-  <si>
-    <t>How to Use This Workbook</t>
-  </si>
-  <si>
-    <t>Cell Color Legend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Navigation</t>
-  </si>
-  <si>
-    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
-  </si>
-  <si>
-    <t>Structure</t>
-  </si>
-  <si>
-    <t>Assumptions &amp; Drivers: Model inputs and calculations</t>
-  </si>
-  <si>
-    <t>5-Year P&amp;L &amp; Cash Flow: Financial projections</t>
-  </si>
-  <si>
-    <t>Staffing &amp; Loan Snapshot: Personnel and debt detail</t>
-  </si>
-  <si>
-    <t>Summary &amp; Financial Health: Key metrics dashboard</t>
-  </si>
-  <si>
-    <t>Debt Service Convention</t>
-  </si>
-  <si>
-    <t>operating expense on the Operating Statement. This is a standard</t>
-  </si>
-  <si>
-    <t>simplification used in school financial underwriting that ensures internal</t>
-  </si>
-  <si>
-    <t>consistency across all tabs.</t>
-  </si>
-  <si>
-    <t>Tips</t>
-  </si>
-  <si>
-    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
-  </si>
-  <si>
-    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
-  </si>
-  <si>
-    <t>Next Steps</t>
-  </si>
-  <si>
-    <t>2. Verify enrollment and revenue projections match your plan.</t>
-  </si>
-  <si>
-    <t>3. Check the Financial Health dashboard for risk signals.</t>
-  </si>
-  <si>
-    <t>4. Share this workbook with your lender or financial advisor.</t>
-  </si>
-  <si>
-    <t>5. Update inputs as your school's plan evolves.</t>
-  </si>
-  <si>
-    <t>Disclaimer</t>
-  </si>
-  <si>
-    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
-  </si>
-  <si>
-    <t>user-provided assumptions and should be independently verified.</t>
   </si>
   <si>
     <t>SchoolStack Budget - Lender Pro Forma Assumptions</t>
@@ -613,36 +613,7 @@
     <font>
       <b/>
       <color rgb="FF1E293B"/>
-      <sz val="22"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF328555"/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF1E293B"/>
       <sz val="16"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF1E293B"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0563C1"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF6B7280"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -657,11 +628,40 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="22"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF328555"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0563C1"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -815,15 +815,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -831,27 +831,27 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -864,7 +864,7 @@
     <xf numFmtId="165" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="15" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -910,10 +910,10 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1410,107 +1410,192 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF1E293B"/>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:C19"/>
+  <dimension ref="B2:B37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="3"/>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="4"/>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>4</v>
+      <c r="B9" s="7" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
-        <v>5</v>
+      <c r="B10" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
-        <v>6</v>
+      <c r="B11" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
-        <v>9</v>
+      <c r="B14" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6"/>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="6"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="6" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="B9" r:id="rId1" location="#'Assumptions'!A1"/>
-    <hyperlink ref="B10" r:id="rId2" location="#'Drivers'!A1"/>
-    <hyperlink ref="B11" r:id="rId3" location="#'5-Year P&amp;L'!A1"/>
-    <hyperlink ref="B12" r:id="rId4" location="#'Cash Flow &amp; DSCR'!A1"/>
-    <hyperlink ref="B13" r:id="rId5" location="#'Staffing'!A1"/>
-    <hyperlink ref="B14" r:id="rId6" location="#'Loan Snapshot'!A1"/>
-    <hyperlink ref="B15" r:id="rId7" location="#'Summary'!A1"/>
-  </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -1535,24 +1620,24 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="38" t="s">
@@ -1988,7 +2073,7 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="47" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C31" s="27" t="s">
         <v>188</v>
@@ -2119,192 +2204,107 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF328555"/>
+    <tabColor rgb="FF1E293B"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B37"/>
+  <dimension ref="B3:C19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="80" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="11" t="s">
-        <v>16</v>
-      </c>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="8"/>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="9"/>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="10"/>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="12" t="s">
-        <v>17</v>
+      <c r="B9" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
-        <v>19</v>
+      <c r="B11" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
-        <v>21</v>
+      <c r="B14" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="11" t="s">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="12"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="s">
         <v>40</v>
       </c>
+      <c r="C19" s="12"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B9" r:id="rId1" location="#'Assumptions'!A1"/>
+    <hyperlink ref="B10" r:id="rId2" location="#'Drivers'!A1"/>
+    <hyperlink ref="B11" r:id="rId3" location="#'5-Year P&amp;L'!A1"/>
+    <hyperlink ref="B12" r:id="rId4" location="#'Cash Flow &amp; DSCR'!A1"/>
+    <hyperlink ref="B13" r:id="rId5" location="#'Staffing'!A1"/>
+    <hyperlink ref="B14" r:id="rId6" location="#'Loan Snapshot'!A1"/>
+    <hyperlink ref="B15" r:id="rId7" location="#'Summary'!A1"/>
+  </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -2337,7 +2337,7 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>42</v>
@@ -2355,7 +2355,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
@@ -4066,10 +4066,10 @@
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="191">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -28,118 +28,121 @@
     <t>Heritage Academy</t>
   </si>
   <si>
+    <t>Generated March 26, 2026 · nonprofit_501c3</t>
+  </si>
+  <si>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>Assumptions &amp; Drivers: Model inputs and calculations</t>
+  </si>
+  <si>
+    <t>5-Year P&amp;L &amp; Cash Flow: Financial projections</t>
+  </si>
+  <si>
+    <t>Staffing &amp; Loan Snapshot: Personnel and debt detail</t>
+  </si>
+  <si>
+    <t>Summary &amp; Financial Health: Key metrics dashboard</t>
+  </si>
+  <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs.</t>
+  </si>
+  <si>
+    <t>Tips</t>
+  </si>
+  <si>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Next Steps</t>
+  </si>
+  <si>
+    <t>2. Verify enrollment and revenue projections match your plan.</t>
+  </si>
+  <si>
+    <t>3. Check the Financial Health dashboard for risk signals.</t>
+  </si>
+  <si>
+    <t>4. Share this workbook with your lender or financial advisor.</t>
+  </si>
+  <si>
+    <t>5. Update inputs as your school's plan evolves.</t>
+  </si>
+  <si>
+    <t>Disclaimer</t>
+  </si>
+  <si>
+    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
+  </si>
+  <si>
+    <t>user-provided assumptions and should be independently verified.</t>
+  </si>
+  <si>
+    <t>SCHOOLSTACK BUDGET</t>
+  </si>
+  <si>
+    <t>Lender-Ready Pro Forma</t>
+  </si>
+  <si>
+    <t>TABLE OF CONTENTS</t>
+  </si>
+  <si>
+    <t>Assumptions</t>
+  </si>
+  <si>
+    <t>Drivers</t>
+  </si>
+  <si>
+    <t>5-Year P&amp;L</t>
+  </si>
+  <si>
+    <t>Cash Flow &amp; DSCR</t>
+  </si>
+  <si>
+    <t>Staffing</t>
+  </si>
+  <si>
+    <t>Loan Snapshot</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
     <t>Generated March 26, 2026</t>
-  </si>
-  <si>
-    <t>Cell Color Legend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Navigation</t>
-  </si>
-  <si>
-    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
-  </si>
-  <si>
-    <t>Structure</t>
-  </si>
-  <si>
-    <t>Assumptions &amp; Drivers: Model inputs and calculations</t>
-  </si>
-  <si>
-    <t>5-Year P&amp;L &amp; Cash Flow: Financial projections</t>
-  </si>
-  <si>
-    <t>Staffing &amp; Loan Snapshot: Personnel and debt detail</t>
-  </si>
-  <si>
-    <t>Summary &amp; Financial Health: Key metrics dashboard</t>
-  </si>
-  <si>
-    <t>Debt Service Convention</t>
-  </si>
-  <si>
-    <t>operating expense on the Operating Statement. This is a standard</t>
-  </si>
-  <si>
-    <t>simplification used in school financial underwriting that ensures internal</t>
-  </si>
-  <si>
-    <t>consistency across all tabs.</t>
-  </si>
-  <si>
-    <t>Tips</t>
-  </si>
-  <si>
-    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
-  </si>
-  <si>
-    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
-  </si>
-  <si>
-    <t>Next Steps</t>
-  </si>
-  <si>
-    <t>2. Verify enrollment and revenue projections match your plan.</t>
-  </si>
-  <si>
-    <t>3. Check the Financial Health dashboard for risk signals.</t>
-  </si>
-  <si>
-    <t>4. Share this workbook with your lender or financial advisor.</t>
-  </si>
-  <si>
-    <t>5. Update inputs as your school's plan evolves.</t>
-  </si>
-  <si>
-    <t>Disclaimer</t>
-  </si>
-  <si>
-    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
-  </si>
-  <si>
-    <t>user-provided assumptions and should be independently verified.</t>
-  </si>
-  <si>
-    <t>SCHOOLSTACK BUDGET</t>
-  </si>
-  <si>
-    <t>Lender-Ready Pro Forma</t>
-  </si>
-  <si>
-    <t>TABLE OF CONTENTS</t>
-  </si>
-  <si>
-    <t>Assumptions</t>
-  </si>
-  <si>
-    <t>Drivers</t>
-  </si>
-  <si>
-    <t>5-Year P&amp;L</t>
-  </si>
-  <si>
-    <t>Cash Flow &amp; DSCR</t>
-  </si>
-  <si>
-    <t>Staffing</t>
-  </si>
-  <si>
-    <t>Loan Snapshot</t>
-  </si>
-  <si>
-    <t>Summary</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -1621,7 +1624,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1631,7 +1634,7 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="12" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -1641,27 +1644,27 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="38" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" s="25">
         <v>100</v>
@@ -1681,7 +1684,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C7" s="26">
         <v>995000</v>
@@ -1701,7 +1704,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C8" s="26">
         <v>824466.6666666666</v>
@@ -1721,7 +1724,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C9" s="26">
         <v>271400</v>
@@ -1741,7 +1744,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C10" s="26">
         <v>59064.39316600799</v>
@@ -1761,7 +1764,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="29">
         <v>-159931.0598326745</v>
@@ -1781,7 +1784,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" s="29">
         <v>-84931.05983267451</v>
@@ -1801,7 +1804,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" s="40">
         <v>-0.1607347335001754</v>
@@ -1821,7 +1824,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C14" s="26">
         <v>9950</v>
@@ -1841,7 +1844,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C15" s="40">
         <v>0.8286097152428811</v>
@@ -1861,7 +1864,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C16" s="42">
         <v>0.08182914572864322</v>
@@ -1881,7 +1884,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C17" s="40">
         <v>-0.10137353433835843</v>
@@ -1901,7 +1904,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C18" s="43">
         <v>-1.7077406752181137</v>
@@ -1921,10 +1924,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D19" s="45"/>
       <c r="E19" s="45"/>
@@ -1933,10 +1936,10 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C20" s="46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D20" s="46"/>
       <c r="E20" s="46"/>
@@ -1945,129 +1948,129 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="38" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="38" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G22" s="38"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D23" s="49" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E23" s="49"/>
       <c r="F23" s="50" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G23" s="50"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="47" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D24" s="49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E24" s="49"/>
       <c r="F24" s="50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G24" s="50"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="47" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D25" s="49" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E25" s="49"/>
       <c r="F25" s="50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G25" s="50"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="47" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E26" s="49"/>
       <c r="F26" s="50" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G26" s="50"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="47" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E27" s="49"/>
       <c r="F27" s="50" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G27" s="50"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="47" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D28" s="49" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E28" s="49"/>
       <c r="F28" s="50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G28" s="50"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="47" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D29" s="49" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E29" s="49"/>
       <c r="F29" s="50" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G29" s="50"/>
     </row>
@@ -2076,14 +2079,14 @@
         <v>39</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D31" s="27"/>
       <c r="E31" s="27"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" s="52" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C33" s="52"/>
       <c r="D33" s="52"/>
@@ -2277,13 +2280,13 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="12" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C18" s="12"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="12"/>
     </row>
@@ -2330,7 +2333,7 @@
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -2340,19 +2343,19 @@
         <v>7</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" s="18" t="s">
         <v>1</v>
@@ -2360,23 +2363,23 @@
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="18">
         <v>2023</v>
@@ -2384,14 +2387,14 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" s="19">
         <v>100</v>
@@ -2399,7 +2402,7 @@
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" s="19">
         <v>130</v>
@@ -2407,7 +2410,7 @@
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" s="19">
         <v>160</v>
@@ -2415,7 +2418,7 @@
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" s="19">
         <v>185</v>
@@ -2423,7 +2426,7 @@
     </row>
     <row r="16" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C16" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="19">
         <v>200</v>
@@ -2431,14 +2434,14 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C20" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="20">
         <v>0</v>
@@ -2446,7 +2449,7 @@
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C21" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D21" s="21">
         <v>0.03</v>
@@ -2454,7 +2457,7 @@
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C22" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D22" s="20">
         <v>8700</v>
@@ -2462,7 +2465,7 @@
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C23" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D23" s="21">
         <v>0.03</v>
@@ -2470,7 +2473,7 @@
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C24" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D24" s="20">
         <v>500</v>
@@ -2478,7 +2481,7 @@
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C25" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D25" s="21">
         <v>0.03</v>
@@ -2486,7 +2489,7 @@
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C26" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D26" s="21">
         <v>0.95</v>
@@ -2494,7 +2497,7 @@
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C27" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D27" s="20">
         <v>75000</v>
@@ -2502,7 +2505,7 @@
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C28" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D28" s="21">
         <v>0</v>
@@ -2510,14 +2513,14 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C32" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D32" s="19">
         <v>11</v>
@@ -2525,7 +2528,7 @@
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C33" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D33" s="20">
         <v>40000</v>
@@ -2533,7 +2536,7 @@
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C34" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D34" s="21">
         <v>0.03</v>
@@ -2541,7 +2544,7 @@
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C35" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D35" s="19">
         <v>4</v>
@@ -2549,7 +2552,7 @@
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C36" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D36" s="19">
         <v>4</v>
@@ -2557,7 +2560,7 @@
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C37" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D37" s="19">
         <v>4</v>
@@ -2565,7 +2568,7 @@
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C38" s="17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D38" s="19">
         <v>4</v>
@@ -2573,7 +2576,7 @@
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C39" s="17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D39" s="19">
         <v>4</v>
@@ -2581,7 +2584,7 @@
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C40" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D40" s="20">
         <v>66000</v>
@@ -2589,7 +2592,7 @@
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C41" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D41" s="21">
         <v>0.03</v>
@@ -2597,7 +2600,7 @@
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C42" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D42" s="21">
         <v>0.24166666666666667</v>
@@ -2605,14 +2608,14 @@
     </row>
     <row r="44" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C46" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D46" s="20">
         <v>102000</v>
@@ -2620,7 +2623,7 @@
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C47" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D47" s="21">
         <v>0.03</v>
@@ -2628,7 +2631,7 @@
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C48" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D48" s="20">
         <v>34400</v>
@@ -2636,7 +2639,7 @@
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C49" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D49" s="21">
         <v>0.03</v>
@@ -2644,7 +2647,7 @@
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C50" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D50" s="20">
         <v>600</v>
@@ -2652,7 +2655,7 @@
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C51" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D51" s="21">
         <v>0.339</v>
@@ -2660,7 +2663,7 @@
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C52" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D52" s="20">
         <v>75000</v>
@@ -2668,7 +2671,7 @@
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C53" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D53" s="21">
         <v>0.1948</v>
@@ -2676,14 +2679,14 @@
     </row>
     <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C57" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D57" s="20">
         <v>75000</v>
@@ -2691,7 +2694,7 @@
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C58" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D58" s="20">
         <v>25000</v>
@@ -2699,7 +2702,7 @@
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C59" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D59" s="20">
         <v>250000</v>
@@ -2707,7 +2710,7 @@
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C60" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D60" s="21">
         <v>0.065</v>
@@ -2715,7 +2718,7 @@
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C61" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D61" s="19">
         <v>10</v>
@@ -2755,7 +2758,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -2766,24 +2769,24 @@
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="22"/>
       <c r="C3" s="23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="25">
         <f>Assumptions!D12</f>
@@ -2808,7 +2811,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="26" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
@@ -2833,7 +2836,7 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="26" t="str">
         <f>C5*Assumptions!D26</f>
@@ -2858,7 +2861,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C7" s="26">
         <f>Assumptions!D12*Assumptions!D22</f>
@@ -2883,7 +2886,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" s="26">
         <f>Assumptions!D12*Assumptions!D24</f>
@@ -2908,7 +2911,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="26">
         <f>Assumptions!D27</f>
@@ -2933,7 +2936,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="28">
         <f>C6+C7+C8+C9</f>
@@ -2958,7 +2961,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C12" s="25">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
@@ -2983,7 +2986,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C13" s="26">
         <f>C12*Assumptions!D33</f>
@@ -3008,7 +3011,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C14" s="26">
         <f>Assumptions!D35*Assumptions!D40</f>
@@ -3033,7 +3036,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C15" s="26">
         <f>(C13+C14)*Assumptions!D42</f>
@@ -3058,7 +3061,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C16" s="28">
         <f>C13+C14+C15</f>
@@ -3083,7 +3086,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C18" s="26">
         <f>Assumptions!D46</f>
@@ -3108,7 +3111,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C19" s="26">
         <f>Assumptions!D48</f>
@@ -3133,7 +3136,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C20" s="26">
         <f>Assumptions!D12*Assumptions!D50</f>
@@ -3158,7 +3161,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C21" s="26">
         <f>Assumptions!D52</f>
@@ -3183,7 +3186,7 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C22" s="28">
         <f>C18+C19+C20+C21</f>
@@ -3234,7 +3237,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3245,24 +3248,24 @@
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="22"/>
       <c r="C3" s="23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="25">
         <f>Drivers!C4</f>
@@ -3287,7 +3290,7 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C6" s="26" t="str">
         <f>Drivers!C6</f>
@@ -3312,7 +3315,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C7" s="26">
         <f>Drivers!C7</f>
@@ -3337,7 +3340,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C8" s="26">
         <f>Drivers!C8</f>
@@ -3362,7 +3365,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="26">
         <f>Drivers!C9</f>
@@ -3387,7 +3390,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="28">
         <f>Drivers!C10</f>
@@ -3412,7 +3415,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="26">
         <f>Drivers!C16</f>
@@ -3437,7 +3440,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C13" s="26">
         <f>Drivers!C22</f>
@@ -3462,7 +3465,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C15" s="28">
         <f>C12+C13</f>
@@ -3487,7 +3490,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="27" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C16" s="29">
         <f>C10-C15</f>
@@ -3512,7 +3515,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C17" s="31">
         <f>IF(C10&gt;0,C16/C10,0)</f>
@@ -3563,7 +3566,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3574,24 +3577,24 @@
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="22"/>
       <c r="C3" s="23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C4" s="26">
         <f>'5-Year P&amp;L'!C16</f>
@@ -3616,7 +3619,7 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C6" s="26">
         <f>Assumptions!D58</f>
@@ -3641,7 +3644,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C7" s="26">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -3666,7 +3669,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C8" s="28">
         <f>C6+C7</f>
@@ -3691,7 +3694,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C10" s="32">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
@@ -3716,7 +3719,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C12" s="26">
         <f>C4-C8</f>
@@ -3741,7 +3744,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C14" s="34">
         <f>Assumptions!D57+C12</f>
@@ -3792,7 +3795,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3803,24 +3806,24 @@
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="22"/>
       <c r="C3" s="23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C4" s="25">
         <f>Drivers!C12</f>
@@ -3845,7 +3848,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C5" s="25">
         <f>Assumptions!D35</f>
@@ -3870,7 +3873,7 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="27" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C6" s="35">
         <f>C4+C5</f>
@@ -3921,13 +3924,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C3" s="26">
         <f>Assumptions!D59</f>
@@ -3936,7 +3939,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C4" s="31">
         <f>Assumptions!D60</f>
@@ -3945,7 +3948,7 @@
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" s="25">
         <f>Assumptions!D61</f>
@@ -3954,7 +3957,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C6" s="36">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -3963,7 +3966,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C8" s="32">
         <f>'Cash Flow &amp; DSCR'!C10</f>
@@ -3998,13 +4001,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="24" t="str">
         <f>Assumptions!D5</f>
@@ -4013,7 +4016,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="24" t="str">
         <f>Assumptions!D7</f>
@@ -4022,7 +4025,7 @@
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5" s="24" t="str">
         <f>Assumptions!D6</f>
@@ -4031,7 +4034,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C6" s="24">
         <f>Assumptions!D8</f>
@@ -4040,7 +4043,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" s="25">
         <f>Assumptions!D16</f>
@@ -4049,7 +4052,7 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C9" s="26">
         <f>Drivers!G10</f>
@@ -4058,7 +4061,7 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C10" s="37">
         <f>'5-Year P&amp;L'!G16</f>
@@ -4067,7 +4070,7 @@
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C12" s="12"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -605,7 +605,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -673,6 +673,9 @@
       <color rgb="FF1E293B"/>
       <sz val="14"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1E3A5F"/>
     </font>
     <font>
       <i/>
@@ -828,26 +831,26 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -857,60 +860,60 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -919,10 +922,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="192">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -151,7 +151,10 @@
     <t>SchoolStack Budget - Lender Pro Forma Assumptions</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs</t>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -718,7 +721,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -733,6 +736,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -756,7 +764,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -770,6 +778,15 @@
       <top/>
       <bottom style="medium">
         <color rgb="FF328555"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -816,7 +833,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -833,96 +850,97 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1627,7 +1645,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1646,456 +1664,456 @@
       <c r="G3" s="12"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="C5" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="39" t="s">
+      <c r="B5" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="D5" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="39" t="s">
+      <c r="E5" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="39" t="s">
+      <c r="F5" s="40" t="s">
         <v>99</v>
       </c>
+      <c r="G5" s="40" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="26">
         <v>100</v>
       </c>
-      <c r="C6" s="25">
-        <v>100</v>
-      </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>130</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>160</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>185</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="26">
         <v>200</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="C7" s="26">
+      <c r="B7" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="27">
         <v>995000</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <v>1306880</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <v>1636644.8</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <v>1934821.354</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="27">
         <v>2145936.2104</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="26">
+      <c r="B8" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" s="27">
         <v>824466.6666666666</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <v>951514</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <v>1138133.52</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <v>1280821.7409333333</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="27">
         <v>1431046.934954667</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="26">
+      <c r="B9" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" s="27">
         <v>271400</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <v>334544</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <v>423893.20399999997</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <v>543450.5083634</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="27">
         <v>692109.0785088772</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="C10" s="26">
+      <c r="B10" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" s="27">
         <v>59064.39316600799</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <v>59064.39316600799</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <v>59064.39316600799</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <v>59064.39316600799</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="27">
         <v>59064.39316600799</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="C11" s="29">
+      <c r="B11" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" s="30">
         <v>-159931.0598326745</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>-38242.39316600799</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>15553.682833992127</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>51484.71153725888</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="30">
         <v>-36284.19622955197</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="C12" s="29">
+      <c r="B12" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" s="30">
         <v>-84931.05983267451</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>-123173.45299868251</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>-107619.77016469039</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>-56135.05862743151</v>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="30">
         <v>-92419.25485698348</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" s="40">
+      <c r="B13" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="41">
         <v>-0.1607347335001754</v>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="41">
         <v>-0.029262360098867523</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="42">
         <v>0.009503395504016587</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="42">
         <v>0.026609542752265323</v>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="41">
         <v>-0.016908329359328268</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="26">
+      <c r="B14" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="C14" s="27">
         <v>9950</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <v>10052.923076923076</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <v>10229.03</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="27">
         <v>10458.493805405406</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="27">
         <v>10729.681052000002</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="C15" s="40">
+      <c r="B15" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" s="41">
         <v>0.8286097152428811</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="41">
         <v>0.7280806194906954</v>
       </c>
-      <c r="E15" s="40">
+      <c r="E15" s="41">
         <v>0.6954065537005952</v>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="41">
         <v>0.6619844970624266</v>
       </c>
-      <c r="G15" s="40">
+      <c r="G15" s="41">
         <v>0.6668636877551553</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C16" s="42">
+      <c r="B16" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C16" s="43">
         <v>0.08182914572864322</v>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="43">
         <v>0.0767960333006856</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="43">
         <v>0.07770040341068507</v>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="43">
         <v>0.0842636722878654</v>
       </c>
-      <c r="G16" s="42">
+      <c r="G16" s="43">
         <v>0.09675624212238845</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="40">
+      <c r="B17" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="41">
         <v>-0.10137353433835843</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="42">
         <v>0.015932602840352597</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="42">
         <v>0.04559210159712117</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="42">
         <v>0.057136595311355426</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="42">
         <v>0.010615505170216507</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C18" s="43">
+      <c r="B18" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" s="44">
         <v>-1.7077406752181137</v>
       </c>
-      <c r="D18" s="43">
+      <c r="D18" s="44">
         <v>0.35253049906865414</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="45">
         <v>1.2633343373269994</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="45">
         <v>1.871670879484945</v>
       </c>
-      <c r="G18" s="43">
+      <c r="G18" s="44">
         <v>0.38568409350163607</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="C19" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
+      <c r="B19" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="C20" s="46" t="s">
+      <c r="B20" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
+      <c r="C20" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="C22" s="38" t="s">
+      <c r="B22" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="C22" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38" t="s">
+      <c r="D22" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="G22" s="38"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="G22" s="39"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="C23" s="48" t="s">
+      <c r="B23" s="48" t="s">
         <v>167</v>
       </c>
-      <c r="D23" s="49" t="s">
+      <c r="C23" s="49" t="s">
         <v>168</v>
       </c>
-      <c r="E23" s="49"/>
-      <c r="F23" s="50" t="s">
+      <c r="D23" s="50" t="s">
         <v>169</v>
       </c>
-      <c r="G23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="G23" s="51"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="47" t="s">
-        <v>170</v>
-      </c>
-      <c r="C24" s="48" t="s">
-        <v>167</v>
-      </c>
-      <c r="D24" s="49" t="s">
+      <c r="B24" s="48" t="s">
         <v>171</v>
       </c>
-      <c r="E24" s="49"/>
-      <c r="F24" s="50" t="s">
+      <c r="C24" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="D24" s="50" t="s">
         <v>172</v>
       </c>
-      <c r="G24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="G24" s="51"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="47" t="s">
-        <v>173</v>
-      </c>
-      <c r="C25" s="48" t="s">
-        <v>167</v>
-      </c>
-      <c r="D25" s="49" t="s">
+      <c r="B25" s="48" t="s">
         <v>174</v>
       </c>
-      <c r="E25" s="49"/>
-      <c r="F25" s="50" t="s">
+      <c r="C25" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="D25" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="G25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="G25" s="51"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="C26" s="51" t="s">
+      <c r="B26" s="48" t="s">
         <v>177</v>
       </c>
-      <c r="D26" s="49" t="s">
+      <c r="C26" s="52" t="s">
         <v>178</v>
       </c>
-      <c r="E26" s="49"/>
-      <c r="F26" s="50" t="s">
+      <c r="D26" s="50" t="s">
         <v>179</v>
       </c>
-      <c r="G26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="51" t="s">
+        <v>180</v>
+      </c>
+      <c r="G26" s="51"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="C27" s="48" t="s">
-        <v>167</v>
-      </c>
-      <c r="D27" s="49" t="s">
+      <c r="B27" s="48" t="s">
         <v>181</v>
       </c>
-      <c r="E27" s="49"/>
-      <c r="F27" s="50" t="s">
+      <c r="C27" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="D27" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="G27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="G27" s="51"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="C28" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="D28" s="49" t="s">
+      <c r="B28" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="E28" s="49"/>
-      <c r="F28" s="50" t="s">
+      <c r="C28" s="52" t="s">
+        <v>178</v>
+      </c>
+      <c r="D28" s="50" t="s">
         <v>185</v>
       </c>
-      <c r="G28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="G28" s="51"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="47" t="s">
-        <v>186</v>
-      </c>
-      <c r="C29" s="48" t="s">
-        <v>167</v>
-      </c>
-      <c r="D29" s="49" t="s">
+      <c r="B29" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="E29" s="49"/>
-      <c r="F29" s="50" t="s">
+      <c r="C29" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="D29" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="G29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="G29" s="51"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="47" t="s">
+      <c r="B31" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
+      <c r="C31" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="52" t="s">
-        <v>190</v>
-      </c>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
+      <c r="B33" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -2341,389 +2359,392 @@
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>43</v>
       </c>
+      <c r="D2" s="16" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
+      <c r="B3" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="18" t="s">
+      <c r="C5" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="18" t="s">
+      <c r="C6" s="18" t="s">
         <v>47</v>
       </c>
+      <c r="D6" s="19" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="18" t="s">
+      <c r="C7" s="18" t="s">
         <v>49</v>
       </c>
+      <c r="D7" s="19" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="18">
+      <c r="C8" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="19">
         <v>2023</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
+      <c r="B10" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="19">
+      <c r="C12" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="20">
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="19">
+      <c r="C13" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="20">
         <v>130</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="19">
+      <c r="C14" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="20">
         <v>160</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="19">
+      <c r="C15" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="20">
         <v>185</v>
       </c>
     </row>
     <row r="16" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="19">
+      <c r="C16" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="20">
         <v>200</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
+      <c r="B18" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="20">
+      <c r="C20" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="21">
+      <c r="C21" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="20">
+      <c r="C22" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="21">
         <v>8700</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="21">
+      <c r="C23" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="20">
+      <c r="C24" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="21">
         <v>500</v>
       </c>
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="21">
+      <c r="C25" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="21">
+      <c r="C26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="22">
         <v>0.95</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="20">
+      <c r="C27" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="21">
         <v>75000</v>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="21">
+      <c r="C28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
+      <c r="B30" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="19">
+      <c r="C32" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="20">
         <v>11</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D33" s="20">
+      <c r="C33" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="21">
         <v>40000</v>
       </c>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="21">
+      <c r="C34" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" s="19">
+      <c r="C35" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="20">
         <v>4</v>
       </c>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" s="19">
+      <c r="C36" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="20">
         <v>4</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D37" s="19">
+      <c r="C37" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="20">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D38" s="19">
+      <c r="C38" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" s="20">
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C39" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D39" s="19">
+      <c r="C39" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="20">
         <v>4</v>
       </c>
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C40" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D40" s="20">
+      <c r="C40" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" s="21">
         <v>66000</v>
       </c>
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C41" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D41" s="21">
+      <c r="C41" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D41" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C42" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D42" s="21">
+      <c r="C42" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" s="22">
         <v>0.24166666666666667</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
+      <c r="B44" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D46" s="20">
+      <c r="C46" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D46" s="21">
         <v>102000</v>
       </c>
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D47" s="21">
+      <c r="C47" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D47" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D48" s="20">
+      <c r="C48" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D48" s="21">
         <v>34400</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D49" s="21">
+      <c r="C49" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D49" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="D50" s="20">
+      <c r="C50" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D50" s="21">
         <v>600</v>
       </c>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D51" s="21">
+      <c r="C51" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" s="22">
         <v>0.339</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="D52" s="20">
+      <c r="C52" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D52" s="21">
         <v>75000</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D53" s="21">
+      <c r="C53" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D53" s="22">
         <v>0.1948</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
+      <c r="B55" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C57" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D57" s="20">
+      <c r="C57" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D57" s="21">
         <v>75000</v>
       </c>
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C58" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D58" s="20">
+      <c r="C58" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58" s="21">
         <v>25000</v>
       </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C59" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D59" s="20">
+      <c r="C59" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D59" s="21">
         <v>250000</v>
       </c>
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C60" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D60" s="21">
+      <c r="C60" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D60" s="22">
         <v>0.065</v>
       </c>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C61" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D61" s="19">
+      <c r="C61" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D61" s="20">
         <v>10</v>
       </c>
     </row>
@@ -2761,7 +2782,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -2770,444 +2791,444 @@
       <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="22"/>
-      <c r="C3" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="23" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="E3" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="F3" s="24" t="s">
         <v>99</v>
       </c>
+      <c r="G3" s="24" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="25">
+      <c r="B4" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="26">
         <f>Assumptions!D12</f>
         <v>100</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="26">
         <f>Assumptions!D13</f>
         <v>130</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="26">
         <f>Assumptions!D14</f>
         <v>160</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="26">
         <f>Assumptions!D15</f>
         <v>185</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="26">
         <f>Assumptions!D16</f>
         <v>200</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="26" t="str">
+      <c r="B5" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="27" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
         <v>0</v>
       </c>
-      <c r="D5" s="26" t="str">
+      <c r="D5" s="27" t="str">
         <f>Assumptions!D13*Assumptions!D20*(1+Assumptions!D21)^1</f>
         <v>0</v>
       </c>
-      <c r="E5" s="26" t="str">
+      <c r="E5" s="27" t="str">
         <f>Assumptions!D14*Assumptions!D20*(1+Assumptions!D21)^2</f>
         <v>0</v>
       </c>
-      <c r="F5" s="26" t="str">
+      <c r="F5" s="27" t="str">
         <f>Assumptions!D15*Assumptions!D20*(1+Assumptions!D21)^3</f>
         <v>0</v>
       </c>
-      <c r="G5" s="26" t="str">
+      <c r="G5" s="27" t="str">
         <f>Assumptions!D16*Assumptions!D20*(1+Assumptions!D21)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="26" t="str">
+      <c r="B6" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="27" t="str">
         <f>C5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="D6" s="26" t="str">
+      <c r="D6" s="27" t="str">
         <f>D5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="E6" s="26" t="str">
+      <c r="E6" s="27" t="str">
         <f>E5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="F6" s="26" t="str">
+      <c r="F6" s="27" t="str">
         <f>F5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="G6" s="26" t="str">
+      <c r="G6" s="27" t="str">
         <f>G5*Assumptions!D26</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="26">
+      <c r="B7" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="27">
         <f>Assumptions!D12*Assumptions!D22</f>
         <v>870000</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>Assumptions!D13*Assumptions!D22*(1+Assumptions!D23)^1</f>
         <v>1164930</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>Assumptions!D14*Assumptions!D22*(1+Assumptions!D23)^2</f>
         <v>1476772.8</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>Assumptions!D15*Assumptions!D22*(1+Assumptions!D23)^3</f>
         <v>1758744.1065</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="27">
         <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
         <v>1958385.3294</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="26">
+      <c r="B8" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="27">
         <f>Assumptions!D12*Assumptions!D24</f>
         <v>50000</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>Assumptions!D13*Assumptions!D24*(1+Assumptions!D25)^1</f>
         <v>66950</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>Assumptions!D14*Assumptions!D24*(1+Assumptions!D25)^2</f>
         <v>84872</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>Assumptions!D15*Assumptions!D24*(1+Assumptions!D25)^3</f>
         <v>101077.2475</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="27">
         <f>Assumptions!D16*Assumptions!D24*(1+Assumptions!D25)^4</f>
         <v>112550.881</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" s="26">
+      <c r="B9" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="27">
         <f>Assumptions!D27</f>
         <v>75000</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <f>Assumptions!D27*(1+Assumptions!D28)^1</f>
         <v>75000</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <f>Assumptions!D27*(1+Assumptions!D28)^2</f>
         <v>75000</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <f>Assumptions!D27*(1+Assumptions!D28)^3</f>
         <v>75000</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="27">
         <f>Assumptions!D27*(1+Assumptions!D28)^4</f>
         <v>75000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="28">
+      <c r="B10" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="29">
         <f>C6+C7+C8+C9</f>
         <v>995000</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>D6+D7+D8+D9</f>
         <v>1306880</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>E6+E7+E8+E9</f>
         <v>1636644.8</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>F6+F7+F8+F9</f>
         <v>1934821.354</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>G6+G7+G8+G9</f>
         <v>2145936.2104</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="25">
+      <c r="B12" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="26">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
         <v>10</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <f>CEILING(Assumptions!D13/Assumptions!D32,1)</f>
         <v>12</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <f>CEILING(Assumptions!D14/Assumptions!D32,1)</f>
         <v>15</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="26">
         <f>CEILING(Assumptions!D15/Assumptions!D32,1)</f>
         <v>17</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="26">
         <f>CEILING(Assumptions!D16/Assumptions!D32,1)</f>
         <v>19</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" s="26">
+      <c r="B13" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="27">
         <f>C12*Assumptions!D33</f>
         <v>400000</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <f>D12*Assumptions!D33*(1+Assumptions!D34)^1</f>
         <v>494400</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>E12*Assumptions!D33*(1+Assumptions!D34)^2</f>
         <v>636540</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <f>F12*Assumptions!D33*(1+Assumptions!D34)^3</f>
         <v>743054.36</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="27">
         <f>G12*Assumptions!D33*(1+Assumptions!D34)^4</f>
         <v>855386.6956</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" s="26">
+      <c r="B14" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="27">
         <f>Assumptions!D35*Assumptions!D40</f>
         <v>264000</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <f>Assumptions!D36*Assumptions!D40*(1+Assumptions!D41)^1</f>
         <v>271920</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <f>Assumptions!D37*Assumptions!D40*(1+Assumptions!D41)^2</f>
         <v>280077.6</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="27">
         <f>Assumptions!D38*Assumptions!D40*(1+Assumptions!D41)^3</f>
         <v>288479.928</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="27">
         <f>Assumptions!D39*Assumptions!D40*(1+Assumptions!D41)^4</f>
         <v>297134.32584</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="26">
+      <c r="B15" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="27">
         <f>(C13+C14)*Assumptions!D42</f>
         <v>160466.66666667</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="27">
         <f>(D13+D14)*Assumptions!D42</f>
         <v>185194</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="27">
         <f>(E13+E14)*Assumptions!D42</f>
         <v>221515.92</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="27">
         <f>(F13+F14)*Assumptions!D42</f>
         <v>249287.45293333</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="27">
         <f>(G13+G14)*Assumptions!D42</f>
         <v>278525.91351467</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C16" s="28">
+      <c r="B16" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" s="29">
         <f>C13+C14+C15</f>
         <v>824466.66666667</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>D13+D14+D15</f>
         <v>951514</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>E13+E14+E15</f>
         <v>1138133.52</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>F13+F14+F15</f>
         <v>1280821.74093333</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>G13+G14+G15</f>
         <v>1431046.93495467</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" s="26">
+      <c r="B18" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="27">
         <f>Assumptions!D46</f>
         <v>102000</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="27">
         <f>Assumptions!D46*(1+Assumptions!D47)^1</f>
         <v>105060</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="27">
         <f>Assumptions!D46*(1+Assumptions!D47)^2</f>
         <v>108211.8</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="27">
         <f>Assumptions!D46*(1+Assumptions!D47)^3</f>
         <v>111458.154</v>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="27">
         <f>Assumptions!D46*(1+Assumptions!D47)^4</f>
         <v>114801.89862</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" s="26">
+      <c r="B19" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="27">
         <f>Assumptions!D48</f>
         <v>34400</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="27">
         <f>Assumptions!D48*(1+Assumptions!D49)^1</f>
         <v>35432</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="27">
         <f>Assumptions!D48*(1+Assumptions!D49)^2</f>
         <v>36494.96</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="27">
         <f>Assumptions!D48*(1+Assumptions!D49)^3</f>
         <v>37589.8088</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="27">
         <f>Assumptions!D48*(1+Assumptions!D49)^4</f>
         <v>38717.503064</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" s="26">
+      <c r="B20" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="27">
         <f>Assumptions!D12*Assumptions!D50</f>
         <v>60000</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="27">
         <f>Assumptions!D13*Assumptions!D50*(1+Assumptions!D51)^1</f>
         <v>104442</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="27">
         <f>Assumptions!D14*Assumptions!D50*(1+Assumptions!D51)^2</f>
         <v>172120.416</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="27">
         <f>Assumptions!D15*Assumptions!D50*(1+Assumptions!D51)^3</f>
         <v>266480.055309</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="27">
         <f>Assumptions!D16*Assumptions!D50*(1+Assumptions!D51)^4</f>
         <v>385747.88546892</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="C21" s="26">
+      <c r="B21" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" s="27">
         <f>Assumptions!D52</f>
         <v>75000</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <f>Assumptions!D52*(1+Assumptions!D53)^1</f>
         <v>89610</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="27">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
         <v>107066.028</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="27">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
         <v>127922.4902544</v>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="27">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
         <v>152841.79135596</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="28">
+      <c r="B22" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="29">
         <f>C18+C19+C20+C21</f>
         <v>271400</v>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="29">
         <f>D18+D19+D20+D21</f>
         <v>334544</v>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="29">
         <f>E18+E19+E20+E21</f>
         <v>423893.204</v>
       </c>
-      <c r="F22" s="28">
+      <c r="F22" s="29">
         <f>F18+F19+F20+F21</f>
         <v>543450.5083634</v>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="29">
         <f>G18+G19+G20+G21</f>
         <v>692109.07850888</v>
       </c>
@@ -3240,7 +3261,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3249,294 +3270,294 @@
       <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="22"/>
-      <c r="C3" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="23" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="E3" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="F3" s="24" t="s">
         <v>99</v>
       </c>
+      <c r="G3" s="24" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="25">
+      <c r="B5" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="26">
         <f>Drivers!C4</f>
         <v>100</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <f>Drivers!D4</f>
         <v>130</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <f>Drivers!E4</f>
         <v>160</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <f>Drivers!F4</f>
         <v>185</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="26">
         <f>Drivers!G4</f>
         <v>200</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="26" t="str">
+      <c r="B6" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="27" t="str">
         <f>Drivers!C6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="26" t="str">
+      <c r="D6" s="27" t="str">
         <f>Drivers!D6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="26" t="str">
+      <c r="E6" s="27" t="str">
         <f>Drivers!E6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="26" t="str">
+      <c r="F6" s="27" t="str">
         <f>Drivers!F6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="26" t="str">
+      <c r="G6" s="27" t="str">
         <f>Drivers!G6</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="26">
+      <c r="B7" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="27">
         <f>Drivers!C7</f>
         <v>870000</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>Drivers!D7</f>
         <v>1164930</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>Drivers!E7</f>
         <v>1476772.8</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>Drivers!F7</f>
         <v>1758744.1065</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="27">
         <f>Drivers!G7</f>
         <v>1958385.3294</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" s="26">
+      <c r="B8" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="27">
         <f>Drivers!C8</f>
         <v>50000</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>Drivers!D8</f>
         <v>66950</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>Drivers!E8</f>
         <v>84872</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>Drivers!F8</f>
         <v>101077.2475</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="27">
         <f>Drivers!G8</f>
         <v>112550.881</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" s="26">
+      <c r="B9" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="27">
         <f>Drivers!C9</f>
         <v>75000</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <f>Drivers!D9</f>
         <v>75000</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <f>Drivers!E9</f>
         <v>75000</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <f>Drivers!F9</f>
         <v>75000</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="27">
         <f>Drivers!G9</f>
         <v>75000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="28">
+      <c r="B10" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="29">
         <f>Drivers!C10</f>
         <v>995000</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>Drivers!D10</f>
         <v>1306880</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>Drivers!E10</f>
         <v>1636644.8</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>Drivers!F10</f>
         <v>1934821.354</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>Drivers!G10</f>
         <v>2145936.2104</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="C12" s="26">
+      <c r="B12" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="27">
         <f>Drivers!C16</f>
         <v>824466.66666667</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>Drivers!D16</f>
         <v>951514</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>Drivers!E16</f>
         <v>1138133.52</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <f>Drivers!F16</f>
         <v>1280821.74093333</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="27">
         <f>Drivers!G16</f>
         <v>1431046.93495467</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="C13" s="26">
+      <c r="B13" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="27">
         <f>Drivers!C22</f>
         <v>271400</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <f>Drivers!D22</f>
         <v>334544</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>Drivers!E22</f>
         <v>423893.204</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <f>Drivers!F22</f>
         <v>543450.5083634</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="27">
         <f>Drivers!G22</f>
         <v>692109.07850888</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="C15" s="28">
+      <c r="B15" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="29">
         <f>C12+C13</f>
         <v>1095866.66666667</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="29">
         <f>D12+D13</f>
         <v>1286058</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="29">
         <f>E12+E13</f>
         <v>1562026.724</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>F12+F13</f>
         <v>1824272.24929673</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="29">
         <f>G12+G13</f>
         <v>2123156.01346354</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="29">
+      <c r="B16" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="30">
         <f>C10-C15</f>
         <v>-100866.66666667</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <f>D10-D15</f>
         <v>20822</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <f>E10-E15</f>
         <v>74618.076</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <f>F10-F15</f>
         <v>110549.10470327</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="31">
         <f>G10-G15</f>
         <v>22780.19693646</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="31">
+      <c r="B17" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="32">
         <f>IF(C10&gt;0,C16/C10,0)</f>
         <v>-0.10137353</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>IF(D10&gt;0,D16/D10,0)</f>
         <v>0.0159326</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>IF(E10&gt;0,E16/E10,0)</f>
         <v>0.0455921</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>IF(F10&gt;0,F16/F10,0)</f>
         <v>0.0571366</v>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="32">
         <f>IF(G10&gt;0,G16/G10,0)</f>
         <v>0.01061551</v>
       </c>
@@ -3569,7 +3590,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3578,194 +3599,194 @@
       <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="22"/>
-      <c r="C3" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="23" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="E3" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="F3" s="24" t="s">
         <v>99</v>
       </c>
+      <c r="G3" s="24" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="C4" s="26">
+      <c r="B4" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="27">
         <f>'5-Year P&amp;L'!C16</f>
         <v>-100866.66666667</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <f>'5-Year P&amp;L'!D16</f>
         <v>20822</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <f>'5-Year P&amp;L'!E16</f>
         <v>74618.076</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <f>'5-Year P&amp;L'!F16</f>
         <v>110549.10470327</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="27">
         <f>'5-Year P&amp;L'!G16</f>
         <v>22780.19693646</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="26">
+      <c r="B6" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="27">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="27">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="27">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="C7" s="26">
+      <c r="B7" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="28">
+      <c r="B8" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" s="29">
         <f>C6+C7</f>
         <v>59064.39316601</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <f>D6+D7</f>
         <v>59064.39316601</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <f>E6+E7</f>
         <v>59064.39316601</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <f>F6+F7</f>
         <v>59064.39316601</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="29">
         <f>G6+G7</f>
         <v>59064.39316601</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" s="32">
+      <c r="B10" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" s="33">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
         <v>-1.70774068</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="33">
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
         <v>0.3525305</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="34">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
         <v>1.26333434</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="34">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
         <v>1.87167088</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="33">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
         <v>0.38568409</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="C12" s="26">
+      <c r="B12" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="27">
         <f>C4-C8</f>
         <v>-159931.05983267</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>D4-D8</f>
         <v>-38242.39316601</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>E4-E8</f>
         <v>15553.68283399</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <f>F4-F8</f>
         <v>51484.71153726</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="27">
         <f>G4-G8</f>
         <v>-36284.19622955</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="34">
+      <c r="B14" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="35">
         <f>Assumptions!D57+C12</f>
         <v>-84931.05983267</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="35">
         <f>C14+D12</f>
         <v>-123173.45299868</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="35">
         <f>D14+E12</f>
         <v>-107619.77016469</v>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="35">
         <f>E14+F12</f>
         <v>-56135.05862743</v>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="35">
         <f>F14+G12</f>
         <v>-92419.25485698</v>
       </c>
@@ -3798,7 +3819,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3807,94 +3828,94 @@
       <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="22"/>
-      <c r="C3" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="23" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="E3" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="F3" s="24" t="s">
         <v>99</v>
       </c>
+      <c r="G3" s="24" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="25">
+      <c r="B4" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="26">
         <f>Drivers!C12</f>
         <v>10</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="26">
         <f>Drivers!D12</f>
         <v>12</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="26">
         <f>Drivers!E12</f>
         <v>15</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="26">
         <f>Drivers!F12</f>
         <v>17</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="26">
         <f>Drivers!G12</f>
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="25">
+      <c r="B5" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="26">
         <f>Assumptions!D35</f>
         <v>4</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <f>Assumptions!D36</f>
         <v>4</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <f>Assumptions!D37</f>
         <v>4</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <f>Assumptions!D38</f>
         <v>4</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="26">
         <f>Assumptions!D39</f>
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="35">
+      <c r="B6" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="36">
         <f>C4+C5</f>
         <v>14</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="36">
         <f>D4+D5</f>
         <v>16</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="36">
         <f>E4+E5</f>
         <v>19</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="36">
         <f>F4+F5</f>
         <v>21</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="36">
         <f>G4+G5</f>
         <v>23</v>
       </c>
@@ -3927,51 +3948,51 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="C3" s="26">
+      <c r="B3" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="27">
         <f>Assumptions!D59</f>
         <v>250000</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="31">
+      <c r="B4" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="32">
         <f>Assumptions!D60</f>
         <v>0.065</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="25">
+      <c r="B5" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="26">
         <f>Assumptions!D61</f>
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="36">
+      <c r="B6" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="37">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="32">
+      <c r="B8" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="33">
         <f>'Cash Flow &amp; DSCR'!C10</f>
         <v>-1.70774068</v>
       </c>
@@ -4004,76 +4025,76 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="24" t="str">
+      <c r="B3" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="25" t="str">
         <f>Assumptions!D5</f>
         <v>Heritage Academy</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="24" t="str">
+      <c r="B4" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="25" t="str">
         <f>Assumptions!D7</f>
         <v>Private School</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="24" t="str">
+      <c r="B5" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="25" t="str">
         <f>Assumptions!D6</f>
         <v>FL</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="C6" s="24">
+      <c r="B6" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="25">
         <f>Assumptions!D8</f>
         <v>2023</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="25">
+      <c r="B8" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="26">
         <f>Assumptions!D16</f>
         <v>200</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="C9" s="26">
+      <c r="B9" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" s="27">
         <f>Drivers!G10</f>
         <v>2145936.2104</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="37">
+      <c r="B10" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="38">
         <f>'5-Year P&amp;L'!G16</f>
         <v>22780.19693646</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C12" s="12"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="192">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -850,7 +850,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2343,7 +2343,7 @@
     <tabColor rgb="FFD97706"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D61"/>
+  <dimension ref="B1:E61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -2359,7 +2359,7 @@
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
     </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
         <v>7</v>
       </c>
@@ -2367,6 +2367,9 @@
         <v>43</v>
       </c>
       <c r="D2" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>44</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="204">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -466,9 +466,21 @@
     <t>Heritage Academy — Financial Health Dashboard</t>
   </si>
   <si>
+    <t>● Green = healthy</t>
+  </si>
+  <si>
+    <t>◐ Yellow = monitor</t>
+  </si>
+  <si>
+    <t>○ Red = action needed</t>
+  </si>
+  <si>
     <t>Metric</t>
   </si>
   <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
     <t>Revenue</t>
   </si>
   <si>
@@ -493,15 +505,36 @@
     <t>Revenue per Student</t>
   </si>
   <si>
+    <t>≥ $10,000</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
+    <t>≤ 55%</t>
+  </si>
+  <si>
     <t>Facility %</t>
   </si>
   <si>
+    <t>≤ 15%</t>
+  </si>
+  <si>
+    <t>≥ 10%</t>
+  </si>
+  <si>
+    <t>Revenue Sources</t>
+  </si>
+  <si>
+    <t>≥ 3 sources</t>
+  </si>
+  <si>
     <t>DSCR</t>
   </si>
   <si>
+    <t>≥ 1.25x</t>
+  </si>
+  <si>
     <t>Break-even Year</t>
   </si>
   <si>
@@ -509,6 +542,9 @@
   </si>
   <si>
     <t>5 months</t>
+  </si>
+  <si>
+    <t>60+ months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -608,7 +644,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -705,6 +741,12 @@
     <font>
       <b/>
       <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -833,7 +875,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -909,6 +951,9 @@
     <xf numFmtId="165" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -919,9 +964,17 @@
     <xf numFmtId="166" fontId="16" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -929,9 +982,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -943,14 +996,35 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1631,19 +1705,20 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF0D9488"/>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G33"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>147</v>
       </c>
@@ -1652,8 +1727,9 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="12" t="s">
         <v>40</v>
       </c>
@@ -1662,559 +1738,632 @@
       <c r="E3" s="12"/>
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="39" t="s">
+      <c r="H3" s="12"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="D4" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D6" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E6" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="40" t="s">
+      <c r="F6" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="G5" s="40" t="s">
+      <c r="G6" s="43" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="26">
-        <v>100</v>
-      </c>
-      <c r="D6" s="26">
-        <v>130</v>
-      </c>
-      <c r="E6" s="26">
-        <v>160</v>
-      </c>
-      <c r="F6" s="26">
-        <v>185</v>
-      </c>
-      <c r="G6" s="26">
-        <v>200</v>
+      <c r="H6" s="43" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="27">
-        <v>995000</v>
-      </c>
-      <c r="D7" s="27">
-        <v>1306880</v>
-      </c>
-      <c r="E7" s="27">
-        <v>1636644.8</v>
-      </c>
-      <c r="F7" s="27">
-        <v>1934821.354</v>
-      </c>
-      <c r="G7" s="27">
-        <v>2145936.2104</v>
+        <v>101</v>
+      </c>
+      <c r="C7" s="26">
+        <v>100</v>
+      </c>
+      <c r="D7" s="26">
+        <v>130</v>
+      </c>
+      <c r="E7" s="26">
+        <v>160</v>
+      </c>
+      <c r="F7" s="26">
+        <v>185</v>
+      </c>
+      <c r="G7" s="26">
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C8" s="27">
-        <v>824466.6666666666</v>
+        <v>995000</v>
       </c>
       <c r="D8" s="27">
-        <v>951514</v>
+        <v>1306880</v>
       </c>
       <c r="E8" s="27">
-        <v>1138133.52</v>
+        <v>1636644.8</v>
       </c>
       <c r="F8" s="27">
-        <v>1280821.7409333333</v>
+        <v>1934821.354</v>
       </c>
       <c r="G8" s="27">
-        <v>1431046.934954667</v>
+        <v>2145936.2104</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C9" s="27">
-        <v>271400</v>
+        <v>824466.6666666666</v>
       </c>
       <c r="D9" s="27">
-        <v>334544</v>
+        <v>951514</v>
       </c>
       <c r="E9" s="27">
-        <v>423893.20399999997</v>
+        <v>1138133.52</v>
       </c>
       <c r="F9" s="27">
-        <v>543450.5083634</v>
+        <v>1280821.7409333333</v>
       </c>
       <c r="G9" s="27">
-        <v>692109.0785088772</v>
+        <v>1431046.934954667</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C10" s="27">
+        <v>271400</v>
+      </c>
+      <c r="D10" s="27">
+        <v>334544</v>
+      </c>
+      <c r="E10" s="27">
+        <v>423893.20399999997</v>
+      </c>
+      <c r="F10" s="27">
+        <v>543450.5083634</v>
+      </c>
+      <c r="G10" s="27">
+        <v>692109.0785088772</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="27">
         <v>59064.39316600799</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D11" s="27">
         <v>59064.39316600799</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E11" s="27">
         <v>59064.39316600799</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F11" s="27">
         <v>59064.39316600799</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G11" s="27">
         <v>59064.39316600799</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="28" t="s">
-        <v>153</v>
-      </c>
-      <c r="C11" s="30">
-        <v>-159931.0598326745</v>
-      </c>
-      <c r="D11" s="30">
-        <v>-38242.39316600799</v>
-      </c>
-      <c r="E11" s="31">
-        <v>15553.682833992127</v>
-      </c>
-      <c r="F11" s="31">
-        <v>51484.71153725888</v>
-      </c>
-      <c r="G11" s="30">
-        <v>-36284.19622955197</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="28" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C12" s="30">
-        <v>-84931.05983267451</v>
+        <v>-159931.0598326745</v>
       </c>
       <c r="D12" s="30">
-        <v>-123173.45299868251</v>
-      </c>
-      <c r="E12" s="30">
-        <v>-107619.77016469039</v>
-      </c>
-      <c r="F12" s="30">
-        <v>-56135.05862743151</v>
+        <v>-38242.39316600799</v>
+      </c>
+      <c r="E12" s="31">
+        <v>15553.682833992127</v>
+      </c>
+      <c r="F12" s="31">
+        <v>51484.71153725888</v>
       </c>
       <c r="G12" s="30">
-        <v>-92419.25485698348</v>
+        <v>-36284.19622955197</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="41">
-        <v>-0.1607347335001754</v>
-      </c>
-      <c r="D13" s="41">
-        <v>-0.029262360098867523</v>
-      </c>
-      <c r="E13" s="42">
-        <v>0.009503395504016587</v>
-      </c>
-      <c r="F13" s="42">
-        <v>0.026609542752265323</v>
-      </c>
-      <c r="G13" s="41">
-        <v>-0.016908329359328268</v>
+        <v>158</v>
+      </c>
+      <c r="C13" s="30">
+        <v>-84931.05983267451</v>
+      </c>
+      <c r="D13" s="30">
+        <v>-123173.45299868251</v>
+      </c>
+      <c r="E13" s="30">
+        <v>-107619.77016469039</v>
+      </c>
+      <c r="F13" s="30">
+        <v>-56135.05862743151</v>
+      </c>
+      <c r="G13" s="30">
+        <v>-92419.25485698348</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="C14" s="27">
+        <v>159</v>
+      </c>
+      <c r="C14" s="44">
+        <v>-0.1607347335001754</v>
+      </c>
+      <c r="D14" s="44">
+        <v>-0.029262360098867523</v>
+      </c>
+      <c r="E14" s="45">
+        <v>0.009503395504016587</v>
+      </c>
+      <c r="F14" s="45">
+        <v>0.026609542752265323</v>
+      </c>
+      <c r="G14" s="44">
+        <v>-0.016908329359328268</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="46">
         <v>9950</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D15" s="47">
         <v>10052.923076923076</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E15" s="47">
         <v>10229.03</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F15" s="47">
         <v>10458.493805405406</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G15" s="47">
         <v>10729.681052000002</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="C15" s="41">
+      <c r="H15" s="48" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="44">
         <v>0.8286097152428811</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D16" s="44">
         <v>0.7280806194906954</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E16" s="44">
         <v>0.6954065537005952</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F16" s="44">
         <v>0.6619844970624266</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G16" s="44">
         <v>0.6668636877551553</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="C16" s="43">
+      <c r="H16" s="48" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="C17" s="49">
         <v>0.08182914572864322</v>
       </c>
-      <c r="D16" s="43">
+      <c r="D17" s="49">
         <v>0.0767960333006856</v>
       </c>
-      <c r="E16" s="43">
+      <c r="E17" s="49">
         <v>0.07770040341068507</v>
       </c>
-      <c r="F16" s="43">
+      <c r="F17" s="49">
         <v>0.0842636722878654</v>
       </c>
-      <c r="G16" s="43">
+      <c r="G17" s="49">
         <v>0.09675624212238845</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="28" t="s">
+      <c r="H17" s="48" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="41">
+      <c r="C18" s="44">
         <v>-0.10137353433835843</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D18" s="45">
         <v>0.015932602840352597</v>
       </c>
-      <c r="E17" s="42">
+      <c r="E18" s="45">
         <v>0.04559210159712117</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F18" s="45">
         <v>0.057136595311355426</v>
       </c>
-      <c r="G17" s="42">
+      <c r="G18" s="45">
         <v>0.010615505170216507</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="C18" s="44">
+      <c r="H18" s="48" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" s="50">
+        <v>1</v>
+      </c>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="48" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="51">
         <v>-1.7077406752181137</v>
       </c>
-      <c r="D18" s="44">
+      <c r="D20" s="51">
         <v>0.35253049906865414</v>
       </c>
-      <c r="E18" s="45">
+      <c r="E20" s="52">
         <v>1.2633343373269994</v>
       </c>
-      <c r="F18" s="45">
+      <c r="F20" s="52">
         <v>1.871670879484945</v>
       </c>
-      <c r="G18" s="44">
+      <c r="G20" s="51">
         <v>0.38568409350163607</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="C19" s="46" t="s">
+      <c r="H20" s="48" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="C20" s="47" t="s">
-        <v>162</v>
-      </c>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="C22" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="D22" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="G22" s="39"/>
-    </row>
-    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="48" t="s">
-        <v>167</v>
-      </c>
-      <c r="C23" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="D23" s="50" t="s">
-        <v>169</v>
-      </c>
-      <c r="E23" s="50"/>
-      <c r="F23" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="G23" s="51"/>
-    </row>
-    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="48" t="s">
-        <v>171</v>
-      </c>
-      <c r="C24" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="D24" s="50" t="s">
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="48" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="E24" s="50"/>
-      <c r="F24" s="51" t="s">
+      <c r="C22" s="54" t="s">
         <v>173</v>
       </c>
-      <c r="G24" s="51"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="48" t="s">
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="48" t="s">
         <v>174</v>
       </c>
-      <c r="C25" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="D25" s="50" t="s">
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="E25" s="50"/>
-      <c r="F25" s="51" t="s">
+      <c r="C24" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="G25" s="51"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="48" t="s">
+      <c r="D24" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="C26" s="52" t="s">
+      <c r="E24" s="42"/>
+      <c r="F24" s="42" t="s">
         <v>178</v>
       </c>
-      <c r="D26" s="50" t="s">
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="55" t="s">
         <v>179</v>
       </c>
-      <c r="E26" s="50"/>
-      <c r="F26" s="51" t="s">
+      <c r="C25" s="56" t="s">
         <v>180</v>
       </c>
-      <c r="G26" s="51"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="48" t="s">
+      <c r="D25" s="57" t="s">
         <v>181</v>
       </c>
-      <c r="C27" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="D27" s="50" t="s">
+      <c r="E25" s="57"/>
+      <c r="F25" s="58" t="s">
         <v>182</v>
       </c>
-      <c r="E27" s="50"/>
-      <c r="F27" s="51" t="s">
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="55" t="s">
         <v>183</v>
       </c>
-      <c r="G27" s="51"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="48" t="s">
+      <c r="C26" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="D26" s="57" t="s">
         <v>184</v>
       </c>
-      <c r="C28" s="52" t="s">
-        <v>178</v>
-      </c>
-      <c r="D28" s="50" t="s">
+      <c r="E26" s="57"/>
+      <c r="F26" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="E28" s="50"/>
-      <c r="F28" s="51" t="s">
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="55" t="s">
         <v>186</v>
       </c>
-      <c r="G28" s="51"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="48" t="s">
+      <c r="C27" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="D27" s="57" t="s">
         <v>187</v>
       </c>
-      <c r="C29" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="D29" s="50" t="s">
+      <c r="E27" s="57"/>
+      <c r="F27" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="50"/>
-      <c r="F29" s="51" t="s">
+      <c r="G27" s="58"/>
+      <c r="H27" s="58"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="55" t="s">
         <v>189</v>
       </c>
-      <c r="G29" s="51"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="48" t="s">
+      <c r="C28" s="59" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="E28" s="57"/>
+      <c r="F28" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="55" t="s">
+        <v>193</v>
+      </c>
+      <c r="C29" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="D29" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="E29" s="57"/>
+      <c r="F29" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="C30" s="59" t="s">
+        <v>190</v>
+      </c>
+      <c r="D30" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="E30" s="57"/>
+      <c r="F30" s="58" t="s">
+        <v>198</v>
+      </c>
+      <c r="G30" s="58"/>
+      <c r="H30" s="58"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="C31" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="D31" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="E31" s="57"/>
+      <c r="F31" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="53" t="s">
-        <v>191</v>
-      </c>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="53"/>
-      <c r="G33" s="53"/>
+      <c r="C33" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="60" t="s">
+        <v>203</v>
+      </c>
+      <c r="C35" s="60"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="60"/>
+      <c r="H35" s="60"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
+  <mergeCells count="23">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F26:H26"/>
     <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F27:H27"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
-  <conditionalFormatting sqref="C11:G11">
+  <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C11&gt;=0</formula>
+      <formula>C12&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C11&gt;=-1</formula>
+      <formula>C12&gt;=-1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>C11&lt;-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:G12">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>C12&gt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>C12&gt;=-1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
       <formula>C12&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C13&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C13&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G14">
     <cfRule type="expression" dxfId="6" priority="1">
-      <formula>C13&gt;=0.05</formula>
+      <formula>C14&gt;=0.05</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="2">
-      <formula>C13&gt;=0</formula>
+      <formula>C14&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="8" priority="3">
-      <formula>C13&lt;0</formula>
+      <formula>C14&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:G15">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>C15&lt;=0.55</formula>
+      <formula>C15&gt;=10000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>C15&lt;=0.65</formula>
+      <formula>C15&gt;=7000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="3">
-      <formula>C15&gt;0.65</formula>
+      <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.15</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.25</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.25</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&gt;=0.10</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&gt;=0</formula>
+      <formula>C17&lt;=0.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&lt;0</formula>
+      <formula>C17&gt;0.25</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=1.25</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=1.0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;1.0</formula>
+      <formula>C18&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G20">
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>C20&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>C20&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="3">
+      <formula>C20&lt;1.0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="208">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -397,6 +397,15 @@
     <t>Operating Margin</t>
   </si>
   <si>
+    <t>Cumulative Net Income</t>
+  </si>
+  <si>
+    <t>Break-even</t>
+  </si>
+  <si>
+    <t>✓ Break-even</t>
+  </si>
+  <si>
     <t>Cash Flow &amp; Debt Service Coverage</t>
   </si>
   <si>
@@ -538,6 +547,9 @@
     <t>Break-even Year</t>
   </si>
   <si>
+    <t>Not reached</t>
+  </si>
+  <si>
     <t>Cash Runway</t>
   </si>
   <si>
@@ -565,7 +577,7 @@
     <t>○ Needs attention</t>
   </si>
   <si>
-    <t>Year 5 margin of -2% signals the model is not yet on a sustainable path.</t>
+    <t>The model does not reach break-even within 5 years. This needs to be addressed before approaching lenders.</t>
   </si>
   <si>
     <t>Revisit revenue assumptions and cost structure to build a clear path to break-even.</t>
@@ -933,6 +945,15 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -943,9 +964,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -974,14 +992,13 @@
     <xf numFmtId="166" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -992,9 +1009,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1720,7 +1734,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1741,37 +1755,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" s="40" t="s">
-        <v>149</v>
-      </c>
-      <c r="F4" s="41" t="s">
-        <v>150</v>
+      <c r="B4" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="F4" s="43" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="42" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="43" t="s">
+      <c r="B6" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="43" t="s">
+      <c r="F6" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="43" t="s">
+      <c r="G6" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="43" t="s">
-        <v>152</v>
+      <c r="H6" s="45" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1796,7 +1810,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C8" s="27">
         <v>995000</v>
@@ -1816,7 +1830,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C9" s="27">
         <v>824466.6666666666</v>
@@ -1836,7 +1850,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C10" s="27">
         <v>271400</v>
@@ -1856,7 +1870,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C11" s="27">
         <v>59064.39316600799</v>
@@ -1876,7 +1890,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="28" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C12" s="30">
         <v>-159931.0598326745</v>
@@ -1896,7 +1910,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="28" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C13" s="30">
         <v>-84931.05983267451</v>
@@ -1916,326 +1930,326 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="C14" s="44">
+        <v>162</v>
+      </c>
+      <c r="C14" s="46">
         <v>-0.1607347335001754</v>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="46">
         <v>-0.029262360098867523</v>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="47">
         <v>0.009503395504016587</v>
       </c>
-      <c r="F14" s="45">
+      <c r="F14" s="47">
         <v>0.026609542752265323</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="46">
         <v>-0.016908329359328268</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="C15" s="46">
+        <v>163</v>
+      </c>
+      <c r="C15" s="48">
         <v>9950</v>
       </c>
-      <c r="D15" s="47">
+      <c r="D15" s="49">
         <v>10052.923076923076</v>
       </c>
-      <c r="E15" s="47">
+      <c r="E15" s="49">
         <v>10229.03</v>
       </c>
-      <c r="F15" s="47">
+      <c r="F15" s="49">
         <v>10458.493805405406</v>
       </c>
-      <c r="G15" s="47">
+      <c r="G15" s="49">
         <v>10729.681052000002</v>
       </c>
-      <c r="H15" s="48" t="s">
-        <v>161</v>
+      <c r="H15" s="50" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="C16" s="44">
+        <v>165</v>
+      </c>
+      <c r="C16" s="46">
         <v>0.8286097152428811</v>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="46">
         <v>0.7280806194906954</v>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="46">
         <v>0.6954065537005952</v>
       </c>
-      <c r="F16" s="44">
+      <c r="F16" s="46">
         <v>0.6619844970624266</v>
       </c>
-      <c r="G16" s="44">
+      <c r="G16" s="46">
         <v>0.6668636877551553</v>
       </c>
-      <c r="H16" s="48" t="s">
-        <v>163</v>
+      <c r="H16" s="50" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="C17" s="49">
+        <v>167</v>
+      </c>
+      <c r="C17" s="51">
         <v>0.08182914572864322</v>
       </c>
-      <c r="D17" s="49">
+      <c r="D17" s="51">
         <v>0.0767960333006856</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="51">
         <v>0.07770040341068507</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="51">
         <v>0.0842636722878654</v>
       </c>
-      <c r="G17" s="49">
+      <c r="G17" s="51">
         <v>0.09675624212238845</v>
       </c>
-      <c r="H17" s="48" t="s">
-        <v>165</v>
+      <c r="H17" s="50" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="44">
+      <c r="C18" s="46">
         <v>-0.10137353433835843</v>
       </c>
-      <c r="D18" s="45">
+      <c r="D18" s="47">
         <v>0.015932602840352597</v>
       </c>
-      <c r="E18" s="45">
+      <c r="E18" s="47">
         <v>0.04559210159712117</v>
       </c>
-      <c r="F18" s="45">
+      <c r="F18" s="47">
         <v>0.057136595311355426</v>
       </c>
-      <c r="G18" s="45">
+      <c r="G18" s="47">
         <v>0.010615505170216507</v>
       </c>
-      <c r="H18" s="48" t="s">
-        <v>166</v>
+      <c r="H18" s="50" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="C19" s="50">
-        <v>1</v>
-      </c>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="48" t="s">
-        <v>168</v>
+        <v>170</v>
+      </c>
+      <c r="C19" s="52">
+        <v>3</v>
+      </c>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="50" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="C20" s="51">
+        <v>172</v>
+      </c>
+      <c r="C20" s="53">
         <v>-1.7077406752181137</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="53">
         <v>0.35253049906865414</v>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="54">
         <v>1.2633343373269994</v>
       </c>
-      <c r="F20" s="52">
+      <c r="F20" s="54">
         <v>1.871670879484945</v>
       </c>
-      <c r="G20" s="51">
+      <c r="G20" s="53">
         <v>0.38568409350163607</v>
       </c>
-      <c r="H20" s="48" t="s">
-        <v>170</v>
+      <c r="H20" s="50" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="C21" s="53" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" s="55" t="s">
+        <v>175</v>
+      </c>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="50" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="C22" s="54" t="s">
-        <v>173</v>
-      </c>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="48" t="s">
-        <v>174</v>
+        <v>176</v>
+      </c>
+      <c r="C22" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="50" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="42" t="s">
-        <v>175</v>
-      </c>
-      <c r="C24" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="D24" s="42" t="s">
-        <v>177</v>
-      </c>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42" t="s">
-        <v>178</v>
-      </c>
-      <c r="G24" s="42"/>
-      <c r="H24" s="42"/>
+      <c r="B24" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="C24" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="D24" s="44" t="s">
+        <v>181</v>
+      </c>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="55" t="s">
-        <v>179</v>
-      </c>
-      <c r="C25" s="56" t="s">
-        <v>180</v>
-      </c>
-      <c r="D25" s="57" t="s">
-        <v>181</v>
-      </c>
-      <c r="E25" s="57"/>
-      <c r="F25" s="58" t="s">
-        <v>182</v>
-      </c>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
+      <c r="B25" s="56" t="s">
+        <v>183</v>
+      </c>
+      <c r="C25" s="57" t="s">
+        <v>184</v>
+      </c>
+      <c r="D25" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="E25" s="58"/>
+      <c r="F25" s="59" t="s">
+        <v>186</v>
+      </c>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="55" t="s">
-        <v>183</v>
-      </c>
-      <c r="C26" s="56" t="s">
-        <v>180</v>
-      </c>
-      <c r="D26" s="57" t="s">
+      <c r="B26" s="56" t="s">
+        <v>187</v>
+      </c>
+      <c r="C26" s="57" t="s">
         <v>184</v>
       </c>
-      <c r="E26" s="57"/>
-      <c r="F26" s="58" t="s">
-        <v>185</v>
-      </c>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
+      <c r="D26" s="58" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" s="58"/>
+      <c r="F26" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="55" t="s">
-        <v>186</v>
-      </c>
-      <c r="C27" s="56" t="s">
-        <v>180</v>
-      </c>
-      <c r="D27" s="57" t="s">
-        <v>187</v>
-      </c>
-      <c r="E27" s="57"/>
-      <c r="F27" s="58" t="s">
-        <v>188</v>
-      </c>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
+      <c r="B27" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="C27" s="57" t="s">
+        <v>184</v>
+      </c>
+      <c r="D27" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="E27" s="58"/>
+      <c r="F27" s="59" t="s">
+        <v>192</v>
+      </c>
+      <c r="G27" s="59"/>
+      <c r="H27" s="59"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="55" t="s">
-        <v>189</v>
-      </c>
-      <c r="C28" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="D28" s="57" t="s">
-        <v>191</v>
-      </c>
-      <c r="E28" s="57"/>
-      <c r="F28" s="58" t="s">
-        <v>192</v>
-      </c>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
+      <c r="B28" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="D28" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="E28" s="58"/>
+      <c r="F28" s="59" t="s">
+        <v>196</v>
+      </c>
+      <c r="G28" s="59"/>
+      <c r="H28" s="59"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="55" t="s">
-        <v>193</v>
-      </c>
-      <c r="C29" s="56" t="s">
-        <v>180</v>
-      </c>
-      <c r="D29" s="57" t="s">
+      <c r="B29" s="56" t="s">
+        <v>197</v>
+      </c>
+      <c r="C29" s="57" t="s">
+        <v>184</v>
+      </c>
+      <c r="D29" s="58" t="s">
+        <v>198</v>
+      </c>
+      <c r="E29" s="58"/>
+      <c r="F29" s="59" t="s">
+        <v>199</v>
+      </c>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="C30" s="35" t="s">
         <v>194</v>
       </c>
-      <c r="E29" s="57"/>
-      <c r="F29" s="58" t="s">
-        <v>195</v>
-      </c>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="C30" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="D30" s="57" t="s">
-        <v>197</v>
-      </c>
-      <c r="E30" s="57"/>
-      <c r="F30" s="58" t="s">
-        <v>198</v>
-      </c>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
+      <c r="D30" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="E30" s="58"/>
+      <c r="F30" s="59" t="s">
+        <v>202</v>
+      </c>
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="55" t="s">
-        <v>199</v>
-      </c>
-      <c r="C31" s="56" t="s">
-        <v>180</v>
-      </c>
-      <c r="D31" s="57" t="s">
-        <v>200</v>
-      </c>
-      <c r="E31" s="57"/>
-      <c r="F31" s="58" t="s">
-        <v>201</v>
-      </c>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
+      <c r="B31" s="56" t="s">
+        <v>203</v>
+      </c>
+      <c r="C31" s="57" t="s">
+        <v>184</v>
+      </c>
+      <c r="D31" s="58" t="s">
+        <v>204</v>
+      </c>
+      <c r="E31" s="58"/>
+      <c r="F31" s="59" t="s">
+        <v>205</v>
+      </c>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="55" t="s">
+      <c r="B33" s="56" t="s">
         <v>39</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D33" s="28"/>
       <c r="E33" s="28"/>
@@ -2243,7 +2257,7 @@
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="60" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C35" s="60"/>
       <c r="D35" s="60"/>
@@ -3403,7 +3417,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G17"/>
+  <dimension ref="B1:G20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -3712,6 +3726,51 @@
       <c r="G17" s="32">
         <f>IF(G10&gt;0,G16/G10,0)</f>
         <v>0.01061551</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="33">
+        <f>C16</f>
+        <v>-100866.66666667</v>
+      </c>
+      <c r="D19" s="33">
+        <f>C19+D16</f>
+        <v>-80044.66666667</v>
+      </c>
+      <c r="E19" s="33">
+        <f>D19+E16</f>
+        <v>-5426.59066667</v>
+      </c>
+      <c r="F19" s="33">
+        <f>E19+F16</f>
+        <v>105122.5140366</v>
+      </c>
+      <c r="G19" s="33">
+        <f>F19+G16</f>
+        <v>127902.71097306</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3742,7 +3801,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3770,7 +3829,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C4" s="27">
         <f>'5-Year P&amp;L'!C16</f>
@@ -3795,7 +3854,7 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C6" s="27">
         <f>Assumptions!D58</f>
@@ -3820,7 +3879,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="25" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C7" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -3845,7 +3904,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="28" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C8" s="29">
         <f>C6+C7</f>
@@ -3870,32 +3929,32 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="C10" s="33">
+        <v>133</v>
+      </c>
+      <c r="C10" s="36">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
         <v>-1.70774068</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="36">
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
         <v>0.3525305</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="37">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
         <v>1.26333434</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="37">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
         <v>1.87167088</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="36">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
         <v>0.38568409</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="25" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C12" s="27">
         <f>C4-C8</f>
@@ -3920,25 +3979,25 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C14" s="35">
+        <v>135</v>
+      </c>
+      <c r="C14" s="38">
         <f>Assumptions!D57+C12</f>
         <v>-84931.05983267</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="38">
         <f>C14+D12</f>
         <v>-123173.45299868</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="38">
         <f>D14+E12</f>
         <v>-107619.77016469</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="38">
         <f>E14+F12</f>
         <v>-56135.05862743</v>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="38">
         <f>F14+G12</f>
         <v>-92419.25485698</v>
       </c>
@@ -3971,7 +4030,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3999,7 +4058,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C4" s="26">
         <f>Drivers!C12</f>
@@ -4024,7 +4083,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="25" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C5" s="26">
         <f>Assumptions!D35</f>
@@ -4049,25 +4108,25 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="36">
+        <v>139</v>
+      </c>
+      <c r="C6" s="39">
         <f>C4+C5</f>
         <v>14</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="39">
         <f>D4+D5</f>
         <v>16</v>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="39">
         <f>E4+E5</f>
         <v>19</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="39">
         <f>F4+F5</f>
         <v>21</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="39">
         <f>G4+G5</f>
         <v>23</v>
       </c>
@@ -4100,13 +4159,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="25" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C3" s="27">
         <f>Assumptions!D59</f>
@@ -4115,7 +4174,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C4" s="32">
         <f>Assumptions!D60</f>
@@ -4133,18 +4192,18 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="37">
+        <v>143</v>
+      </c>
+      <c r="C6" s="33">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" s="33">
+        <v>144</v>
+      </c>
+      <c r="C8" s="36">
         <f>'Cash Flow &amp; DSCR'!C10</f>
         <v>-1.70774068</v>
       </c>
@@ -4177,7 +4236,7 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C1" s="13"/>
     </row>
@@ -4210,7 +4269,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C6" s="25">
         <f>Assumptions!D8</f>
@@ -4228,7 +4287,7 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C9" s="27">
         <f>Drivers!G10</f>
@@ -4237,16 +4296,16 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" s="38">
+        <v>148</v>
+      </c>
+      <c r="C10" s="40">
         <f>'5-Year P&amp;L'!G16</f>
         <v>22780.19693646</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C12" s="12"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -2374,10 +2374,10 @@
       <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1.0</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1.0</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="207">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -545,9 +545,6 @@
   </si>
   <si>
     <t>Break-even Year</t>
-  </si>
-  <si>
-    <t>Not reached</t>
   </si>
   <si>
     <t>Cash Runway</t>
@@ -887,7 +884,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -998,6 +995,9 @@
     </xf>
     <xf numFmtId="167" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2082,196 +2082,208 @@
       <c r="B21" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="C21" s="55" t="s">
-        <v>175</v>
-      </c>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
+      <c r="C21" s="55" t="str">
+        <f>IF('5-Year P&amp;L'!C19&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="55" t="str">
+        <f>IF('5-Year P&amp;L'!D19&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="55" t="str">
+        <f>IF('5-Year P&amp;L'!E19&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="55" t="str">
+        <f>IF('5-Year P&amp;L'!F19&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="55" t="str">
+        <f>IF('5-Year P&amp;L'!G19&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="50" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="C22" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="C22" s="55" t="s">
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="50" t="s">
         <v>177</v>
-      </c>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="50" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="C24" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="C24" s="44" t="s">
+      <c r="D24" s="44" t="s">
         <v>180</v>
-      </c>
-      <c r="D24" s="44" t="s">
-        <v>181</v>
       </c>
       <c r="E24" s="44"/>
       <c r="F24" s="44" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G24" s="44"/>
       <c r="H24" s="44"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="56" t="s">
+      <c r="B25" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="C25" s="58" t="s">
         <v>183</v>
       </c>
-      <c r="C25" s="57" t="s">
+      <c r="D25" s="59" t="s">
         <v>184</v>
       </c>
-      <c r="D25" s="58" t="s">
+      <c r="E25" s="59"/>
+      <c r="F25" s="60" t="s">
         <v>185</v>
       </c>
-      <c r="E25" s="58"/>
-      <c r="F25" s="59" t="s">
+      <c r="G25" s="60"/>
+      <c r="H25" s="60"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="57" t="s">
         <v>186</v>
       </c>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="56" t="s">
+      <c r="C26" s="58" t="s">
+        <v>183</v>
+      </c>
+      <c r="D26" s="59" t="s">
         <v>187</v>
       </c>
-      <c r="C26" s="57" t="s">
-        <v>184</v>
-      </c>
-      <c r="D26" s="58" t="s">
+      <c r="E26" s="59"/>
+      <c r="F26" s="60" t="s">
         <v>188</v>
       </c>
-      <c r="E26" s="58"/>
-      <c r="F26" s="59" t="s">
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="57" t="s">
         <v>189</v>
       </c>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="56" t="s">
+      <c r="C27" s="58" t="s">
+        <v>183</v>
+      </c>
+      <c r="D27" s="59" t="s">
         <v>190</v>
       </c>
-      <c r="C27" s="57" t="s">
-        <v>184</v>
-      </c>
-      <c r="D27" s="58" t="s">
+      <c r="E27" s="59"/>
+      <c r="F27" s="60" t="s">
         <v>191</v>
       </c>
-      <c r="E27" s="58"/>
-      <c r="F27" s="59" t="s">
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="57" t="s">
         <v>192</v>
       </c>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="56" t="s">
+      <c r="C28" s="35" t="s">
         <v>193</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="D28" s="59" t="s">
         <v>194</v>
       </c>
-      <c r="D28" s="58" t="s">
+      <c r="E28" s="59"/>
+      <c r="F28" s="60" t="s">
         <v>195</v>
       </c>
-      <c r="E28" s="58"/>
-      <c r="F28" s="59" t="s">
+      <c r="G28" s="60"/>
+      <c r="H28" s="60"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="57" t="s">
         <v>196</v>
       </c>
-      <c r="G28" s="59"/>
-      <c r="H28" s="59"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="56" t="s">
+      <c r="C29" s="58" t="s">
+        <v>183</v>
+      </c>
+      <c r="D29" s="59" t="s">
         <v>197</v>
       </c>
-      <c r="C29" s="57" t="s">
-        <v>184</v>
-      </c>
-      <c r="D29" s="58" t="s">
+      <c r="E29" s="59"/>
+      <c r="F29" s="60" t="s">
         <v>198</v>
       </c>
-      <c r="E29" s="58"/>
-      <c r="F29" s="59" t="s">
+      <c r="G29" s="60"/>
+      <c r="H29" s="60"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="57" t="s">
         <v>199</v>
       </c>
-      <c r="G29" s="59"/>
-      <c r="H29" s="59"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="56" t="s">
+      <c r="C30" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="D30" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="C30" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="D30" s="58" t="s">
+      <c r="E30" s="59"/>
+      <c r="F30" s="60" t="s">
         <v>201</v>
       </c>
-      <c r="E30" s="58"/>
-      <c r="F30" s="59" t="s">
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="57" t="s">
         <v>202</v>
       </c>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="56" t="s">
+      <c r="C31" s="58" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" s="59" t="s">
         <v>203</v>
       </c>
-      <c r="C31" s="57" t="s">
-        <v>184</v>
-      </c>
-      <c r="D31" s="58" t="s">
+      <c r="E31" s="59"/>
+      <c r="F31" s="60" t="s">
         <v>204</v>
       </c>
-      <c r="E31" s="58"/>
-      <c r="F31" s="59" t="s">
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="28" t="s">
         <v>205</v>
-      </c>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="56" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="28" t="s">
-        <v>206</v>
       </c>
       <c r="D33" s="28"/>
       <c r="E33" s="28"/>
       <c r="F33" s="28"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="60" t="s">
-        <v>207</v>
-      </c>
-      <c r="C35" s="60"/>
-      <c r="D35" s="60"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="60"/>
-      <c r="G35" s="60"/>
-      <c r="H35" s="60"/>
+      <c r="B35" s="61" t="s">
+        <v>206</v>
+      </c>
+      <c r="C35" s="61"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="61"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -2352,10 +2364,10 @@
       <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.25</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.25</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="206">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -547,13 +547,10 @@
     <t>Break-even Year</t>
   </si>
   <si>
-    <t>Cash Runway</t>
-  </si>
-  <si>
-    <t>5 months</t>
-  </si>
-  <si>
-    <t>60+ months</t>
+    <t>Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t>≥ 24 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -989,7 +986,9 @@
     <xf numFmtId="166" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -999,7 +998,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2047,10 +2048,18 @@
       <c r="C19" s="52">
         <v>3</v>
       </c>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="52"/>
+      <c r="D19" s="52">
+        <v>3</v>
+      </c>
+      <c r="E19" s="52">
+        <v>3</v>
+      </c>
+      <c r="F19" s="52">
+        <v>3</v>
+      </c>
+      <c r="G19" s="52">
+        <v>3</v>
+      </c>
       <c r="H19" s="50" t="s">
         <v>171</v>
       </c>
@@ -2087,19 +2096,19 @@
         <v>0</v>
       </c>
       <c r="D21" s="55" t="str">
-        <f>IF('5-Year P&amp;L'!D19&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!D19&gt;=0,'5-Year P&amp;L'!C19&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="E21" s="55" t="str">
-        <f>IF('5-Year P&amp;L'!E19&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!E19&gt;=0,'5-Year P&amp;L'!D19&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F21" s="55" t="str">
-        <f>IF('5-Year P&amp;L'!F19&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!F19&gt;=0,'5-Year P&amp;L'!E19&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="55" t="str">
-        <f>IF('5-Year P&amp;L'!G19&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!G19&gt;=0,'5-Year P&amp;L'!F19&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="50" t="s">
@@ -2110,149 +2119,157 @@
       <c r="B22" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="C22" s="56" t="s">
+      <c r="C22" s="56">
+        <v>-1</v>
+      </c>
+      <c r="D22" s="56">
+        <v>-1</v>
+      </c>
+      <c r="E22" s="56">
+        <v>-1</v>
+      </c>
+      <c r="F22" s="56">
+        <v>0</v>
+      </c>
+      <c r="G22" s="56">
+        <v>-1</v>
+      </c>
+      <c r="H22" s="50" t="s">
         <v>176</v>
-      </c>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="50" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C24" s="44" t="s">
         <v>178</v>
       </c>
-      <c r="C24" s="44" t="s">
+      <c r="D24" s="44" t="s">
         <v>179</v>
-      </c>
-      <c r="D24" s="44" t="s">
-        <v>180</v>
       </c>
       <c r="E24" s="44"/>
       <c r="F24" s="44" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G24" s="44"/>
       <c r="H24" s="44"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="C25" s="58" t="s">
         <v>182</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="D25" s="59" t="s">
         <v>183</v>
-      </c>
-      <c r="D25" s="59" t="s">
-        <v>184</v>
       </c>
       <c r="E25" s="59"/>
       <c r="F25" s="60" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G25" s="60"/>
       <c r="H25" s="60"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="C26" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="D26" s="59" t="s">
         <v>186</v>
-      </c>
-      <c r="C26" s="58" t="s">
-        <v>183</v>
-      </c>
-      <c r="D26" s="59" t="s">
-        <v>187</v>
       </c>
       <c r="E26" s="59"/>
       <c r="F26" s="60" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G26" s="60"/>
       <c r="H26" s="60"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="C27" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="D27" s="59" t="s">
         <v>189</v>
-      </c>
-      <c r="C27" s="58" t="s">
-        <v>183</v>
-      </c>
-      <c r="D27" s="59" t="s">
-        <v>190</v>
       </c>
       <c r="E27" s="59"/>
       <c r="F27" s="60" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G27" s="60"/>
       <c r="H27" s="60"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="C28" s="35" t="s">
         <v>192</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="D28" s="59" t="s">
         <v>193</v>
-      </c>
-      <c r="D28" s="59" t="s">
-        <v>194</v>
       </c>
       <c r="E28" s="59"/>
       <c r="F28" s="60" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G28" s="60"/>
       <c r="H28" s="60"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="C29" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="D29" s="59" t="s">
         <v>196</v>
-      </c>
-      <c r="C29" s="58" t="s">
-        <v>183</v>
-      </c>
-      <c r="D29" s="59" t="s">
-        <v>197</v>
       </c>
       <c r="E29" s="59"/>
       <c r="F29" s="60" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G29" s="60"/>
       <c r="H29" s="60"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="D30" s="59" t="s">
         <v>199</v>
-      </c>
-      <c r="C30" s="35" t="s">
-        <v>193</v>
-      </c>
-      <c r="D30" s="59" t="s">
-        <v>200</v>
       </c>
       <c r="E30" s="59"/>
       <c r="F30" s="60" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G30" s="60"/>
       <c r="H30" s="60"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="D31" s="59" t="s">
         <v>202</v>
-      </c>
-      <c r="C31" s="58" t="s">
-        <v>183</v>
-      </c>
-      <c r="D31" s="59" t="s">
-        <v>203</v>
       </c>
       <c r="E31" s="59"/>
       <c r="F31" s="60" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G31" s="60"/>
       <c r="H31" s="60"/>
@@ -2262,7 +2279,7 @@
         <v>39</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D33" s="28"/>
       <c r="E33" s="28"/>
@@ -2270,7 +2287,7 @@
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="61" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C35" s="61"/>
       <c r="D35" s="61"/>
@@ -2280,11 +2297,9 @@
       <c r="H35" s="61"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -601,7 +601,7 @@
     <t>● Healthy</t>
   </si>
   <si>
-    <t>Facility costs at 10% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 7% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -2000,19 +2000,19 @@
         <v>167</v>
       </c>
       <c r="C17" s="51">
-        <v>0.08182914572864322</v>
+        <v>0.1370854271356784</v>
       </c>
       <c r="D17" s="51">
-        <v>0.0767960333006856</v>
+        <v>0.10750183643486777</v>
       </c>
       <c r="E17" s="51">
-        <v>0.07770040341068507</v>
+        <v>0.08841671693210401</v>
       </c>
       <c r="F17" s="51">
-        <v>0.0842636722878654</v>
+        <v>0.07703448305026303</v>
       </c>
       <c r="G17" s="51">
-        <v>0.09675624212238845</v>
+        <v>0.0715395923420222</v>
       </c>
       <c r="H17" s="50" t="s">
         <v>168</v>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="214">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -397,18 +397,27 @@
     <t>Operating Margin</t>
   </si>
   <si>
+    <t>Capital &amp; Debt Service</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
     <t>Cumulative Net Income</t>
   </si>
   <si>
     <t>Break-even</t>
   </si>
   <si>
-    <t>✓ Break-even</t>
-  </si>
-  <si>
     <t>Cash Flow &amp; Debt Service Coverage</t>
   </si>
   <si>
+    <t>Beginning Cash</t>
+  </si>
+  <si>
     <t>Net Operating Income</t>
   </si>
   <si>
@@ -427,7 +436,10 @@
     <t>Net Income After Debt</t>
   </si>
   <si>
-    <t>Cumulative Cash</t>
+    <t>Net Cash Flow</t>
+  </si>
+  <si>
+    <t>Ending Cash</t>
   </si>
   <si>
     <t>Staffing Detail</t>
@@ -469,6 +481,27 @@
     <t>Year 5 NOI</t>
   </si>
   <si>
+    <t>KEY RATIOS</t>
+  </si>
+  <si>
+    <t>Net Margin (Year 5)</t>
+  </si>
+  <si>
+    <t>Personnel % of Revenue (Year 5)</t>
+  </si>
+  <si>
+    <t>Revenue per Student (Year 5)</t>
+  </si>
+  <si>
+    <t>Expense per Student (Year 5)</t>
+  </si>
+  <si>
+    <t>DSCR (Year 1)</t>
+  </si>
+  <si>
+    <t>DSCR (Year 5)</t>
+  </si>
+  <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -500,15 +533,6 @@
   </si>
   <si>
     <t>Debt Service</t>
-  </si>
-  <si>
-    <t>Net Income</t>
-  </si>
-  <si>
-    <t>Ending Cash</t>
-  </si>
-  <si>
-    <t>Net Margin</t>
   </si>
   <si>
     <t>Revenue per Student</t>
@@ -881,7 +905,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -945,22 +969,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="167" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1010,6 +1032,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1735,7 +1760,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1757,18 +1782,18 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="41" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="D4" s="42" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="F4" s="43" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="44" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="C6" s="45" t="s">
         <v>96</v>
@@ -1786,7 +1811,7 @@
         <v>100</v>
       </c>
       <c r="H6" s="45" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1811,7 +1836,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C8" s="27">
         <v>995000</v>
@@ -1831,7 +1856,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C9" s="27">
         <v>824466.6666666666</v>
@@ -1851,7 +1876,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="C10" s="27">
         <v>271400</v>
@@ -1871,7 +1896,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="C11" s="27">
         <v>59064.39316600799</v>
@@ -1891,7 +1916,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="28" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="C12" s="30">
         <v>-159931.0598326745</v>
@@ -1911,7 +1936,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="28" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="C13" s="30">
         <v>-84931.05983267451</v>
@@ -1931,7 +1956,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="C14" s="46">
         <v>-0.1607347335001754</v>
@@ -1951,7 +1976,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C15" s="48">
         <v>9950</v>
@@ -1969,12 +1994,12 @@
         <v>10729.681052000002</v>
       </c>
       <c r="H15" s="50" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C16" s="46">
         <v>0.8286097152428811</v>
@@ -1992,12 +2017,12 @@
         <v>0.6668636877551553</v>
       </c>
       <c r="H16" s="50" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="28" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C17" s="51">
         <v>0.1370854271356784</v>
@@ -2015,7 +2040,7 @@
         <v>0.0715395923420222</v>
       </c>
       <c r="H17" s="50" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
@@ -2038,12 +2063,12 @@
         <v>0.010615505170216507</v>
       </c>
       <c r="H18" s="50" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C19" s="52">
         <v>3</v>
@@ -2061,12 +2086,12 @@
         <v>3</v>
       </c>
       <c r="H19" s="50" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C20" s="53">
         <v>-1.7077406752181137</v>
@@ -2084,31 +2109,31 @@
         <v>0.38568409350163607</v>
       </c>
       <c r="H20" s="50" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C21" s="55" t="str">
-        <f>IF('5-Year P&amp;L'!C19&gt;=0,"✓ Break-even","")</f>
+        <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="D21" s="55" t="str">
-        <f>IF(AND('5-Year P&amp;L'!D19&gt;=0,'5-Year P&amp;L'!C19&lt;0),"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="E21" s="55" t="str">
-        <f>IF(AND('5-Year P&amp;L'!E19&gt;=0,'5-Year P&amp;L'!D19&lt;0),"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F21" s="55" t="str">
-        <f>IF(AND('5-Year P&amp;L'!F19&gt;=0,'5-Year P&amp;L'!E19&lt;0),"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="55" t="str">
-        <f>IF(AND('5-Year P&amp;L'!G19&gt;=0,'5-Year P&amp;L'!F19&lt;0),"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="50" t="s">
@@ -2117,7 +2142,7 @@
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C22" s="56">
         <v>-1</v>
@@ -2135,141 +2160,141 @@
         <v>-1</v>
       </c>
       <c r="H22" s="50" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="44" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C24" s="44" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E24" s="44"/>
       <c r="F24" s="44" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="G24" s="44"/>
       <c r="H24" s="44"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="57" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C25" s="58" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D25" s="59" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="E25" s="59"/>
       <c r="F25" s="60" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="G25" s="60"/>
       <c r="H25" s="60"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="57" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C26" s="58" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D26" s="59" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="E26" s="59"/>
       <c r="F26" s="60" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="G26" s="60"/>
       <c r="H26" s="60"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="57" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C27" s="58" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D27" s="59" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E27" s="59"/>
       <c r="F27" s="60" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="G27" s="60"/>
       <c r="H27" s="60"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="57" t="s">
-        <v>191</v>
-      </c>
-      <c r="C28" s="35" t="s">
-        <v>192</v>
+        <v>199</v>
+      </c>
+      <c r="C28" s="61" t="s">
+        <v>200</v>
       </c>
       <c r="D28" s="59" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E28" s="59"/>
       <c r="F28" s="60" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="G28" s="60"/>
       <c r="H28" s="60"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="57" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C29" s="58" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D29" s="59" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E29" s="59"/>
       <c r="F29" s="60" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="G29" s="60"/>
       <c r="H29" s="60"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="57" t="s">
-        <v>198</v>
-      </c>
-      <c r="C30" s="35" t="s">
-        <v>192</v>
+        <v>206</v>
+      </c>
+      <c r="C30" s="61" t="s">
+        <v>200</v>
       </c>
       <c r="D30" s="59" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="E30" s="59"/>
       <c r="F30" s="60" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="G30" s="60"/>
       <c r="H30" s="60"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="57" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C31" s="58" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D31" s="59" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E31" s="59"/>
       <c r="F31" s="60" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="G31" s="60"/>
       <c r="H31" s="60"/>
@@ -2279,22 +2304,22 @@
         <v>39</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D33" s="28"/>
       <c r="E33" s="28"/>
       <c r="F33" s="28"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="61" t="s">
-        <v>205</v>
-      </c>
-      <c r="C35" s="61"/>
-      <c r="D35" s="61"/>
-      <c r="E35" s="61"/>
-      <c r="F35" s="61"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="61"/>
+      <c r="B35" s="62" t="s">
+        <v>213</v>
+      </c>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="62"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -3444,7 +3469,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G20"/>
+  <dimension ref="B1:G25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -3756,47 +3781,122 @@
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="C19" s="33">
-        <f>C16</f>
-        <v>-100866.66666667</v>
-      </c>
-      <c r="D19" s="33">
-        <f>C19+D16</f>
-        <v>-80044.66666667</v>
-      </c>
-      <c r="E19" s="33">
-        <f>D19+E16</f>
-        <v>-5426.59066667</v>
-      </c>
-      <c r="F19" s="33">
-        <f>E19+F16</f>
-        <v>105122.5140366</v>
-      </c>
-      <c r="G19" s="33">
-        <f>F19+G16</f>
-        <v>127902.71097306</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="28" t="s">
+      <c r="C19" s="27">
+        <f>'Cash Flow &amp; DSCR'!C9</f>
+        <v>59064.39316601</v>
+      </c>
+      <c r="D19" s="27">
+        <f>'Cash Flow &amp; DSCR'!D9</f>
+        <v>59064.39316601</v>
+      </c>
+      <c r="E19" s="27">
+        <f>'Cash Flow &amp; DSCR'!E9</f>
+        <v>59064.39316601</v>
+      </c>
+      <c r="F19" s="27">
+        <f>'Cash Flow &amp; DSCR'!F9</f>
+        <v>59064.39316601</v>
+      </c>
+      <c r="G19" s="27">
+        <f>'Cash Flow &amp; DSCR'!G9</f>
+        <v>59064.39316601</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C21" s="30">
+        <f>C16-C19</f>
+        <v>-159931.05983267</v>
+      </c>
+      <c r="D21" s="30">
+        <f>D16-D19</f>
+        <v>-38242.39316601</v>
+      </c>
+      <c r="E21" s="31">
+        <f>E16-E19</f>
+        <v>15553.68283399</v>
+      </c>
+      <c r="F21" s="31">
+        <f>F16-F19</f>
+        <v>51484.71153726</v>
+      </c>
+      <c r="G21" s="30">
+        <f>G16-G19</f>
+        <v>-36284.19622955</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="32">
+        <f>IF(C10&gt;0,C21/C10,0)</f>
+        <v>-0.16073473</v>
+      </c>
+      <c r="D22" s="32">
+        <f>IF(D10&gt;0,D21/D10,0)</f>
+        <v>-0.02926236</v>
+      </c>
+      <c r="E22" s="32">
+        <f>IF(E10&gt;0,E21/E10,0)</f>
+        <v>0.0095034</v>
+      </c>
+      <c r="F22" s="32">
+        <f>IF(F10&gt;0,F21/F10,0)</f>
+        <v>0.02660954</v>
+      </c>
+      <c r="G22" s="32">
+        <f>IF(G10&gt;0,G21/G10,0)</f>
+        <v>-0.01690833</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="33">
+        <f>C21</f>
+        <v>-159931.05983267</v>
+      </c>
+      <c r="D24" s="33">
+        <f>C24+D21</f>
+        <v>-198173.45299868</v>
+      </c>
+      <c r="E24" s="33">
+        <f>D24+E21</f>
+        <v>-182619.77016469</v>
+      </c>
+      <c r="F24" s="33">
+        <f>E24+F21</f>
+        <v>-131135.05862743</v>
+      </c>
+      <c r="G24" s="33">
+        <f>F24+G21</f>
+        <v>-167419.25485698</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="34" t="s">
+      <c r="D25" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="34" t="s">
+      <c r="E25" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="G20" s="34" t="s">
+      <c r="F25" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" s="34" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3818,7 +3918,7 @@
     <tabColor rgb="FFD97706"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G14"/>
+  <dimension ref="B1:G16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -3828,7 +3928,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3855,177 +3955,227 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="C4" s="27">
+      <c r="B4" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="33">
+        <f>Assumptions!D57</f>
+        <v>75000</v>
+      </c>
+      <c r="D4" s="33">
+        <f>C16</f>
+        <v>-84931.05983267</v>
+      </c>
+      <c r="E4" s="33">
+        <f>D16</f>
+        <v>-123173.45299868</v>
+      </c>
+      <c r="F4" s="33">
+        <f>E16</f>
+        <v>-107619.77016469</v>
+      </c>
+      <c r="G4" s="33">
+        <f>F16</f>
+        <v>-56135.05862743</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="27">
         <f>'5-Year P&amp;L'!C16</f>
         <v>-100866.66666667</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D5" s="27">
         <f>'5-Year P&amp;L'!D16</f>
         <v>20822</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E5" s="27">
         <f>'5-Year P&amp;L'!E16</f>
         <v>74618.076</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F5" s="27">
         <f>'5-Year P&amp;L'!F16</f>
         <v>110549.10470327</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G5" s="27">
         <f>'5-Year P&amp;L'!G16</f>
         <v>22780.19693646</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="27">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="27">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D7" s="27">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E7" s="27">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F7" s="27">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G7" s="27">
         <f>Assumptions!D58</f>
         <v>25000</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="C7" s="27">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D8" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E8" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F8" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G8" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C8" s="29">
-        <f>C6+C7</f>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="29">
+        <f>C7+C8</f>
         <v>59064.39316601</v>
       </c>
-      <c r="D8" s="29">
-        <f>D6+D7</f>
+      <c r="D9" s="29">
+        <f>D7+D8</f>
         <v>59064.39316601</v>
       </c>
-      <c r="E8" s="29">
-        <f>E6+E7</f>
+      <c r="E9" s="29">
+        <f>E7+E8</f>
         <v>59064.39316601</v>
       </c>
-      <c r="F8" s="29">
-        <f>F6+F7</f>
+      <c r="F9" s="29">
+        <f>F7+F8</f>
         <v>59064.39316601</v>
       </c>
-      <c r="G8" s="29">
-        <f>G6+G7</f>
+      <c r="G9" s="29">
+        <f>G7+G8</f>
         <v>59064.39316601</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" s="36">
-        <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C11" s="35">
+        <f>IF(C9&gt;0,C5/C9,IF(C5&gt;0,99.9,0))</f>
         <v>-1.70774068</v>
       </c>
-      <c r="D10" s="36">
-        <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
+      <c r="D11" s="35">
+        <f>IF(D9&gt;0,D5/D9,IF(D5&gt;0,99.9,0))</f>
         <v>0.3525305</v>
       </c>
-      <c r="E10" s="37">
-        <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
+      <c r="E11" s="36">
+        <f>IF(E9&gt;0,E5/E9,IF(E5&gt;0,99.9,0))</f>
         <v>1.26333434</v>
       </c>
-      <c r="F10" s="37">
-        <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
+      <c r="F11" s="36">
+        <f>IF(F9&gt;0,F5/F9,IF(F5&gt;0,99.9,0))</f>
         <v>1.87167088</v>
       </c>
-      <c r="G10" s="36">
-        <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
+      <c r="G11" s="35">
+        <f>IF(G9&gt;0,G5/G9,IF(G5&gt;0,99.9,0))</f>
         <v>0.38568409</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12" s="27">
-        <f>C4-C8</f>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="27">
+        <f>C5-C9</f>
         <v>-159931.05983267</v>
       </c>
-      <c r="D12" s="27">
-        <f>D4-D8</f>
+      <c r="D13" s="27">
+        <f>D5-D9</f>
         <v>-38242.39316601</v>
       </c>
-      <c r="E12" s="27">
-        <f>E4-E8</f>
+      <c r="E13" s="27">
+        <f>E5-E9</f>
         <v>15553.68283399</v>
       </c>
-      <c r="F12" s="27">
-        <f>F4-F8</f>
+      <c r="F13" s="27">
+        <f>F5-F9</f>
         <v>51484.71153726</v>
       </c>
-      <c r="G12" s="27">
-        <f>G4-G8</f>
+      <c r="G13" s="27">
+        <f>G5-G9</f>
         <v>-36284.19622955</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="38">
-        <f>Assumptions!D57+C12</f>
+        <v>138</v>
+      </c>
+      <c r="C14" s="33">
+        <f>C5-C9</f>
+        <v>-159931.05983267</v>
+      </c>
+      <c r="D14" s="33">
+        <f>D5-D9</f>
+        <v>-38242.39316601</v>
+      </c>
+      <c r="E14" s="33">
+        <f>E5-E9</f>
+        <v>15553.68283399</v>
+      </c>
+      <c r="F14" s="33">
+        <f>F5-F9</f>
+        <v>51484.71153726</v>
+      </c>
+      <c r="G14" s="33">
+        <f>G5-G9</f>
+        <v>-36284.19622955</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="30">
+        <f>C4+C14</f>
         <v>-84931.05983267</v>
       </c>
-      <c r="D14" s="38">
-        <f>C14+D12</f>
+      <c r="D16" s="30">
+        <f>D4+D14</f>
         <v>-123173.45299868</v>
       </c>
-      <c r="E14" s="38">
-        <f>D14+E12</f>
+      <c r="E16" s="30">
+        <f>E4+E14</f>
         <v>-107619.77016469</v>
       </c>
-      <c r="F14" s="38">
-        <f>E14+F12</f>
+      <c r="F16" s="30">
+        <f>F4+F14</f>
         <v>-56135.05862743</v>
       </c>
-      <c r="G14" s="38">
-        <f>F14+G12</f>
+      <c r="G16" s="30">
+        <f>G4+G14</f>
         <v>-92419.25485698</v>
       </c>
     </row>
@@ -4057,7 +4207,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4085,7 +4235,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C4" s="26">
         <f>Drivers!C12</f>
@@ -4110,7 +4260,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="25" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C5" s="26">
         <f>Assumptions!D35</f>
@@ -4135,25 +4285,25 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="39">
+        <v>143</v>
+      </c>
+      <c r="C6" s="37">
         <f>C4+C5</f>
         <v>14</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="37">
         <f>D4+D5</f>
         <v>16</v>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="37">
         <f>E4+E5</f>
         <v>19</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="37">
         <f>F4+F5</f>
         <v>21</v>
       </c>
-      <c r="G6" s="39">
+      <c r="G6" s="37">
         <f>G4+G5</f>
         <v>23</v>
       </c>
@@ -4186,13 +4336,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="25" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C3" s="27">
         <f>Assumptions!D59</f>
@@ -4201,7 +4351,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C4" s="32">
         <f>Assumptions!D60</f>
@@ -4219,7 +4369,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C6" s="33">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -4228,10 +4378,10 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="C8" s="36">
-        <f>'Cash Flow &amp; DSCR'!C10</f>
+        <v>148</v>
+      </c>
+      <c r="C8" s="35">
+        <f>'Cash Flow &amp; DSCR'!C11</f>
         <v>-1.70774068</v>
       </c>
     </row>
@@ -4253,7 +4403,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C12"/>
+  <dimension ref="B1:C20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4263,7 +4413,7 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C1" s="13"/>
     </row>
@@ -4296,7 +4446,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C6" s="25">
         <f>Assumptions!D8</f>
@@ -4314,7 +4464,7 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C9" s="27">
         <f>Drivers!G10</f>
@@ -4323,23 +4473,83 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="C10" s="40">
+        <v>152</v>
+      </c>
+      <c r="C10" s="38">
         <f>'5-Year P&amp;L'!G16</f>
         <v>22780.19693646</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="C12" s="12"/>
+    <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" s="23"/>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="40">
+        <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
+        <v>-0.01690833</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="32">
+        <f>IF(Drivers!G10&gt;0,Drivers!G16/Drivers!G10,0)</f>
+        <v>0.66686369</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C15" s="27">
+        <f>IF(Assumptions!D16&gt;0,Drivers!G10/Assumptions!D16,0)</f>
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="27">
+        <f>IF(Assumptions!D16&gt;0,('5-Year P&amp;L'!G12+'5-Year P&amp;L'!G13)/Assumptions!D16,0)</f>
+        <v>10616</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" s="35">
+        <f>'Cash Flow &amp; DSCR'!C11</f>
+        <v>-1.70774068</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" s="35">
+        <f>'Cash Flow &amp; DSCR'!G11</f>
+        <v>0.38568409</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C20" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -28,7 +28,7 @@
     <t>Heritage Academy</t>
   </si>
   <si>
-    <t>Generated March 26, 2026 · nonprofit_501c3</t>
+    <t>Generated March 27, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -142,7 +142,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
+    <t>Generated March 27, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="217">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -502,6 +502,9 @@
     <t>DSCR (Year 5)</t>
   </si>
   <si>
+    <t>Days Cash on Hand (Year 1)</t>
+  </si>
+  <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -575,6 +578,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -905,7 +914,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -983,6 +992,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1748,7 +1760,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1760,7 +1772,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1781,37 +1793,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="41" t="s">
-        <v>162</v>
-      </c>
-      <c r="D4" s="42" t="s">
+      <c r="B4" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="D4" s="43" t="s">
         <v>164</v>
       </c>
+      <c r="F4" s="44" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="44" t="s">
-        <v>165</v>
-      </c>
-      <c r="C6" s="45" t="s">
+      <c r="B6" s="45" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="45" t="s">
+      <c r="E6" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="45" t="s">
+      <c r="F6" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="45" t="s">
+      <c r="G6" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="45" t="s">
-        <v>166</v>
+      <c r="H6" s="46" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1836,7 +1848,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C8" s="27">
         <v>995000</v>
@@ -1856,7 +1868,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C9" s="27">
         <v>824466.6666666666</v>
@@ -1876,7 +1888,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C10" s="27">
         <v>271400</v>
@@ -1896,7 +1908,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C11" s="27">
         <v>59064.39316600799</v>
@@ -1958,375 +1970,396 @@
       <c r="B14" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="46">
+      <c r="C14" s="47">
         <v>-0.1607347335001754</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="47">
         <v>-0.029262360098867523</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="48">
         <v>0.009503395504016587</v>
       </c>
-      <c r="F14" s="47">
+      <c r="F14" s="48">
         <v>0.026609542752265323</v>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="47">
         <v>-0.016908329359328268</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="C15" s="48">
+        <v>172</v>
+      </c>
+      <c r="C15" s="49">
         <v>9950</v>
       </c>
-      <c r="D15" s="49">
+      <c r="D15" s="50">
         <v>10052.923076923076</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="50">
         <v>10229.03</v>
       </c>
-      <c r="F15" s="49">
+      <c r="F15" s="50">
         <v>10458.493805405406</v>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="50">
         <v>10729.681052000002</v>
       </c>
-      <c r="H15" s="50" t="s">
-        <v>172</v>
+      <c r="H15" s="51" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C16" s="46">
+        <v>174</v>
+      </c>
+      <c r="C16" s="47">
         <v>0.8286097152428811</v>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="47">
         <v>0.7280806194906954</v>
       </c>
-      <c r="E16" s="46">
+      <c r="E16" s="47">
         <v>0.6954065537005952</v>
       </c>
-      <c r="F16" s="46">
+      <c r="F16" s="47">
         <v>0.6619844970624266</v>
       </c>
-      <c r="G16" s="46">
+      <c r="G16" s="47">
         <v>0.6668636877551553</v>
       </c>
-      <c r="H16" s="50" t="s">
-        <v>174</v>
+      <c r="H16" s="51" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="C17" s="51">
+        <v>176</v>
+      </c>
+      <c r="C17" s="52">
         <v>0.1370854271356784</v>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="52">
         <v>0.10750183643486777</v>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="52">
         <v>0.08841671693210401</v>
       </c>
-      <c r="F17" s="51">
+      <c r="F17" s="52">
         <v>0.07703448305026303</v>
       </c>
-      <c r="G17" s="51">
+      <c r="G17" s="52">
         <v>0.0715395923420222</v>
       </c>
-      <c r="H17" s="50" t="s">
-        <v>176</v>
+      <c r="H17" s="51" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="46">
+      <c r="C18" s="47">
         <v>-0.10137353433835843</v>
       </c>
-      <c r="D18" s="47">
+      <c r="D18" s="48">
         <v>0.015932602840352597</v>
       </c>
-      <c r="E18" s="47">
+      <c r="E18" s="48">
         <v>0.04559210159712117</v>
       </c>
-      <c r="F18" s="47">
+      <c r="F18" s="48">
         <v>0.057136595311355426</v>
       </c>
-      <c r="G18" s="47">
+      <c r="G18" s="48">
         <v>0.010615505170216507</v>
       </c>
-      <c r="H18" s="50" t="s">
-        <v>177</v>
+      <c r="H18" s="51" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="C19" s="52">
+        <v>179</v>
+      </c>
+      <c r="C19" s="53">
         <v>3</v>
       </c>
-      <c r="D19" s="52">
+      <c r="D19" s="53">
         <v>3</v>
       </c>
-      <c r="E19" s="52">
+      <c r="E19" s="53">
         <v>3</v>
       </c>
-      <c r="F19" s="52">
+      <c r="F19" s="53">
         <v>3</v>
       </c>
-      <c r="G19" s="52">
+      <c r="G19" s="53">
         <v>3</v>
       </c>
-      <c r="H19" s="50" t="s">
-        <v>179</v>
+      <c r="H19" s="51" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="C20" s="53">
+        <v>181</v>
+      </c>
+      <c r="C20" s="54">
         <v>-1.7077406752181137</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="54">
         <v>0.35253049906865414</v>
       </c>
-      <c r="E20" s="54">
+      <c r="E20" s="55">
         <v>1.2633343373269994</v>
       </c>
-      <c r="F20" s="54">
+      <c r="F20" s="55">
         <v>1.871670879484945</v>
       </c>
-      <c r="G20" s="53">
+      <c r="G20" s="54">
         <v>0.38568409350163607</v>
       </c>
-      <c r="H20" s="50" t="s">
-        <v>181</v>
+      <c r="H20" s="51" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="C21" s="55" t="str">
+        <v>183</v>
+      </c>
+      <c r="C21" s="56" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="55" t="str">
+      <c r="D21" s="56" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="55" t="str">
+      <c r="E21" s="56" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="55" t="str">
+      <c r="F21" s="56" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="55" t="str">
+      <c r="G21" s="56" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="50" t="s">
+      <c r="H21" s="51" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="C22" s="56">
+        <v>184</v>
+      </c>
+      <c r="C22" s="57">
         <v>-1</v>
       </c>
-      <c r="D22" s="56">
+      <c r="D22" s="57">
         <v>-1</v>
       </c>
-      <c r="E22" s="56">
+      <c r="E22" s="57">
         <v>-1</v>
       </c>
-      <c r="F22" s="56">
+      <c r="F22" s="57">
         <v>0</v>
       </c>
-      <c r="G22" s="56">
+      <c r="G22" s="57">
         <v>-1</v>
       </c>
-      <c r="H22" s="50" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="44" t="s">
+      <c r="H22" s="51" t="s">
         <v>185</v>
       </c>
-      <c r="C24" s="44" t="s">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="D24" s="44" t="s">
+      <c r="C23" s="57">
+        <v>0</v>
+      </c>
+      <c r="D23" s="57">
+        <v>0</v>
+      </c>
+      <c r="E23" s="57">
+        <v>0</v>
+      </c>
+      <c r="F23" s="57">
+        <v>0</v>
+      </c>
+      <c r="G23" s="57">
+        <v>0</v>
+      </c>
+      <c r="H23" s="51" t="s">
         <v>187</v>
       </c>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="45" t="s">
         <v>188</v>
       </c>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="57" t="s">
+      <c r="C25" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="D25" s="45" t="s">
         <v>190</v>
       </c>
-      <c r="D25" s="59" t="s">
+      <c r="E25" s="45"/>
+      <c r="F25" s="45" t="s">
         <v>191</v>
       </c>
-      <c r="E25" s="59"/>
-      <c r="F25" s="60" t="s">
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="58" t="s">
         <v>192</v>
       </c>
-      <c r="G25" s="60"/>
-      <c r="H25" s="60"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="57" t="s">
+      <c r="C26" s="59" t="s">
         <v>193</v>
       </c>
-      <c r="C26" s="58" t="s">
-        <v>190</v>
-      </c>
-      <c r="D26" s="59" t="s">
+      <c r="D26" s="60" t="s">
         <v>194</v>
       </c>
-      <c r="E26" s="59"/>
-      <c r="F26" s="60" t="s">
+      <c r="E26" s="60"/>
+      <c r="F26" s="61" t="s">
         <v>195</v>
       </c>
-      <c r="G26" s="60"/>
-      <c r="H26" s="60"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="C27" s="58" t="s">
-        <v>190</v>
-      </c>
-      <c r="D27" s="59" t="s">
+      <c r="C27" s="59" t="s">
+        <v>193</v>
+      </c>
+      <c r="D27" s="60" t="s">
         <v>197</v>
       </c>
-      <c r="E27" s="59"/>
-      <c r="F27" s="60" t="s">
+      <c r="E27" s="60"/>
+      <c r="F27" s="61" t="s">
         <v>198</v>
       </c>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="61"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="58" t="s">
         <v>199</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="59" t="s">
+        <v>193</v>
+      </c>
+      <c r="D28" s="60" t="s">
         <v>200</v>
       </c>
-      <c r="D28" s="59" t="s">
+      <c r="E28" s="60"/>
+      <c r="F28" s="61" t="s">
         <v>201</v>
       </c>
-      <c r="E28" s="59"/>
-      <c r="F28" s="60" t="s">
+      <c r="G28" s="61"/>
+      <c r="H28" s="61"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="58" t="s">
         <v>202</v>
       </c>
-      <c r="G28" s="60"/>
-      <c r="H28" s="60"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="57" t="s">
+      <c r="C29" s="62" t="s">
         <v>203</v>
       </c>
-      <c r="C29" s="58" t="s">
-        <v>190</v>
-      </c>
-      <c r="D29" s="59" t="s">
+      <c r="D29" s="60" t="s">
         <v>204</v>
       </c>
-      <c r="E29" s="59"/>
-      <c r="F29" s="60" t="s">
+      <c r="E29" s="60"/>
+      <c r="F29" s="61" t="s">
         <v>205</v>
       </c>
-      <c r="G29" s="60"/>
-      <c r="H29" s="60"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="61"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="57" t="s">
+      <c r="B30" s="58" t="s">
         <v>206</v>
       </c>
-      <c r="C30" s="61" t="s">
-        <v>200</v>
-      </c>
-      <c r="D30" s="59" t="s">
+      <c r="C30" s="59" t="s">
+        <v>193</v>
+      </c>
+      <c r="D30" s="60" t="s">
         <v>207</v>
       </c>
-      <c r="E30" s="59"/>
-      <c r="F30" s="60" t="s">
+      <c r="E30" s="60"/>
+      <c r="F30" s="61" t="s">
         <v>208</v>
       </c>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="57" t="s">
+      <c r="B31" s="58" t="s">
         <v>209</v>
       </c>
-      <c r="C31" s="58" t="s">
-        <v>190</v>
-      </c>
-      <c r="D31" s="59" t="s">
+      <c r="C31" s="62" t="s">
+        <v>203</v>
+      </c>
+      <c r="D31" s="60" t="s">
         <v>210</v>
       </c>
-      <c r="E31" s="59"/>
-      <c r="F31" s="60" t="s">
+      <c r="E31" s="60"/>
+      <c r="F31" s="61" t="s">
         <v>211</v>
       </c>
-      <c r="G31" s="60"/>
-      <c r="H31" s="60"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="57" t="s">
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="58" t="s">
+        <v>212</v>
+      </c>
+      <c r="C32" s="59" t="s">
+        <v>193</v>
+      </c>
+      <c r="D32" s="60" t="s">
+        <v>213</v>
+      </c>
+      <c r="E32" s="60"/>
+      <c r="F32" s="61" t="s">
+        <v>214</v>
+      </c>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="62" t="s">
-        <v>213</v>
-      </c>
-      <c r="C35" s="62"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
+      <c r="C34" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="63" t="s">
+        <v>216</v>
+      </c>
+      <c r="C36" s="63"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -2341,8 +2374,10 @@
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4403,7 +4438,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C20"/>
+  <dimension ref="B1:C21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4540,16 +4575,24 @@
         <v>0.38568409</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="12" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="C20" s="12"/>
+      <c r="C19" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="222">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -542,6 +542,21 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -914,7 +929,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1017,6 +1032,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1760,7 +1778,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H36"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2009,365 +2027,440 @@
         <v>173</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="47">
-        <v>0.8286097152428811</v>
-      </c>
-      <c r="D16" s="47">
-        <v>0.7280806194906954</v>
-      </c>
-      <c r="E16" s="47">
-        <v>0.6954065537005952</v>
-      </c>
-      <c r="F16" s="47">
-        <v>0.6619844970624266</v>
-      </c>
-      <c r="G16" s="47">
-        <v>0.6668636877551553</v>
-      </c>
-      <c r="H16" s="51" t="s">
+      <c r="C16" s="33">
+        <v>11549.310598326745</v>
+      </c>
+      <c r="D16" s="33">
+        <v>10347.095332046214</v>
+      </c>
+      <c r="E16" s="33">
+        <v>10131.819482287548</v>
+      </c>
+      <c r="F16" s="33">
+        <v>10180.198067366167</v>
+      </c>
+      <c r="G16" s="33">
+        <v>10911.102033147761</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="25" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="28" t="s">
+      <c r="C17" s="27">
+        <v>600</v>
+      </c>
+      <c r="D17" s="27">
+        <v>803.4</v>
+      </c>
+      <c r="E17" s="27">
+        <v>1075.7526</v>
+      </c>
+      <c r="F17" s="27">
+        <v>1440.4327313999997</v>
+      </c>
+      <c r="G17" s="27">
+        <v>1928.7394273446</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="C17" s="52">
-        <v>0.1370854271356784</v>
-      </c>
-      <c r="D17" s="52">
-        <v>0.10750183643486777</v>
-      </c>
-      <c r="E17" s="52">
-        <v>0.08841671693210401</v>
-      </c>
-      <c r="F17" s="52">
-        <v>0.07703448305026303</v>
-      </c>
-      <c r="G17" s="52">
-        <v>0.0715395923420222</v>
-      </c>
-      <c r="H17" s="51" t="s">
+      <c r="C18" s="50">
+        <v>1364</v>
+      </c>
+      <c r="D18" s="50">
+        <v>1080.7076923076922</v>
+      </c>
+      <c r="E18" s="50">
+        <v>904.4172499999999</v>
+      </c>
+      <c r="F18" s="50">
+        <v>805.6646637837837</v>
+      </c>
+      <c r="G18" s="50">
+        <v>767.5970084200001</v>
+      </c>
+      <c r="H18" s="51" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" s="47">
-        <v>-0.10137353433835843</v>
-      </c>
-      <c r="D18" s="48">
-        <v>0.015932602840352597</v>
-      </c>
-      <c r="E18" s="48">
-        <v>0.04559210159712117</v>
-      </c>
-      <c r="F18" s="48">
-        <v>0.057136595311355426</v>
-      </c>
-      <c r="G18" s="48">
-        <v>0.010615505170216507</v>
-      </c>
-      <c r="H18" s="51" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="28" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="C19" s="53">
-        <v>3</v>
-      </c>
-      <c r="D19" s="53">
-        <v>3</v>
-      </c>
-      <c r="E19" s="53">
-        <v>3</v>
-      </c>
-      <c r="F19" s="53">
-        <v>3</v>
-      </c>
-      <c r="G19" s="53">
-        <v>3</v>
-      </c>
-      <c r="H19" s="51" t="s">
-        <v>180</v>
+      <c r="C19" s="52">
+        <v>-1599.310598326745</v>
+      </c>
+      <c r="D19" s="52">
+        <v>-294.17225512313837</v>
+      </c>
+      <c r="E19" s="38">
+        <v>97.2105177124508</v>
+      </c>
+      <c r="F19" s="38">
+        <v>278.2957380392372</v>
+      </c>
+      <c r="G19" s="52">
+        <v>-181.42098114775985</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="C20" s="54">
-        <v>-1.7077406752181137</v>
-      </c>
-      <c r="D20" s="54">
-        <v>0.35253049906865414</v>
-      </c>
-      <c r="E20" s="55">
-        <v>1.2633343373269994</v>
-      </c>
-      <c r="F20" s="55">
-        <v>1.871670879484945</v>
-      </c>
-      <c r="G20" s="54">
-        <v>0.38568409350163607</v>
+        <v>179</v>
+      </c>
+      <c r="C20" s="47">
+        <v>0.8286097152428811</v>
+      </c>
+      <c r="D20" s="47">
+        <v>0.7280806194906954</v>
+      </c>
+      <c r="E20" s="47">
+        <v>0.6954065537005952</v>
+      </c>
+      <c r="F20" s="47">
+        <v>0.6619844970624266</v>
+      </c>
+      <c r="G20" s="47">
+        <v>0.6668636877551553</v>
       </c>
       <c r="H20" s="51" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="C21" s="53">
+        <v>0.1370854271356784</v>
+      </c>
+      <c r="D21" s="53">
+        <v>0.10750183643486777</v>
+      </c>
+      <c r="E21" s="53">
+        <v>0.08841671693210401</v>
+      </c>
+      <c r="F21" s="53">
+        <v>0.07703448305026303</v>
+      </c>
+      <c r="G21" s="53">
+        <v>0.0715395923420222</v>
+      </c>
+      <c r="H21" s="51" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="47">
+        <v>-0.10137353433835843</v>
+      </c>
+      <c r="D22" s="48">
+        <v>0.015932602840352597</v>
+      </c>
+      <c r="E22" s="48">
+        <v>0.04559210159712117</v>
+      </c>
+      <c r="F22" s="48">
+        <v>0.057136595311355426</v>
+      </c>
+      <c r="G22" s="48">
+        <v>0.010615505170216507</v>
+      </c>
+      <c r="H22" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="C21" s="56" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="C23" s="54">
+        <v>3</v>
+      </c>
+      <c r="D23" s="54">
+        <v>3</v>
+      </c>
+      <c r="E23" s="54">
+        <v>3</v>
+      </c>
+      <c r="F23" s="54">
+        <v>3</v>
+      </c>
+      <c r="G23" s="54">
+        <v>3</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" s="55">
+        <v>-1.7077406752181137</v>
+      </c>
+      <c r="D24" s="55">
+        <v>0.35253049906865414</v>
+      </c>
+      <c r="E24" s="56">
+        <v>1.2633343373269994</v>
+      </c>
+      <c r="F24" s="56">
+        <v>1.871670879484945</v>
+      </c>
+      <c r="G24" s="55">
+        <v>0.38568409350163607</v>
+      </c>
+      <c r="H24" s="51" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="C25" s="57" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="56" t="str">
+      <c r="D25" s="57" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="56" t="str">
+      <c r="E25" s="57" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="56" t="str">
+      <c r="F25" s="57" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="56" t="str">
+      <c r="G25" s="57" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="51" t="s">
+      <c r="H25" s="51" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="C22" s="57">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" s="58">
         <v>-1</v>
       </c>
-      <c r="D22" s="57">
+      <c r="D26" s="58">
         <v>-1</v>
       </c>
-      <c r="E22" s="57">
+      <c r="E26" s="58">
         <v>-1</v>
       </c>
-      <c r="F22" s="57">
+      <c r="F26" s="58">
         <v>0</v>
       </c>
-      <c r="G22" s="57">
+      <c r="G26" s="58">
         <v>-1</v>
       </c>
-      <c r="H22" s="51" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="C23" s="57">
+      <c r="H26" s="51" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="C27" s="58">
         <v>0</v>
       </c>
-      <c r="D23" s="57">
+      <c r="D27" s="58">
         <v>0</v>
       </c>
-      <c r="E23" s="57">
+      <c r="E27" s="58">
         <v>0</v>
       </c>
-      <c r="F23" s="57">
+      <c r="F27" s="58">
         <v>0</v>
       </c>
-      <c r="G23" s="57">
+      <c r="G27" s="58">
         <v>0</v>
       </c>
-      <c r="H23" s="51" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="C25" s="45" t="s">
-        <v>189</v>
-      </c>
-      <c r="D25" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45" t="s">
-        <v>191</v>
-      </c>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="58" t="s">
+      <c r="H27" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="C26" s="59" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="45" t="s">
         <v>193</v>
       </c>
-      <c r="D26" s="60" t="s">
+      <c r="C29" s="45" t="s">
         <v>194</v>
       </c>
-      <c r="E26" s="60"/>
-      <c r="F26" s="61" t="s">
+      <c r="D29" s="45" t="s">
         <v>195</v>
       </c>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="58" t="s">
+      <c r="E29" s="45"/>
+      <c r="F29" s="45" t="s">
         <v>196</v>
       </c>
-      <c r="C27" s="59" t="s">
-        <v>193</v>
-      </c>
-      <c r="D27" s="60" t="s">
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="59" t="s">
         <v>197</v>
       </c>
-      <c r="E27" s="60"/>
-      <c r="F27" s="61" t="s">
+      <c r="C30" s="60" t="s">
         <v>198</v>
       </c>
-      <c r="G27" s="61"/>
-      <c r="H27" s="61"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="58" t="s">
+      <c r="D30" s="61" t="s">
         <v>199</v>
       </c>
-      <c r="C28" s="59" t="s">
-        <v>193</v>
-      </c>
-      <c r="D28" s="60" t="s">
+      <c r="E30" s="61"/>
+      <c r="F30" s="62" t="s">
         <v>200</v>
       </c>
-      <c r="E28" s="60"/>
-      <c r="F28" s="61" t="s">
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="59" t="s">
         <v>201</v>
       </c>
-      <c r="G28" s="61"/>
-      <c r="H28" s="61"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="58" t="s">
+      <c r="C31" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="D31" s="61" t="s">
         <v>202</v>
       </c>
-      <c r="C29" s="62" t="s">
+      <c r="E31" s="61"/>
+      <c r="F31" s="62" t="s">
         <v>203</v>
       </c>
-      <c r="D29" s="60" t="s">
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="59" t="s">
         <v>204</v>
       </c>
-      <c r="E29" s="60"/>
-      <c r="F29" s="61" t="s">
+      <c r="C32" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="D32" s="61" t="s">
         <v>205</v>
       </c>
-      <c r="G29" s="61"/>
-      <c r="H29" s="61"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="58" t="s">
+      <c r="E32" s="61"/>
+      <c r="F32" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="C30" s="59" t="s">
-        <v>193</v>
-      </c>
-      <c r="D30" s="60" t="s">
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="59" t="s">
         <v>207</v>
       </c>
-      <c r="E30" s="60"/>
-      <c r="F30" s="61" t="s">
+      <c r="C33" s="63" t="s">
         <v>208</v>
       </c>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="58" t="s">
+      <c r="D33" s="61" t="s">
         <v>209</v>
       </c>
-      <c r="C31" s="62" t="s">
-        <v>203</v>
-      </c>
-      <c r="D31" s="60" t="s">
+      <c r="E33" s="61"/>
+      <c r="F33" s="62" t="s">
         <v>210</v>
       </c>
-      <c r="E31" s="60"/>
-      <c r="F31" s="61" t="s">
+      <c r="G33" s="62"/>
+      <c r="H33" s="62"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="59" t="s">
         <v>211</v>
       </c>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="58" t="s">
+      <c r="C34" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="D34" s="61" t="s">
         <v>212</v>
       </c>
-      <c r="C32" s="59" t="s">
-        <v>193</v>
-      </c>
-      <c r="D32" s="60" t="s">
+      <c r="E34" s="61"/>
+      <c r="F34" s="62" t="s">
         <v>213</v>
       </c>
-      <c r="E32" s="60"/>
-      <c r="F32" s="61" t="s">
+      <c r="G34" s="62"/>
+      <c r="H34" s="62"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="59" t="s">
         <v>214</v>
       </c>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="58" t="s">
+      <c r="C35" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="D35" s="61" t="s">
+        <v>215</v>
+      </c>
+      <c r="E35" s="61"/>
+      <c r="F35" s="62" t="s">
+        <v>216</v>
+      </c>
+      <c r="G35" s="62"/>
+      <c r="H35" s="62"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="59" t="s">
+        <v>217</v>
+      </c>
+      <c r="C36" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="D36" s="61" t="s">
+        <v>218</v>
+      </c>
+      <c r="E36" s="61"/>
+      <c r="F36" s="62" t="s">
+        <v>219</v>
+      </c>
+      <c r="G36" s="62"/>
+      <c r="H36" s="62"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="28" t="s">
-        <v>215</v>
-      </c>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="63" t="s">
-        <v>216</v>
-      </c>
-      <c r="C36" s="63"/>
-      <c r="D36" s="63"/>
-      <c r="E36" s="63"/>
-      <c r="F36" s="63"/>
-      <c r="G36" s="63"/>
-      <c r="H36" s="63"/>
+      <c r="C38" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="64" t="s">
+        <v>221</v>
+      </c>
+      <c r="C40" s="64"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
@@ -2376,8 +2469,16 @@
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2423,48 +2524,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="214">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -502,9 +502,6 @@
     <t>DSCR (Year 5)</t>
   </si>
   <si>
-    <t>Days Cash on Hand (Year 1)</t>
-  </si>
-  <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -544,21 +541,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t>Cost per Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -593,12 +575,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>Days Cash on Hand</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -929,7 +905,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1009,9 +985,6 @@
     <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1032,9 +1005,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="166" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1778,7 +1748,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1790,7 +1760,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1811,37 +1781,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="D4" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="F4" s="43" t="s">
         <v>164</v>
       </c>
-      <c r="F4" s="44" t="s">
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="44" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="45" t="s">
+      <c r="C6" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="45" t="s">
         <v>166</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" s="46" t="s">
-        <v>98</v>
-      </c>
-      <c r="F6" s="46" t="s">
-        <v>99</v>
-      </c>
-      <c r="G6" s="46" t="s">
-        <v>100</v>
-      </c>
-      <c r="H6" s="46" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1866,7 +1836,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C8" s="27">
         <v>995000</v>
@@ -1886,7 +1856,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C9" s="27">
         <v>824466.6666666666</v>
@@ -1906,7 +1876,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C10" s="27">
         <v>271400</v>
@@ -1926,7 +1896,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C11" s="27">
         <v>59064.39316600799</v>
@@ -1988,497 +1958,391 @@
       <c r="B14" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="46">
         <v>-0.1607347335001754</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="46">
         <v>-0.029262360098867523</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="47">
         <v>0.009503395504016587</v>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="47">
         <v>0.026609542752265323</v>
       </c>
-      <c r="G14" s="47">
+      <c r="G14" s="46">
         <v>-0.016908329359328268</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" s="48">
+        <v>9950</v>
+      </c>
+      <c r="D15" s="49">
+        <v>10052.923076923076</v>
+      </c>
+      <c r="E15" s="49">
+        <v>10229.03</v>
+      </c>
+      <c r="F15" s="49">
+        <v>10458.493805405406</v>
+      </c>
+      <c r="G15" s="49">
+        <v>10729.681052000002</v>
+      </c>
+      <c r="H15" s="50" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="49">
-        <v>9950</v>
-      </c>
-      <c r="D15" s="50">
-        <v>10052.923076923076</v>
-      </c>
-      <c r="E15" s="50">
-        <v>10229.03</v>
-      </c>
-      <c r="F15" s="50">
-        <v>10458.493805405406</v>
-      </c>
-      <c r="G15" s="50">
-        <v>10729.681052000002</v>
-      </c>
-      <c r="H15" s="51" t="s">
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="28" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="28" t="s">
+      <c r="C16" s="46">
+        <v>0.8286097152428811</v>
+      </c>
+      <c r="D16" s="46">
+        <v>0.7280806194906954</v>
+      </c>
+      <c r="E16" s="46">
+        <v>0.6954065537005952</v>
+      </c>
+      <c r="F16" s="46">
+        <v>0.6619844970624266</v>
+      </c>
+      <c r="G16" s="46">
+        <v>0.6668636877551553</v>
+      </c>
+      <c r="H16" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="33">
-        <v>11549.310598326745</v>
-      </c>
-      <c r="D16" s="33">
-        <v>10347.095332046214</v>
-      </c>
-      <c r="E16" s="33">
-        <v>10131.819482287548</v>
-      </c>
-      <c r="F16" s="33">
-        <v>10180.198067366167</v>
-      </c>
-      <c r="G16" s="33">
-        <v>10911.102033147761</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="25" t="s">
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="C17" s="27">
-        <v>600</v>
-      </c>
-      <c r="D17" s="27">
-        <v>803.4</v>
-      </c>
-      <c r="E17" s="27">
-        <v>1075.7526</v>
-      </c>
-      <c r="F17" s="27">
-        <v>1440.4327313999997</v>
-      </c>
-      <c r="G17" s="27">
-        <v>1928.7394273446</v>
+      <c r="C17" s="51">
+        <v>0.1370854271356784</v>
+      </c>
+      <c r="D17" s="51">
+        <v>0.10750183643486777</v>
+      </c>
+      <c r="E17" s="51">
+        <v>0.08841671693210401</v>
+      </c>
+      <c r="F17" s="51">
+        <v>0.07703448305026303</v>
+      </c>
+      <c r="G17" s="51">
+        <v>0.0715395923420222</v>
+      </c>
+      <c r="H17" s="50" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="C18" s="50">
-        <v>1364</v>
-      </c>
-      <c r="D18" s="50">
-        <v>1080.7076923076922</v>
-      </c>
-      <c r="E18" s="50">
-        <v>904.4172499999999</v>
-      </c>
-      <c r="F18" s="50">
-        <v>805.6646637837837</v>
-      </c>
-      <c r="G18" s="50">
-        <v>767.5970084200001</v>
-      </c>
-      <c r="H18" s="51" t="s">
+      <c r="B18" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="46">
+        <v>-0.10137353433835843</v>
+      </c>
+      <c r="D18" s="47">
+        <v>0.015932602840352597</v>
+      </c>
+      <c r="E18" s="47">
+        <v>0.04559210159712117</v>
+      </c>
+      <c r="F18" s="47">
+        <v>0.057136595311355426</v>
+      </c>
+      <c r="G18" s="47">
+        <v>0.010615505170216507</v>
+      </c>
+      <c r="H18" s="50" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
         <v>178</v>
       </c>
       <c r="C19" s="52">
-        <v>-1599.310598326745</v>
+        <v>3</v>
       </c>
       <c r="D19" s="52">
-        <v>-294.17225512313837</v>
-      </c>
-      <c r="E19" s="38">
-        <v>97.2105177124508</v>
-      </c>
-      <c r="F19" s="38">
-        <v>278.2957380392372</v>
+        <v>3</v>
+      </c>
+      <c r="E19" s="52">
+        <v>3</v>
+      </c>
+      <c r="F19" s="52">
+        <v>3</v>
       </c>
       <c r="G19" s="52">
-        <v>-181.42098114775985</v>
+        <v>3</v>
+      </c>
+      <c r="H19" s="50" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="C20" s="47">
-        <v>0.8286097152428811</v>
-      </c>
-      <c r="D20" s="47">
-        <v>0.7280806194906954</v>
-      </c>
-      <c r="E20" s="47">
-        <v>0.6954065537005952</v>
-      </c>
-      <c r="F20" s="47">
-        <v>0.6619844970624266</v>
-      </c>
-      <c r="G20" s="47">
-        <v>0.6668636877551553</v>
-      </c>
-      <c r="H20" s="51" t="s">
         <v>180</v>
+      </c>
+      <c r="C20" s="53">
+        <v>-1.7077406752181137</v>
+      </c>
+      <c r="D20" s="53">
+        <v>0.35253049906865414</v>
+      </c>
+      <c r="E20" s="54">
+        <v>1.2633343373269994</v>
+      </c>
+      <c r="F20" s="54">
+        <v>1.871670879484945</v>
+      </c>
+      <c r="G20" s="53">
+        <v>0.38568409350163607</v>
+      </c>
+      <c r="H20" s="50" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="C21" s="53">
-        <v>0.1370854271356784</v>
-      </c>
-      <c r="D21" s="53">
-        <v>0.10750183643486777</v>
-      </c>
-      <c r="E21" s="53">
-        <v>0.08841671693210401</v>
-      </c>
-      <c r="F21" s="53">
-        <v>0.07703448305026303</v>
-      </c>
-      <c r="G21" s="53">
-        <v>0.0715395923420222</v>
-      </c>
-      <c r="H21" s="51" t="s">
         <v>182</v>
+      </c>
+      <c r="C21" s="55" t="str">
+        <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="55" t="str">
+        <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="55" t="str">
+        <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="55" t="str">
+        <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="55" t="str">
+        <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="50" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="C22" s="47">
-        <v>-0.10137353433835843</v>
-      </c>
-      <c r="D22" s="48">
-        <v>0.015932602840352597</v>
-      </c>
-      <c r="E22" s="48">
-        <v>0.04559210159712117</v>
-      </c>
-      <c r="F22" s="48">
-        <v>0.057136595311355426</v>
-      </c>
-      <c r="G22" s="48">
-        <v>0.010615505170216507</v>
-      </c>
-      <c r="H22" s="51" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="28" t="s">
+      <c r="C22" s="56">
+        <v>-1</v>
+      </c>
+      <c r="D22" s="56">
+        <v>-1</v>
+      </c>
+      <c r="E22" s="56">
+        <v>-1</v>
+      </c>
+      <c r="F22" s="56">
+        <v>0</v>
+      </c>
+      <c r="G22" s="56">
+        <v>-1</v>
+      </c>
+      <c r="H22" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="C23" s="54">
-        <v>3</v>
-      </c>
-      <c r="D23" s="54">
-        <v>3</v>
-      </c>
-      <c r="E23" s="54">
-        <v>3</v>
-      </c>
-      <c r="F23" s="54">
-        <v>3</v>
-      </c>
-      <c r="G23" s="54">
-        <v>3</v>
-      </c>
-      <c r="H23" s="51" t="s">
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="44" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="28" t="s">
+      <c r="C24" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="C24" s="55">
-        <v>-1.7077406752181137</v>
-      </c>
-      <c r="D24" s="55">
-        <v>0.35253049906865414</v>
-      </c>
-      <c r="E24" s="56">
-        <v>1.2633343373269994</v>
-      </c>
-      <c r="F24" s="56">
-        <v>1.871670879484945</v>
-      </c>
-      <c r="G24" s="55">
-        <v>0.38568409350163607</v>
-      </c>
-      <c r="H24" s="51" t="s">
+      <c r="D24" s="44" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="28" t="s">
+      <c r="E24" s="44"/>
+      <c r="F24" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="C25" s="57" t="str">
-        <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="57" t="str">
-        <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="57" t="str">
-        <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="57" t="str">
-        <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="57" t="str">
-        <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="51" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="28" t="s">
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="57" t="s">
         <v>189</v>
       </c>
-      <c r="C26" s="58">
-        <v>-1</v>
-      </c>
-      <c r="D26" s="58">
-        <v>-1</v>
-      </c>
-      <c r="E26" s="58">
-        <v>-1</v>
-      </c>
-      <c r="F26" s="58">
-        <v>0</v>
-      </c>
-      <c r="G26" s="58">
-        <v>-1</v>
-      </c>
-      <c r="H26" s="51" t="s">
+      <c r="C25" s="58" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="28" t="s">
+      <c r="D25" s="59" t="s">
         <v>191</v>
       </c>
-      <c r="C27" s="58">
-        <v>0</v>
-      </c>
-      <c r="D27" s="58">
-        <v>0</v>
-      </c>
-      <c r="E27" s="58">
-        <v>0</v>
-      </c>
-      <c r="F27" s="58">
-        <v>0</v>
-      </c>
-      <c r="G27" s="58">
-        <v>0</v>
-      </c>
-      <c r="H27" s="51" t="s">
+      <c r="E25" s="59"/>
+      <c r="F25" s="60" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="45" t="s">
+      <c r="G25" s="60"/>
+      <c r="H25" s="60"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="57" t="s">
         <v>193</v>
       </c>
-      <c r="C29" s="45" t="s">
+      <c r="C26" s="58" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" s="59" t="s">
         <v>194</v>
       </c>
-      <c r="D29" s="45" t="s">
+      <c r="E26" s="59"/>
+      <c r="F26" s="60" t="s">
         <v>195</v>
       </c>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45" t="s">
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="57" t="s">
         <v>196</v>
       </c>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
+      <c r="C27" s="58" t="s">
+        <v>190</v>
+      </c>
+      <c r="D27" s="59" t="s">
+        <v>197</v>
+      </c>
+      <c r="E27" s="59"/>
+      <c r="F27" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="57" t="s">
+        <v>199</v>
+      </c>
+      <c r="C28" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D28" s="59" t="s">
+        <v>201</v>
+      </c>
+      <c r="E28" s="59"/>
+      <c r="F28" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="G28" s="60"/>
+      <c r="H28" s="60"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="57" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29" s="58" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="59" t="s">
+        <v>204</v>
+      </c>
+      <c r="E29" s="59"/>
+      <c r="F29" s="60" t="s">
+        <v>205</v>
+      </c>
+      <c r="G29" s="60"/>
+      <c r="H29" s="60"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="59" t="s">
-        <v>197</v>
-      </c>
-      <c r="C30" s="60" t="s">
-        <v>198</v>
-      </c>
-      <c r="D30" s="61" t="s">
-        <v>199</v>
-      </c>
-      <c r="E30" s="61"/>
-      <c r="F30" s="62" t="s">
+      <c r="B30" s="57" t="s">
+        <v>206</v>
+      </c>
+      <c r="C30" s="61" t="s">
         <v>200</v>
       </c>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
+      <c r="D30" s="59" t="s">
+        <v>207</v>
+      </c>
+      <c r="E30" s="59"/>
+      <c r="F30" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="59" t="s">
-        <v>201</v>
-      </c>
-      <c r="C31" s="60" t="s">
-        <v>198</v>
-      </c>
-      <c r="D31" s="61" t="s">
-        <v>202</v>
-      </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="62" t="s">
-        <v>203</v>
-      </c>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="59" t="s">
-        <v>204</v>
-      </c>
-      <c r="C32" s="60" t="s">
-        <v>198</v>
-      </c>
-      <c r="D32" s="61" t="s">
-        <v>205</v>
-      </c>
-      <c r="E32" s="61"/>
-      <c r="F32" s="62" t="s">
-        <v>206</v>
-      </c>
-      <c r="G32" s="62"/>
-      <c r="H32" s="62"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="59" t="s">
-        <v>207</v>
-      </c>
-      <c r="C33" s="63" t="s">
-        <v>208</v>
-      </c>
-      <c r="D33" s="61" t="s">
+      <c r="B31" s="57" t="s">
         <v>209</v>
       </c>
-      <c r="E33" s="61"/>
-      <c r="F33" s="62" t="s">
+      <c r="C31" s="58" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="59" t="s">
         <v>210</v>
       </c>
-      <c r="G33" s="62"/>
-      <c r="H33" s="62"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="59" t="s">
+      <c r="E31" s="59"/>
+      <c r="F31" s="60" t="s">
         <v>211</v>
       </c>
-      <c r="C34" s="60" t="s">
-        <v>198</v>
-      </c>
-      <c r="D34" s="61" t="s">
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="E34" s="61"/>
-      <c r="F34" s="62" t="s">
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="62" t="s">
         <v>213</v>
       </c>
-      <c r="G34" s="62"/>
-      <c r="H34" s="62"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="59" t="s">
-        <v>214</v>
-      </c>
-      <c r="C35" s="63" t="s">
-        <v>208</v>
-      </c>
-      <c r="D35" s="61" t="s">
-        <v>215</v>
-      </c>
-      <c r="E35" s="61"/>
-      <c r="F35" s="62" t="s">
-        <v>216</v>
-      </c>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="62"/>
       <c r="G35" s="62"/>
       <c r="H35" s="62"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="59" t="s">
-        <v>217</v>
-      </c>
-      <c r="C36" s="60" t="s">
-        <v>198</v>
-      </c>
-      <c r="D36" s="61" t="s">
-        <v>218</v>
-      </c>
-      <c r="E36" s="61"/>
-      <c r="F36" s="62" t="s">
-        <v>219</v>
-      </c>
-      <c r="G36" s="62"/>
-      <c r="H36" s="62"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="59" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" s="28" t="s">
-        <v>220</v>
-      </c>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="64" t="s">
-        <v>221</v>
-      </c>
-      <c r="C40" s="64"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2524,48 +2388,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4539,7 +4403,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C21"/>
+  <dimension ref="B1:C20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4676,24 +4540,16 @@
         <v>0.38568409</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="C19" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="12"/>
+      <c r="C20" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="222">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -502,6 +502,9 @@
     <t>DSCR (Year 5)</t>
   </si>
   <si>
+    <t>Days Cash on Hand (Year 1)</t>
+  </si>
+  <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -541,6 +544,21 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -575,6 +593,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -905,7 +929,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -985,6 +1009,9 @@
     <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1005,6 +1032,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1748,7 +1778,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1760,7 +1790,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1781,37 +1811,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="41" t="s">
-        <v>162</v>
-      </c>
-      <c r="D4" s="42" t="s">
+      <c r="B4" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="D4" s="43" t="s">
         <v>164</v>
       </c>
+      <c r="F4" s="44" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="44" t="s">
-        <v>165</v>
-      </c>
-      <c r="C6" s="45" t="s">
+      <c r="B6" s="45" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="45" t="s">
+      <c r="E6" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="45" t="s">
+      <c r="F6" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="45" t="s">
+      <c r="G6" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="45" t="s">
-        <v>166</v>
+      <c r="H6" s="46" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1836,7 +1866,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C8" s="27">
         <v>995000</v>
@@ -1856,7 +1886,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C9" s="27">
         <v>824466.6666666666</v>
@@ -1876,7 +1906,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C10" s="27">
         <v>271400</v>
@@ -1896,7 +1926,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C11" s="27">
         <v>59064.39316600799</v>
@@ -1958,391 +1988,497 @@
       <c r="B14" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="46">
+      <c r="C14" s="47">
         <v>-0.1607347335001754</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="47">
         <v>-0.029262360098867523</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="48">
         <v>0.009503395504016587</v>
       </c>
-      <c r="F14" s="47">
+      <c r="F14" s="48">
         <v>0.026609542752265323</v>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="47">
         <v>-0.016908329359328268</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="C15" s="48">
+        <v>172</v>
+      </c>
+      <c r="C15" s="49">
         <v>9950</v>
       </c>
-      <c r="D15" s="49">
+      <c r="D15" s="50">
         <v>10052.923076923076</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="50">
         <v>10229.03</v>
       </c>
-      <c r="F15" s="49">
+      <c r="F15" s="50">
         <v>10458.493805405406</v>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="50">
         <v>10729.681052000002</v>
       </c>
-      <c r="H15" s="50" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H15" s="51" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C16" s="46">
-        <v>0.8286097152428811</v>
-      </c>
-      <c r="D16" s="46">
-        <v>0.7280806194906954</v>
-      </c>
-      <c r="E16" s="46">
-        <v>0.6954065537005952</v>
-      </c>
-      <c r="F16" s="46">
-        <v>0.6619844970624266</v>
-      </c>
-      <c r="G16" s="46">
-        <v>0.6668636877551553</v>
-      </c>
-      <c r="H16" s="50" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="28" t="s">
+      <c r="C16" s="33">
+        <v>11549.310598326745</v>
+      </c>
+      <c r="D16" s="33">
+        <v>10347.095332046214</v>
+      </c>
+      <c r="E16" s="33">
+        <v>10131.819482287548</v>
+      </c>
+      <c r="F16" s="33">
+        <v>10180.198067366167</v>
+      </c>
+      <c r="G16" s="33">
+        <v>10911.102033147761</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="C17" s="51">
-        <v>0.1370854271356784</v>
-      </c>
-      <c r="D17" s="51">
-        <v>0.10750183643486777</v>
-      </c>
-      <c r="E17" s="51">
-        <v>0.08841671693210401</v>
-      </c>
-      <c r="F17" s="51">
-        <v>0.07703448305026303</v>
-      </c>
-      <c r="G17" s="51">
-        <v>0.0715395923420222</v>
-      </c>
-      <c r="H17" s="50" t="s">
+      <c r="C17" s="27">
+        <v>600</v>
+      </c>
+      <c r="D17" s="27">
+        <v>803.4</v>
+      </c>
+      <c r="E17" s="27">
+        <v>1075.7526</v>
+      </c>
+      <c r="F17" s="27">
+        <v>1440.4327313999997</v>
+      </c>
+      <c r="G17" s="27">
+        <v>1928.7394273446</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="25" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" s="46">
-        <v>-0.10137353433835843</v>
-      </c>
-      <c r="D18" s="47">
-        <v>0.015932602840352597</v>
-      </c>
-      <c r="E18" s="47">
-        <v>0.04559210159712117</v>
-      </c>
-      <c r="F18" s="47">
-        <v>0.057136595311355426</v>
-      </c>
-      <c r="G18" s="47">
-        <v>0.010615505170216507</v>
-      </c>
-      <c r="H18" s="50" t="s">
+      <c r="C18" s="50">
+        <v>1364</v>
+      </c>
+      <c r="D18" s="50">
+        <v>1080.7076923076922</v>
+      </c>
+      <c r="E18" s="50">
+        <v>904.4172499999999</v>
+      </c>
+      <c r="F18" s="50">
+        <v>805.6646637837837</v>
+      </c>
+      <c r="G18" s="50">
+        <v>767.5970084200001</v>
+      </c>
+      <c r="H18" s="51" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
         <v>178</v>
       </c>
       <c r="C19" s="52">
-        <v>3</v>
+        <v>-1599.310598326745</v>
       </c>
       <c r="D19" s="52">
-        <v>3</v>
-      </c>
-      <c r="E19" s="52">
-        <v>3</v>
-      </c>
-      <c r="F19" s="52">
-        <v>3</v>
+        <v>-294.17225512313837</v>
+      </c>
+      <c r="E19" s="38">
+        <v>97.2105177124508</v>
+      </c>
+      <c r="F19" s="38">
+        <v>278.2957380392372</v>
       </c>
       <c r="G19" s="52">
-        <v>3</v>
-      </c>
-      <c r="H19" s="50" t="s">
-        <v>179</v>
+        <v>-181.42098114775985</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" s="47">
+        <v>0.8286097152428811</v>
+      </c>
+      <c r="D20" s="47">
+        <v>0.7280806194906954</v>
+      </c>
+      <c r="E20" s="47">
+        <v>0.6954065537005952</v>
+      </c>
+      <c r="F20" s="47">
+        <v>0.6619844970624266</v>
+      </c>
+      <c r="G20" s="47">
+        <v>0.6668636877551553</v>
+      </c>
+      <c r="H20" s="51" t="s">
         <v>180</v>
-      </c>
-      <c r="C20" s="53">
-        <v>-1.7077406752181137</v>
-      </c>
-      <c r="D20" s="53">
-        <v>0.35253049906865414</v>
-      </c>
-      <c r="E20" s="54">
-        <v>1.2633343373269994</v>
-      </c>
-      <c r="F20" s="54">
-        <v>1.871670879484945</v>
-      </c>
-      <c r="G20" s="53">
-        <v>0.38568409350163607</v>
-      </c>
-      <c r="H20" s="50" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="C21" s="53">
+        <v>0.1370854271356784</v>
+      </c>
+      <c r="D21" s="53">
+        <v>0.10750183643486777</v>
+      </c>
+      <c r="E21" s="53">
+        <v>0.08841671693210401</v>
+      </c>
+      <c r="F21" s="53">
+        <v>0.07703448305026303</v>
+      </c>
+      <c r="G21" s="53">
+        <v>0.0715395923420222</v>
+      </c>
+      <c r="H21" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="C21" s="55" t="str">
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="47">
+        <v>-0.10137353433835843</v>
+      </c>
+      <c r="D22" s="48">
+        <v>0.015932602840352597</v>
+      </c>
+      <c r="E22" s="48">
+        <v>0.04559210159712117</v>
+      </c>
+      <c r="F22" s="48">
+        <v>0.057136595311355426</v>
+      </c>
+      <c r="G22" s="48">
+        <v>0.010615505170216507</v>
+      </c>
+      <c r="H22" s="51" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="C23" s="54">
+        <v>3</v>
+      </c>
+      <c r="D23" s="54">
+        <v>3</v>
+      </c>
+      <c r="E23" s="54">
+        <v>3</v>
+      </c>
+      <c r="F23" s="54">
+        <v>3</v>
+      </c>
+      <c r="G23" s="54">
+        <v>3</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" s="55">
+        <v>-1.7077406752181137</v>
+      </c>
+      <c r="D24" s="55">
+        <v>0.35253049906865414</v>
+      </c>
+      <c r="E24" s="56">
+        <v>1.2633343373269994</v>
+      </c>
+      <c r="F24" s="56">
+        <v>1.871670879484945</v>
+      </c>
+      <c r="G24" s="55">
+        <v>0.38568409350163607</v>
+      </c>
+      <c r="H24" s="51" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="C25" s="57" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="55" t="str">
+      <c r="D25" s="57" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="55" t="str">
+      <c r="E25" s="57" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="55" t="str">
+      <c r="F25" s="57" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="55" t="str">
+      <c r="G25" s="57" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="50" t="s">
+      <c r="H25" s="51" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="C22" s="56">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" s="58">
         <v>-1</v>
       </c>
-      <c r="D22" s="56">
+      <c r="D26" s="58">
         <v>-1</v>
       </c>
-      <c r="E22" s="56">
+      <c r="E26" s="58">
         <v>-1</v>
       </c>
-      <c r="F22" s="56">
+      <c r="F26" s="58">
         <v>0</v>
       </c>
-      <c r="G22" s="56">
+      <c r="G26" s="58">
         <v>-1</v>
       </c>
-      <c r="H22" s="50" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="44" t="s">
-        <v>185</v>
-      </c>
-      <c r="C24" s="44" t="s">
-        <v>186</v>
-      </c>
-      <c r="D24" s="44" t="s">
-        <v>187</v>
-      </c>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="57" t="s">
-        <v>189</v>
-      </c>
-      <c r="C25" s="58" t="s">
+      <c r="H26" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="D25" s="59" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="E25" s="59"/>
-      <c r="F25" s="60" t="s">
+      <c r="C27" s="58">
+        <v>0</v>
+      </c>
+      <c r="D27" s="58">
+        <v>0</v>
+      </c>
+      <c r="E27" s="58">
+        <v>0</v>
+      </c>
+      <c r="F27" s="58">
+        <v>0</v>
+      </c>
+      <c r="G27" s="58">
+        <v>0</v>
+      </c>
+      <c r="H27" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="G25" s="60"/>
-      <c r="H25" s="60"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="57" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="45" t="s">
         <v>193</v>
       </c>
-      <c r="C26" s="58" t="s">
-        <v>190</v>
-      </c>
-      <c r="D26" s="59" t="s">
+      <c r="C29" s="45" t="s">
         <v>194</v>
       </c>
-      <c r="E26" s="59"/>
-      <c r="F26" s="60" t="s">
+      <c r="D29" s="45" t="s">
         <v>195</v>
       </c>
-      <c r="G26" s="60"/>
-      <c r="H26" s="60"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="57" t="s">
+      <c r="E29" s="45"/>
+      <c r="F29" s="45" t="s">
         <v>196</v>
       </c>
-      <c r="C27" s="58" t="s">
-        <v>190</v>
-      </c>
-      <c r="D27" s="59" t="s">
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="59" t="s">
         <v>197</v>
       </c>
-      <c r="E27" s="59"/>
-      <c r="F27" s="60" t="s">
+      <c r="C30" s="60" t="s">
         <v>198</v>
       </c>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="57" t="s">
+      <c r="D30" s="61" t="s">
         <v>199</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="E30" s="61"/>
+      <c r="F30" s="62" t="s">
         <v>200</v>
       </c>
-      <c r="D28" s="59" t="s">
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="59" t="s">
         <v>201</v>
       </c>
-      <c r="E28" s="59"/>
-      <c r="F28" s="60" t="s">
+      <c r="C31" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="D31" s="61" t="s">
         <v>202</v>
       </c>
-      <c r="G28" s="60"/>
-      <c r="H28" s="60"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="57" t="s">
+      <c r="E31" s="61"/>
+      <c r="F31" s="62" t="s">
         <v>203</v>
       </c>
-      <c r="C29" s="58" t="s">
-        <v>190</v>
-      </c>
-      <c r="D29" s="59" t="s">
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="59" t="s">
         <v>204</v>
       </c>
-      <c r="E29" s="59"/>
-      <c r="F29" s="60" t="s">
+      <c r="C32" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="D32" s="61" t="s">
         <v>205</v>
       </c>
-      <c r="G29" s="60"/>
-      <c r="H29" s="60"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="57" t="s">
+      <c r="E32" s="61"/>
+      <c r="F32" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="C30" s="61" t="s">
-        <v>200</v>
-      </c>
-      <c r="D30" s="59" t="s">
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="59" t="s">
         <v>207</v>
       </c>
-      <c r="E30" s="59"/>
-      <c r="F30" s="60" t="s">
+      <c r="C33" s="63" t="s">
         <v>208</v>
       </c>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="57" t="s">
+      <c r="D33" s="61" t="s">
         <v>209</v>
       </c>
-      <c r="C31" s="58" t="s">
-        <v>190</v>
-      </c>
-      <c r="D31" s="59" t="s">
+      <c r="E33" s="61"/>
+      <c r="F33" s="62" t="s">
         <v>210</v>
       </c>
-      <c r="E31" s="59"/>
-      <c r="F31" s="60" t="s">
+      <c r="G33" s="62"/>
+      <c r="H33" s="62"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="59" t="s">
         <v>211</v>
       </c>
-      <c r="G31" s="60"/>
-      <c r="H31" s="60"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="28" t="s">
+      <c r="C34" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="D34" s="61" t="s">
         <v>212</v>
       </c>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="62" t="s">
+      <c r="E34" s="61"/>
+      <c r="F34" s="62" t="s">
         <v>213</v>
       </c>
-      <c r="C35" s="62"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="62"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="59" t="s">
+        <v>214</v>
+      </c>
+      <c r="C35" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="D35" s="61" t="s">
+        <v>215</v>
+      </c>
+      <c r="E35" s="61"/>
+      <c r="F35" s="62" t="s">
+        <v>216</v>
+      </c>
       <c r="G35" s="62"/>
       <c r="H35" s="62"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="59" t="s">
+        <v>217</v>
+      </c>
+      <c r="C36" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="D36" s="61" t="s">
+        <v>218</v>
+      </c>
+      <c r="E36" s="61"/>
+      <c r="F36" s="62" t="s">
+        <v>219</v>
+      </c>
+      <c r="G36" s="62"/>
+      <c r="H36" s="62"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="64" t="s">
+        <v>221</v>
+      </c>
+      <c r="C40" s="64"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2388,48 +2524,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4403,7 +4539,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C20"/>
+  <dimension ref="B1:C21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4540,16 +4676,24 @@
         <v>0.38568409</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="12" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="C20" s="12"/>
+      <c r="C19" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -13,14 +13,15 @@
     <sheet sheetId="7" name="Staffing" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="Loan Snapshot" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="Summary" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Financial Health" state="visible" r:id="rId13"/>
+    <sheet sheetId="10" name="Decision History" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Financial Health" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="225">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -28,7 +29,7 @@
     <t>Heritage Academy</t>
   </si>
   <si>
-    <t>Generated March 27, 2026 · nonprofit_501c3</t>
+    <t>Generated April 29, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -142,7 +143,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -508,6 +509,15 @@
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
+    <t>Decision History</t>
+  </si>
+  <si>
+    <t>No decisions have been tracked with an outcome yet. As the team marks saved scenarios as Pursued, Declined, or On hold, those outcomes (and any retrospective notes) will appear here so reviewers can see what actually happened versus what was modeled.</t>
+  </si>
+  <si>
+    <t>Once decisions are saved with a Pursued / Declined / On hold outcome inside the planner, they will be summarized here.</t>
+  </si>
+  <si>
     <t>Heritage Academy — Financial Health Dashboard</t>
   </si>
   <si>
@@ -628,7 +638,7 @@
     <t>Liquidity</t>
   </si>
   <si>
-    <t>Cash goes negative in month 5. The school will need outside funding to continue operating.</t>
+    <t>Cash goes negative in month 6. The school will need outside funding to continue operating.</t>
   </si>
   <si>
     <t>Secure a line of credit or bridge funding before operations begin.</t>
@@ -658,7 +668,7 @@
     <t>Debt Affordability</t>
   </si>
   <si>
-    <t>DSCR of 0.39x means operating income does not cover debt payments. This must be resolved.</t>
+    <t>DSCR of 0.39x is below the 1.15x amber threshold. Any shortfall in revenue makes debt unaffordable.</t>
   </si>
   <si>
     <t>Reduce loan amounts, extend terms, or increase revenue before committing to this debt.</t>
@@ -929,7 +939,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1011,6 +1021,12 @@
     </xf>
     <xf numFmtId="3" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1778,6 +1794,72 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1790,7 +1872,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1811,37 +1893,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="42" t="s">
-        <v>163</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>164</v>
-      </c>
-      <c r="F4" s="44" t="s">
-        <v>165</v>
+      <c r="B4" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="45" t="s">
-        <v>166</v>
-      </c>
-      <c r="C6" s="46" t="s">
+      <c r="B6" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="46" t="s">
+      <c r="E6" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="46" t="s">
+      <c r="F6" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="46" t="s">
+      <c r="G6" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="46" t="s">
-        <v>167</v>
+      <c r="H6" s="48" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1866,7 +1948,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C8" s="27">
         <v>995000</v>
@@ -1886,7 +1968,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C9" s="27">
         <v>824466.6666666666</v>
@@ -1906,7 +1988,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C10" s="27">
         <v>271400</v>
@@ -1926,7 +2008,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C11" s="27">
         <v>59064.39316600799</v>
@@ -1988,48 +2070,48 @@
       <c r="B14" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="49">
         <v>-0.1607347335001754</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="49">
         <v>-0.029262360098867523</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="50">
         <v>0.009503395504016587</v>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="50">
         <v>0.026609542752265323</v>
       </c>
-      <c r="G14" s="47">
+      <c r="G14" s="49">
         <v>-0.016908329359328268</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="C15" s="49">
+        <v>175</v>
+      </c>
+      <c r="C15" s="51">
         <v>9950</v>
       </c>
-      <c r="D15" s="50">
+      <c r="D15" s="52">
         <v>10052.923076923076</v>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="52">
         <v>10229.03</v>
       </c>
-      <c r="F15" s="50">
+      <c r="F15" s="52">
         <v>10458.493805405406</v>
       </c>
-      <c r="G15" s="50">
+      <c r="G15" s="52">
         <v>10729.681052000002</v>
       </c>
-      <c r="H15" s="51" t="s">
-        <v>173</v>
+      <c r="H15" s="53" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C16" s="33">
         <v>11549.310598326745</v>
@@ -2049,7 +2131,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="25" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C17" s="27">
         <v>600</v>
@@ -2069,35 +2151,35 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="C18" s="50">
+        <v>179</v>
+      </c>
+      <c r="C18" s="52">
         <v>1364</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D18" s="52">
         <v>1080.7076923076922</v>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="52">
         <v>904.4172499999999</v>
       </c>
-      <c r="F18" s="50">
+      <c r="F18" s="52">
         <v>805.6646637837837</v>
       </c>
-      <c r="G18" s="50">
+      <c r="G18" s="52">
         <v>767.5970084200001</v>
       </c>
-      <c r="H18" s="51" t="s">
-        <v>177</v>
+      <c r="H18" s="53" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="C19" s="52">
+        <v>181</v>
+      </c>
+      <c r="C19" s="54">
         <v>-1599.310598326745</v>
       </c>
-      <c r="D19" s="52">
+      <c r="D19" s="54">
         <v>-294.17225512313837</v>
       </c>
       <c r="E19" s="38">
@@ -2106,356 +2188,356 @@
       <c r="F19" s="38">
         <v>278.2957380392372</v>
       </c>
-      <c r="G19" s="52">
+      <c r="G19" s="54">
         <v>-181.42098114775985</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="C20" s="47">
+        <v>182</v>
+      </c>
+      <c r="C20" s="49">
         <v>0.8286097152428811</v>
       </c>
-      <c r="D20" s="47">
+      <c r="D20" s="49">
         <v>0.7280806194906954</v>
       </c>
-      <c r="E20" s="47">
+      <c r="E20" s="49">
         <v>0.6954065537005952</v>
       </c>
-      <c r="F20" s="47">
+      <c r="F20" s="49">
         <v>0.6619844970624266</v>
       </c>
-      <c r="G20" s="47">
+      <c r="G20" s="49">
         <v>0.6668636877551553</v>
       </c>
-      <c r="H20" s="51" t="s">
-        <v>180</v>
+      <c r="H20" s="53" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="C21" s="53">
+        <v>184</v>
+      </c>
+      <c r="C21" s="55">
         <v>0.1370854271356784</v>
       </c>
-      <c r="D21" s="53">
+      <c r="D21" s="55">
         <v>0.10750183643486777</v>
       </c>
-      <c r="E21" s="53">
+      <c r="E21" s="55">
         <v>0.08841671693210401</v>
       </c>
-      <c r="F21" s="53">
+      <c r="F21" s="55">
         <v>0.07703448305026303</v>
       </c>
-      <c r="G21" s="53">
+      <c r="G21" s="55">
         <v>0.0715395923420222</v>
       </c>
-      <c r="H21" s="51" t="s">
-        <v>182</v>
+      <c r="H21" s="53" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="49">
         <v>-0.10137353433835843</v>
       </c>
-      <c r="D22" s="48">
+      <c r="D22" s="50">
         <v>0.015932602840352597</v>
       </c>
-      <c r="E22" s="48">
+      <c r="E22" s="50">
         <v>0.04559210159712117</v>
       </c>
-      <c r="F22" s="48">
+      <c r="F22" s="50">
         <v>0.057136595311355426</v>
       </c>
-      <c r="G22" s="48">
+      <c r="G22" s="50">
         <v>0.010615505170216507</v>
       </c>
-      <c r="H22" s="51" t="s">
-        <v>183</v>
+      <c r="H22" s="53" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="C23" s="54">
+        <v>187</v>
+      </c>
+      <c r="C23" s="56">
         <v>3</v>
       </c>
-      <c r="D23" s="54">
+      <c r="D23" s="56">
         <v>3</v>
       </c>
-      <c r="E23" s="54">
+      <c r="E23" s="56">
         <v>3</v>
       </c>
-      <c r="F23" s="54">
+      <c r="F23" s="56">
         <v>3</v>
       </c>
-      <c r="G23" s="54">
+      <c r="G23" s="56">
         <v>3</v>
       </c>
-      <c r="H23" s="51" t="s">
-        <v>185</v>
+      <c r="H23" s="53" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="C24" s="55">
+        <v>189</v>
+      </c>
+      <c r="C24" s="57">
         <v>-1.7077406752181137</v>
       </c>
-      <c r="D24" s="55">
+      <c r="D24" s="57">
         <v>0.35253049906865414</v>
       </c>
-      <c r="E24" s="56">
+      <c r="E24" s="58">
         <v>1.2633343373269994</v>
       </c>
-      <c r="F24" s="56">
+      <c r="F24" s="58">
         <v>1.871670879484945</v>
       </c>
-      <c r="G24" s="55">
+      <c r="G24" s="57">
         <v>0.38568409350163607</v>
       </c>
-      <c r="H24" s="51" t="s">
-        <v>187</v>
+      <c r="H24" s="53" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="C25" s="57" t="str">
+        <v>191</v>
+      </c>
+      <c r="C25" s="59" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D25" s="57" t="str">
+      <c r="D25" s="59" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="57" t="str">
+      <c r="E25" s="59" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="57" t="str">
+      <c r="F25" s="59" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="57" t="str">
+      <c r="G25" s="59" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="51" t="s">
+      <c r="H25" s="53" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="28" t="s">
-        <v>189</v>
-      </c>
-      <c r="C26" s="58">
+        <v>192</v>
+      </c>
+      <c r="C26" s="60">
         <v>-1</v>
       </c>
-      <c r="D26" s="58">
+      <c r="D26" s="60">
         <v>-1</v>
       </c>
-      <c r="E26" s="58">
+      <c r="E26" s="60">
         <v>-1</v>
       </c>
-      <c r="F26" s="58">
+      <c r="F26" s="60">
         <v>0</v>
       </c>
-      <c r="G26" s="58">
+      <c r="G26" s="60">
         <v>-1</v>
       </c>
-      <c r="H26" s="51" t="s">
-        <v>190</v>
+      <c r="H26" s="53" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="C27" s="58">
+        <v>194</v>
+      </c>
+      <c r="C27" s="60">
         <v>0</v>
       </c>
-      <c r="D27" s="58">
+      <c r="D27" s="60">
         <v>0</v>
       </c>
-      <c r="E27" s="58">
+      <c r="E27" s="60">
         <v>0</v>
       </c>
-      <c r="F27" s="58">
+      <c r="F27" s="60">
         <v>0</v>
       </c>
-      <c r="G27" s="58">
+      <c r="G27" s="60">
         <v>0</v>
       </c>
-      <c r="H27" s="51" t="s">
-        <v>192</v>
+      <c r="H27" s="53" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="45" t="s">
-        <v>193</v>
-      </c>
-      <c r="C29" s="45" t="s">
-        <v>194</v>
-      </c>
-      <c r="D29" s="45" t="s">
-        <v>195</v>
-      </c>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45" t="s">
+      <c r="B29" s="47" t="s">
         <v>196</v>
       </c>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
+      <c r="C29" s="47" t="s">
+        <v>197</v>
+      </c>
+      <c r="D29" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47" t="s">
+        <v>199</v>
+      </c>
+      <c r="G29" s="47"/>
+      <c r="H29" s="47"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="59" t="s">
-        <v>197</v>
-      </c>
-      <c r="C30" s="60" t="s">
-        <v>198</v>
-      </c>
-      <c r="D30" s="61" t="s">
-        <v>199</v>
-      </c>
-      <c r="E30" s="61"/>
-      <c r="F30" s="62" t="s">
+      <c r="B30" s="61" t="s">
         <v>200</v>
       </c>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
+      <c r="C30" s="62" t="s">
+        <v>201</v>
+      </c>
+      <c r="D30" s="63" t="s">
+        <v>202</v>
+      </c>
+      <c r="E30" s="63"/>
+      <c r="F30" s="64" t="s">
+        <v>203</v>
+      </c>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="59" t="s">
+      <c r="B31" s="61" t="s">
+        <v>204</v>
+      </c>
+      <c r="C31" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="C31" s="60" t="s">
-        <v>198</v>
-      </c>
-      <c r="D31" s="61" t="s">
-        <v>202</v>
-      </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="62" t="s">
-        <v>203</v>
-      </c>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
+      <c r="D31" s="63" t="s">
+        <v>205</v>
+      </c>
+      <c r="E31" s="63"/>
+      <c r="F31" s="64" t="s">
+        <v>206</v>
+      </c>
+      <c r="G31" s="64"/>
+      <c r="H31" s="64"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="59" t="s">
-        <v>204</v>
-      </c>
-      <c r="C32" s="60" t="s">
-        <v>198</v>
-      </c>
-      <c r="D32" s="61" t="s">
-        <v>205</v>
-      </c>
-      <c r="E32" s="61"/>
-      <c r="F32" s="62" t="s">
-        <v>206</v>
-      </c>
-      <c r="G32" s="62"/>
-      <c r="H32" s="62"/>
+      <c r="B32" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="C32" s="62" t="s">
+        <v>201</v>
+      </c>
+      <c r="D32" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="E32" s="63"/>
+      <c r="F32" s="64" t="s">
+        <v>209</v>
+      </c>
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="59" t="s">
-        <v>207</v>
-      </c>
-      <c r="C33" s="63" t="s">
-        <v>208</v>
-      </c>
-      <c r="D33" s="61" t="s">
-        <v>209</v>
-      </c>
-      <c r="E33" s="61"/>
-      <c r="F33" s="62" t="s">
+      <c r="B33" s="61" t="s">
         <v>210</v>
       </c>
-      <c r="G33" s="62"/>
-      <c r="H33" s="62"/>
+      <c r="C33" s="65" t="s">
+        <v>211</v>
+      </c>
+      <c r="D33" s="63" t="s">
+        <v>212</v>
+      </c>
+      <c r="E33" s="63"/>
+      <c r="F33" s="64" t="s">
+        <v>213</v>
+      </c>
+      <c r="G33" s="64"/>
+      <c r="H33" s="64"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="59" t="s">
+      <c r="B34" s="61" t="s">
+        <v>214</v>
+      </c>
+      <c r="C34" s="62" t="s">
+        <v>201</v>
+      </c>
+      <c r="D34" s="63" t="s">
+        <v>215</v>
+      </c>
+      <c r="E34" s="63"/>
+      <c r="F34" s="64" t="s">
+        <v>216</v>
+      </c>
+      <c r="G34" s="64"/>
+      <c r="H34" s="64"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="61" t="s">
+        <v>217</v>
+      </c>
+      <c r="C35" s="65" t="s">
         <v>211</v>
       </c>
-      <c r="C34" s="60" t="s">
-        <v>198</v>
-      </c>
-      <c r="D34" s="61" t="s">
-        <v>212</v>
-      </c>
-      <c r="E34" s="61"/>
-      <c r="F34" s="62" t="s">
-        <v>213</v>
-      </c>
-      <c r="G34" s="62"/>
-      <c r="H34" s="62"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="59" t="s">
-        <v>214</v>
-      </c>
-      <c r="C35" s="63" t="s">
-        <v>208</v>
-      </c>
-      <c r="D35" s="61" t="s">
-        <v>215</v>
-      </c>
-      <c r="E35" s="61"/>
-      <c r="F35" s="62" t="s">
-        <v>216</v>
-      </c>
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
+      <c r="D35" s="63" t="s">
+        <v>218</v>
+      </c>
+      <c r="E35" s="63"/>
+      <c r="F35" s="64" t="s">
+        <v>219</v>
+      </c>
+      <c r="G35" s="64"/>
+      <c r="H35" s="64"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="59" t="s">
-        <v>217</v>
-      </c>
-      <c r="C36" s="60" t="s">
-        <v>198</v>
-      </c>
-      <c r="D36" s="61" t="s">
-        <v>218</v>
-      </c>
-      <c r="E36" s="61"/>
-      <c r="F36" s="62" t="s">
-        <v>219</v>
-      </c>
-      <c r="G36" s="62"/>
-      <c r="H36" s="62"/>
+      <c r="B36" s="61" t="s">
+        <v>220</v>
+      </c>
+      <c r="C36" s="62" t="s">
+        <v>201</v>
+      </c>
+      <c r="D36" s="63" t="s">
+        <v>221</v>
+      </c>
+      <c r="E36" s="63"/>
+      <c r="F36" s="64" t="s">
+        <v>222</v>
+      </c>
+      <c r="G36" s="64"/>
+      <c r="H36" s="64"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="59" t="s">
+      <c r="B38" s="61" t="s">
         <v>39</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D38" s="28"/>
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="64" t="s">
-        <v>221</v>
-      </c>
-      <c r="C40" s="64"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
+      <c r="B40" s="66" t="s">
+        <v>224</v>
+      </c>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="66"/>
+      <c r="H40" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -2562,10 +2644,10 @@
       <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C24&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C24&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -29,7 +29,7 @@
     <t>Heritage Academy</t>
   </si>
   <si>
-    <t>Generated April 29, 2026 · nonprofit_501c3</t>
+    <t>Generated May 1, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -143,7 +143,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -29,7 +29,7 @@
     <t>Heritage Academy</t>
   </si>
   <si>
-    <t>Generated May 1, 2026 · nonprofit_501c3</t>
+    <t>Generated May 7, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -143,7 +143,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -413,6 +413,9 @@
     <t>Break-even</t>
   </si>
   <si>
+    <t>✓ Break-even</t>
+  </si>
+  <si>
     <t>Cash Flow &amp; Debt Service Coverage</t>
   </si>
   <si>
@@ -626,40 +629,37 @@
     <t>Viability</t>
   </si>
   <si>
-    <t>○ Needs attention</t>
-  </si>
-  <si>
-    <t>The model does not reach break-even within 5 years. This needs to be addressed before approaching lenders.</t>
-  </si>
-  <si>
-    <t>Revisit revenue assumptions and cost structure to build a clear path to break-even.</t>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>The model reaches net income early and sustains strong margins through Year 5.</t>
+  </si>
+  <si>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
   </si>
   <si>
-    <t>Cash goes negative in month 6. The school will need outside funding to continue operating.</t>
-  </si>
-  <si>
-    <t>Secure a line of credit or bridge funding before operations begin.</t>
+    <t>Cash stays positive throughout the projection and reserves exceed 3 months of expenses.</t>
+  </si>
+  <si>
+    <t>Maintain reserves as a buffer against seasonal revenue dips.</t>
   </si>
   <si>
     <t>Staffing Burden</t>
   </si>
   <si>
-    <t>Staffing at 67% of revenue is above the sustainable range. There's too little left for everything else.</t>
-  </si>
-  <si>
-    <t>Review staffing plan for phased hiring, shared roles, or adjusted ratios.</t>
+    <t>Staffing at 33% of revenue leaves room for facilities, programs, and reserves.</t>
+  </si>
+  <si>
+    <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
   </si>
   <si>
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>● Healthy</t>
-  </si>
-  <si>
-    <t>Facility costs at 7% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 3% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -668,10 +668,10 @@
     <t>Debt Affordability</t>
   </si>
   <si>
-    <t>DSCR of 0.39x is below the 1.15x amber threshold. Any shortfall in revenue makes debt unaffordable.</t>
-  </si>
-  <si>
-    <t>Reduce loan amounts, extend terms, or increase revenue before committing to this debt.</t>
+    <t>DSCR of 38.40x provides comfortable coverage of debt payments with room to spare.</t>
+  </si>
+  <si>
+    <t>Maintain this ratio as you take on any additional debt.</t>
   </si>
   <si>
     <t>Revenue Concentration</t>
@@ -686,13 +686,13 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>Less than 1 month of reserves by Year 5. The school has no financial cushion.</t>
-  </si>
-  <si>
-    <t>Prioritize building reserves — even a small surplus each year compounds into meaningful protection.</t>
-  </si>
-  <si>
-    <t>2 Healthy  |  0 Watch  |  5 Needs Attention</t>
+    <t>45.1 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+  </si>
+  <si>
+    <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
+  </si>
+  <si>
+    <t>7 Healthy  |  0 Watch  |  0 Needs Attention</t>
   </si>
   <si>
     <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -856,12 +856,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4EC"/>
+        <fgColor rgb="FFE8EDF2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8EDF2"/>
+        <fgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -939,7 +939,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -988,9 +988,6 @@
     <xf numFmtId="165" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1000,11 +997,11 @@
     <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1016,10 +1013,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1031,33 +1028,18 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1066,21 +1048,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1809,7 +1788,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -1819,26 +1798,26 @@
       <c r="H1" s="13"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="42" t="s">
-        <v>163</v>
-      </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="B2" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="43" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
+      <c r="B4" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1860,7 +1839,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1870,9 +1849,9 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1880,8 +1859,9 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="12" t="s">
         <v>40</v>
       </c>
@@ -1891,39 +1871,40 @@
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="D4" s="45" t="s">
+      <c r="B4" s="43" t="s">
         <v>167</v>
       </c>
-      <c r="F4" s="46" t="s">
+      <c r="D4" s="44" t="s">
         <v>168</v>
       </c>
+      <c r="F4" s="45" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="47" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="48" t="s">
+      <c r="B6" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="F6" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="48" t="s">
+      <c r="G6" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="48" t="s">
-        <v>170</v>
+      <c r="H6" s="47" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1948,27 +1929,27 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C8" s="27">
-        <v>995000</v>
+        <v>1992500</v>
       </c>
       <c r="D8" s="27">
-        <v>1306880</v>
+        <v>2642532.5</v>
       </c>
       <c r="E8" s="27">
-        <v>1636644.8</v>
+        <v>3329841.2</v>
       </c>
       <c r="F8" s="27">
-        <v>1934821.354</v>
+        <v>3951312.4416249995</v>
       </c>
       <c r="G8" s="27">
-        <v>2145936.2104</v>
+        <v>4391326.28635</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C9" s="27">
         <v>824466.6666666666</v>
@@ -1988,7 +1969,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C10" s="27">
         <v>271400</v>
@@ -2008,7 +1989,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C11" s="27">
         <v>59064.39316600799</v>
@@ -2031,107 +2012,107 @@
         <v>126</v>
       </c>
       <c r="C12" s="30">
-        <v>-159931.0598326745</v>
+        <v>837568.9401673255</v>
       </c>
       <c r="D12" s="30">
-        <v>-38242.39316600799</v>
-      </c>
-      <c r="E12" s="31">
-        <v>15553.682833992127</v>
-      </c>
-      <c r="F12" s="31">
-        <v>51484.71153725888</v>
+        <v>1297410.106833992</v>
+      </c>
+      <c r="E12" s="30">
+        <v>1708750.0828339923</v>
+      </c>
+      <c r="F12" s="30">
+        <v>2067975.7991622584</v>
       </c>
       <c r="G12" s="30">
-        <v>-36284.19622955197</v>
+        <v>2209105.8797204476</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="30">
-        <v>-84931.05983267451</v>
+        <v>912568.9401673255</v>
       </c>
       <c r="D13" s="30">
-        <v>-123173.45299868251</v>
+        <v>2209979.0470013176</v>
       </c>
       <c r="E13" s="30">
-        <v>-107619.77016469039</v>
+        <v>3918729.12983531</v>
       </c>
       <c r="F13" s="30">
-        <v>-56135.05862743151</v>
+        <v>5986704.928997569</v>
       </c>
       <c r="G13" s="30">
-        <v>-92419.25485698348</v>
+        <v>8195810.808718016</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="49">
-        <v>-0.1607347335001754</v>
-      </c>
-      <c r="D14" s="49">
-        <v>-0.029262360098867523</v>
-      </c>
-      <c r="E14" s="50">
-        <v>0.009503395504016587</v>
-      </c>
-      <c r="F14" s="50">
-        <v>0.026609542752265323</v>
-      </c>
-      <c r="G14" s="49">
-        <v>-0.016908329359328268</v>
+      <c r="C14" s="48">
+        <v>0.42036082317055234</v>
+      </c>
+      <c r="D14" s="48">
+        <v>0.49097224228424513</v>
+      </c>
+      <c r="E14" s="48">
+        <v>0.5131626345526604</v>
+      </c>
+      <c r="F14" s="48">
+        <v>0.523364282048977</v>
+      </c>
+      <c r="G14" s="48">
+        <v>0.5030612019396584</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="C15" s="51">
-        <v>9950</v>
-      </c>
-      <c r="D15" s="52">
-        <v>10052.923076923076</v>
-      </c>
-      <c r="E15" s="52">
-        <v>10229.03</v>
-      </c>
-      <c r="F15" s="52">
-        <v>10458.493805405406</v>
-      </c>
-      <c r="G15" s="52">
-        <v>10729.681052000002</v>
-      </c>
-      <c r="H15" s="53" t="s">
         <v>176</v>
+      </c>
+      <c r="C15" s="49">
+        <v>19925</v>
+      </c>
+      <c r="D15" s="49">
+        <v>20327.173076923078</v>
+      </c>
+      <c r="E15" s="49">
+        <v>20811.5075</v>
+      </c>
+      <c r="F15" s="49">
+        <v>21358.445630405404</v>
+      </c>
+      <c r="G15" s="49">
+        <v>21956.63143175</v>
+      </c>
+      <c r="H15" s="50" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="C16" s="33">
+        <v>178</v>
+      </c>
+      <c r="C16" s="32">
         <v>11549.310598326745</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="32">
         <v>10347.095332046214</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="32">
         <v>10131.819482287548</v>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="32">
         <v>10180.198067366167</v>
       </c>
-      <c r="G16" s="33">
+      <c r="G16" s="32">
         <v>10911.102033147761</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C17" s="27">
         <v>600</v>
@@ -2151,374 +2132,382 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="C18" s="52">
+        <v>180</v>
+      </c>
+      <c r="C18" s="49">
         <v>1364</v>
       </c>
-      <c r="D18" s="52">
+      <c r="D18" s="49">
         <v>1080.7076923076922</v>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="49">
         <v>904.4172499999999</v>
       </c>
-      <c r="F18" s="52">
+      <c r="F18" s="49">
         <v>805.6646637837837</v>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="49">
         <v>767.5970084200001</v>
       </c>
-      <c r="H18" s="53" t="s">
-        <v>180</v>
+      <c r="H18" s="50" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="C19" s="54">
-        <v>-1599.310598326745</v>
-      </c>
-      <c r="D19" s="54">
-        <v>-294.17225512313837</v>
-      </c>
-      <c r="E19" s="38">
-        <v>97.2105177124508</v>
-      </c>
-      <c r="F19" s="38">
-        <v>278.2957380392372</v>
-      </c>
-      <c r="G19" s="54">
-        <v>-181.42098114775985</v>
+        <v>182</v>
+      </c>
+      <c r="C19" s="37">
+        <v>8375.689401673255</v>
+      </c>
+      <c r="D19" s="37">
+        <v>9980.077744876862</v>
+      </c>
+      <c r="E19" s="37">
+        <v>10679.688017712451</v>
+      </c>
+      <c r="F19" s="37">
+        <v>11178.247563039235</v>
+      </c>
+      <c r="G19" s="37">
+        <v>11045.529398602237</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="C20" s="49">
-        <v>0.8286097152428811</v>
-      </c>
-      <c r="D20" s="49">
-        <v>0.7280806194906954</v>
-      </c>
-      <c r="E20" s="49">
-        <v>0.6954065537005952</v>
-      </c>
-      <c r="F20" s="49">
-        <v>0.6619844970624266</v>
-      </c>
-      <c r="G20" s="49">
-        <v>0.6668636877551553</v>
-      </c>
-      <c r="H20" s="53" t="s">
         <v>183</v>
+      </c>
+      <c r="C20" s="48">
+        <v>0.4137850271852781</v>
+      </c>
+      <c r="D20" s="48">
+        <v>0.3600765553498396</v>
+      </c>
+      <c r="E20" s="48">
+        <v>0.34179813740066645</v>
+      </c>
+      <c r="F20" s="48">
+        <v>0.32415096499091023</v>
+      </c>
+      <c r="G20" s="48">
+        <v>0.3258803472205957</v>
+      </c>
+      <c r="H20" s="50" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="C21" s="55">
-        <v>0.1370854271356784</v>
-      </c>
-      <c r="D21" s="55">
-        <v>0.10750183643486777</v>
-      </c>
-      <c r="E21" s="55">
-        <v>0.08841671693210401</v>
-      </c>
-      <c r="F21" s="55">
-        <v>0.07703448305026303</v>
-      </c>
-      <c r="G21" s="55">
-        <v>0.0715395923420222</v>
-      </c>
-      <c r="H21" s="53" t="s">
         <v>185</v>
+      </c>
+      <c r="C21" s="48">
+        <v>0.06845671267252196</v>
+      </c>
+      <c r="D21" s="48">
+        <v>0.05316566589058034</v>
+      </c>
+      <c r="E21" s="48">
+        <v>0.04345755587383566</v>
+      </c>
+      <c r="F21" s="48">
+        <v>0.03772112810666604</v>
+      </c>
+      <c r="G21" s="48">
+        <v>0.034959689094659116</v>
+      </c>
+      <c r="H21" s="50" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="49">
-        <v>-0.10137353433835843</v>
-      </c>
-      <c r="D22" s="50">
-        <v>0.015932602840352597</v>
-      </c>
-      <c r="E22" s="50">
-        <v>0.04559210159712117</v>
-      </c>
-      <c r="F22" s="50">
-        <v>0.057136595311355426</v>
-      </c>
-      <c r="G22" s="50">
-        <v>0.010615505170216507</v>
-      </c>
-      <c r="H22" s="53" t="s">
-        <v>186</v>
+      <c r="C22" s="48">
+        <v>0.45000418235048106</v>
+      </c>
+      <c r="D22" s="48">
+        <v>0.5133236771922389</v>
+      </c>
+      <c r="E22" s="48">
+        <v>0.5309005354369452</v>
+      </c>
+      <c r="F22" s="48">
+        <v>0.538312326284557</v>
+      </c>
+      <c r="G22" s="48">
+        <v>0.5165114420982191</v>
+      </c>
+      <c r="H22" s="50" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="C23" s="56">
-        <v>3</v>
-      </c>
-      <c r="D23" s="56">
-        <v>3</v>
-      </c>
-      <c r="E23" s="56">
-        <v>3</v>
-      </c>
-      <c r="F23" s="56">
-        <v>3</v>
-      </c>
-      <c r="G23" s="56">
-        <v>3</v>
-      </c>
-      <c r="H23" s="53" t="s">
         <v>188</v>
+      </c>
+      <c r="C23" s="51">
+        <v>4</v>
+      </c>
+      <c r="D23" s="51">
+        <v>4</v>
+      </c>
+      <c r="E23" s="51">
+        <v>4</v>
+      </c>
+      <c r="F23" s="51">
+        <v>4</v>
+      </c>
+      <c r="G23" s="51">
+        <v>4</v>
+      </c>
+      <c r="H23" s="50" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="28" t="s">
-        <v>189</v>
-      </c>
-      <c r="C24" s="57">
-        <v>-1.7077406752181137</v>
-      </c>
-      <c r="D24" s="57">
-        <v>0.35253049906865414</v>
-      </c>
-      <c r="E24" s="58">
-        <v>1.2633343373269994</v>
-      </c>
-      <c r="F24" s="58">
-        <v>1.871670879484945</v>
-      </c>
-      <c r="G24" s="57">
-        <v>0.38568409350163607</v>
-      </c>
-      <c r="H24" s="53" t="s">
         <v>190</v>
+      </c>
+      <c r="C24" s="52">
+        <v>15.18060688125977</v>
+      </c>
+      <c r="D24" s="52">
+        <v>22.966027877192538</v>
+      </c>
+      <c r="E24" s="52">
+        <v>29.930291013594818</v>
+      </c>
+      <c r="F24" s="52">
+        <v>36.012224596127645</v>
+      </c>
+      <c r="G24" s="52">
+        <v>38.401652015817284</v>
+      </c>
+      <c r="H24" s="50" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="C25" s="59" t="str">
+        <v>192</v>
+      </c>
+      <c r="C25" s="33" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="59" t="str">
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D25" s="53" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="59" t="str">
+      <c r="E25" s="53" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="59" t="str">
+      <c r="F25" s="53" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="59" t="str">
+      <c r="G25" s="53" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="53" t="s">
+      <c r="H25" s="50" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="C26" s="60">
-        <v>-1</v>
-      </c>
-      <c r="D26" s="60">
-        <v>-1</v>
-      </c>
-      <c r="E26" s="60">
-        <v>-1</v>
-      </c>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="60">
-        <v>-1</v>
-      </c>
-      <c r="H26" s="53" t="s">
         <v>193</v>
+      </c>
+      <c r="C26" s="54">
+        <v>9</v>
+      </c>
+      <c r="D26" s="55">
+        <v>20</v>
+      </c>
+      <c r="E26" s="51">
+        <v>29</v>
+      </c>
+      <c r="F26" s="51">
+        <v>38</v>
+      </c>
+      <c r="G26" s="51">
+        <v>45</v>
+      </c>
+      <c r="H26" s="50" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="28" t="s">
-        <v>194</v>
-      </c>
-      <c r="C27" s="60">
-        <v>0</v>
-      </c>
-      <c r="D27" s="60">
-        <v>0</v>
-      </c>
-      <c r="E27" s="60">
-        <v>0</v>
-      </c>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="60">
-        <v>0</v>
-      </c>
-      <c r="H27" s="53" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="47" t="s">
+      <c r="C27" s="51">
+        <v>288</v>
+      </c>
+      <c r="D27" s="51">
+        <v>600</v>
+      </c>
+      <c r="E27" s="51">
+        <v>882</v>
+      </c>
+      <c r="F27" s="51">
+        <v>1160</v>
+      </c>
+      <c r="G27" s="51">
+        <v>1371</v>
+      </c>
+      <c r="H27" s="50" t="s">
         <v>196</v>
       </c>
-      <c r="C29" s="47" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="46" t="s">
         <v>197</v>
       </c>
-      <c r="D29" s="47" t="s">
+      <c r="C29" s="46" t="s">
         <v>198</v>
       </c>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47" t="s">
+      <c r="D29" s="46" t="s">
         <v>199</v>
       </c>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="61" t="s">
+      <c r="E29" s="46"/>
+      <c r="F29" s="46" t="s">
         <v>200</v>
       </c>
-      <c r="C30" s="62" t="s">
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="46"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="56" t="s">
         <v>201</v>
       </c>
-      <c r="D30" s="63" t="s">
+      <c r="C30" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="E30" s="63"/>
-      <c r="F30" s="64" t="s">
+      <c r="D30" s="57" t="s">
         <v>203</v>
       </c>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="61" t="s">
+      <c r="E30" s="57"/>
+      <c r="F30" s="58" t="s">
         <v>204</v>
       </c>
-      <c r="C31" s="62" t="s">
-        <v>201</v>
-      </c>
-      <c r="D31" s="63" t="s">
+      <c r="G30" s="58"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="58"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="56" t="s">
         <v>205</v>
       </c>
-      <c r="E31" s="63"/>
-      <c r="F31" s="64" t="s">
+      <c r="C31" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="D31" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="61" t="s">
+      <c r="E31" s="57"/>
+      <c r="F31" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="C32" s="62" t="s">
-        <v>201</v>
-      </c>
-      <c r="D32" s="63" t="s">
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B32" s="56" t="s">
         <v>208</v>
       </c>
-      <c r="E32" s="63"/>
-      <c r="F32" s="64" t="s">
+      <c r="C32" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="D32" s="57" t="s">
         <v>209</v>
       </c>
-      <c r="G32" s="64"/>
-      <c r="H32" s="64"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="61" t="s">
+      <c r="E32" s="57"/>
+      <c r="F32" s="58" t="s">
         <v>210</v>
       </c>
-      <c r="C33" s="65" t="s">
+      <c r="G32" s="58"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="58"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B33" s="56" t="s">
         <v>211</v>
       </c>
-      <c r="D33" s="63" t="s">
+      <c r="C33" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="D33" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="E33" s="63"/>
-      <c r="F33" s="64" t="s">
+      <c r="E33" s="57"/>
+      <c r="F33" s="58" t="s">
         <v>213</v>
       </c>
-      <c r="G33" s="64"/>
-      <c r="H33" s="64"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="61" t="s">
+      <c r="G33" s="58"/>
+      <c r="H33" s="58"/>
+      <c r="I33" s="58"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B34" s="56" t="s">
         <v>214</v>
       </c>
-      <c r="C34" s="62" t="s">
-        <v>201</v>
-      </c>
-      <c r="D34" s="63" t="s">
+      <c r="C34" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="D34" s="57" t="s">
         <v>215</v>
       </c>
-      <c r="E34" s="63"/>
-      <c r="F34" s="64" t="s">
+      <c r="E34" s="57"/>
+      <c r="F34" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="61" t="s">
+      <c r="G34" s="58"/>
+      <c r="H34" s="58"/>
+      <c r="I34" s="58"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" s="56" t="s">
         <v>217</v>
       </c>
-      <c r="C35" s="65" t="s">
-        <v>211</v>
-      </c>
-      <c r="D35" s="63" t="s">
+      <c r="C35" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="D35" s="57" t="s">
         <v>218</v>
       </c>
-      <c r="E35" s="63"/>
-      <c r="F35" s="64" t="s">
+      <c r="E35" s="57"/>
+      <c r="F35" s="58" t="s">
         <v>219</v>
       </c>
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="61" t="s">
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B36" s="56" t="s">
         <v>220</v>
       </c>
-      <c r="C36" s="62" t="s">
-        <v>201</v>
-      </c>
-      <c r="D36" s="63" t="s">
+      <c r="C36" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="D36" s="57" t="s">
         <v>221</v>
       </c>
-      <c r="E36" s="63"/>
-      <c r="F36" s="64" t="s">
+      <c r="E36" s="57"/>
+      <c r="F36" s="58" t="s">
         <v>222</v>
       </c>
-      <c r="G36" s="64"/>
-      <c r="H36" s="64"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="58"/>
+      <c r="I36" s="58"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="61" t="s">
+      <c r="B38" s="56" t="s">
         <v>39</v>
       </c>
       <c r="C38" s="28" t="s">
@@ -2528,39 +2517,40 @@
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="66" t="s">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B40" s="59" t="s">
         <v>224</v>
       </c>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="66"/>
-      <c r="H40" s="66"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2904,7 +2894,7 @@
         <v>59</v>
       </c>
       <c r="D20" s="21">
-        <v>0</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
@@ -3273,50 +3263,50 @@
       <c r="B5" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="27" t="str">
+      <c r="C5" s="27">
         <f>Assumptions!D12*Assumptions!D20</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="27" t="str">
+        <v>1050000</v>
+      </c>
+      <c r="D5" s="27">
         <f>Assumptions!D13*Assumptions!D20*(1+Assumptions!D21)^1</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="27" t="str">
+        <v>1405950</v>
+      </c>
+      <c r="E5" s="27">
         <f>Assumptions!D14*Assumptions!D20*(1+Assumptions!D21)^2</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="27" t="str">
+        <v>1782312</v>
+      </c>
+      <c r="F5" s="27">
         <f>Assumptions!D15*Assumptions!D20*(1+Assumptions!D21)^3</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="27" t="str">
+        <v>2122622.1975</v>
+      </c>
+      <c r="G5" s="27">
         <f>Assumptions!D16*Assumptions!D20*(1+Assumptions!D21)^4</f>
-        <v>0</v>
+        <v>2363568.501</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="27" t="str">
+      <c r="C6" s="27">
         <f>C5*Assumptions!D26</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="27" t="str">
+        <v>997500</v>
+      </c>
+      <c r="D6" s="27">
         <f>D5*Assumptions!D26</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="27" t="str">
+        <v>1335652.5</v>
+      </c>
+      <c r="E6" s="27">
         <f>E5*Assumptions!D26</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="27" t="str">
+        <v>1693196.4</v>
+      </c>
+      <c r="F6" s="27">
         <f>F5*Assumptions!D26</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="27" t="str">
+        <v>2016491.087625</v>
+      </c>
+      <c r="G6" s="27">
         <f>G5*Assumptions!D26</f>
-        <v>0</v>
+        <v>2245390.07595</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -3400,23 +3390,23 @@
       </c>
       <c r="C10" s="29">
         <f>C6+C7+C8+C9</f>
-        <v>995000</v>
+        <v>1992500</v>
       </c>
       <c r="D10" s="29">
         <f>D6+D7+D8+D9</f>
-        <v>1306880</v>
+        <v>2642532.5</v>
       </c>
       <c r="E10" s="29">
         <f>E6+E7+E8+E9</f>
-        <v>1636644.8</v>
+        <v>3329841.2</v>
       </c>
       <c r="F10" s="29">
         <f>F6+F7+F8+F9</f>
-        <v>1934821.354</v>
+        <v>3951312.441625</v>
       </c>
       <c r="G10" s="29">
         <f>G6+G7+G8+G9</f>
-        <v>2145936.2104</v>
+        <v>4391326.28635</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -3752,25 +3742,25 @@
       <c r="B6" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="27" t="str">
+      <c r="C6" s="27">
         <f>Drivers!C6</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="27" t="str">
+        <v>997500</v>
+      </c>
+      <c r="D6" s="27">
         <f>Drivers!D6</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="27" t="str">
+        <v>1335652.5</v>
+      </c>
+      <c r="E6" s="27">
         <f>Drivers!E6</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="27" t="str">
+        <v>1693196.4</v>
+      </c>
+      <c r="F6" s="27">
         <f>Drivers!F6</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="27" t="str">
+        <v>2016491.087625</v>
+      </c>
+      <c r="G6" s="27">
         <f>Drivers!G6</f>
-        <v>0</v>
+        <v>2245390.07595</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -3854,23 +3844,23 @@
       </c>
       <c r="C10" s="29">
         <f>Drivers!C10</f>
-        <v>995000</v>
+        <v>1992500</v>
       </c>
       <c r="D10" s="29">
         <f>Drivers!D10</f>
-        <v>1306880</v>
+        <v>2642532.5</v>
       </c>
       <c r="E10" s="29">
         <f>Drivers!E10</f>
-        <v>1636644.8</v>
+        <v>3329841.2</v>
       </c>
       <c r="F10" s="29">
         <f>Drivers!F10</f>
-        <v>1934821.354</v>
+        <v>3951312.441625</v>
       </c>
       <c r="G10" s="29">
         <f>Drivers!G10</f>
-        <v>2145936.2104</v>
+        <v>4391326.28635</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -3954,48 +3944,48 @@
       </c>
       <c r="C16" s="30">
         <f>C10-C15</f>
-        <v>-100866.66666667</v>
-      </c>
-      <c r="D16" s="31">
+        <v>896633.33333333</v>
+      </c>
+      <c r="D16" s="30">
         <f>D10-D15</f>
-        <v>20822</v>
-      </c>
-      <c r="E16" s="31">
+        <v>1356474.5</v>
+      </c>
+      <c r="E16" s="30">
         <f>E10-E15</f>
-        <v>74618.076</v>
-      </c>
-      <c r="F16" s="31">
+        <v>1767814.476</v>
+      </c>
+      <c r="F16" s="30">
         <f>F10-F15</f>
-        <v>110549.10470327</v>
-      </c>
-      <c r="G16" s="31">
+        <v>2127040.19232827</v>
+      </c>
+      <c r="G16" s="30">
         <f>G10-G15</f>
-        <v>22780.19693646</v>
+        <v>2268170.27288646</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="31">
         <f>IF(C10&gt;0,C16/C10,0)</f>
-        <v>-0.10137353</v>
-      </c>
-      <c r="D17" s="32">
+        <v>0.45000418</v>
+      </c>
+      <c r="D17" s="31">
         <f>IF(D10&gt;0,D16/D10,0)</f>
-        <v>0.0159326</v>
-      </c>
-      <c r="E17" s="32">
+        <v>0.51332368</v>
+      </c>
+      <c r="E17" s="31">
         <f>IF(E10&gt;0,E16/E10,0)</f>
-        <v>0.0455921</v>
-      </c>
-      <c r="F17" s="32">
+        <v>0.53090054</v>
+      </c>
+      <c r="F17" s="31">
         <f>IF(F10&gt;0,F16/F10,0)</f>
-        <v>0.0571366</v>
-      </c>
-      <c r="G17" s="32">
+        <v>0.53831233</v>
+      </c>
+      <c r="G17" s="31">
         <f>IF(G10&gt;0,G16/G10,0)</f>
-        <v>0.01061551</v>
+        <v>0.51651144</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -4029,81 +4019,81 @@
       </c>
       <c r="C21" s="30">
         <f>C16-C19</f>
-        <v>-159931.05983267</v>
+        <v>837568.94016733</v>
       </c>
       <c r="D21" s="30">
         <f>D16-D19</f>
-        <v>-38242.39316601</v>
-      </c>
-      <c r="E21" s="31">
+        <v>1297410.10683399</v>
+      </c>
+      <c r="E21" s="30">
         <f>E16-E19</f>
-        <v>15553.68283399</v>
-      </c>
-      <c r="F21" s="31">
+        <v>1708750.08283399</v>
+      </c>
+      <c r="F21" s="30">
         <f>F16-F19</f>
-        <v>51484.71153726</v>
+        <v>2067975.79916226</v>
       </c>
       <c r="G21" s="30">
         <f>G16-G19</f>
-        <v>-36284.19622955</v>
+        <v>2209105.87972045</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="31">
         <f>IF(C10&gt;0,C21/C10,0)</f>
-        <v>-0.16073473</v>
-      </c>
-      <c r="D22" s="32">
+        <v>0.42036082</v>
+      </c>
+      <c r="D22" s="31">
         <f>IF(D10&gt;0,D21/D10,0)</f>
-        <v>-0.02926236</v>
-      </c>
-      <c r="E22" s="32">
+        <v>0.49097224</v>
+      </c>
+      <c r="E22" s="31">
         <f>IF(E10&gt;0,E21/E10,0)</f>
-        <v>0.0095034</v>
-      </c>
-      <c r="F22" s="32">
+        <v>0.51316263</v>
+      </c>
+      <c r="F22" s="31">
         <f>IF(F10&gt;0,F21/F10,0)</f>
-        <v>0.02660954</v>
-      </c>
-      <c r="G22" s="32">
+        <v>0.52336428</v>
+      </c>
+      <c r="G22" s="31">
         <f>IF(G10&gt;0,G21/G10,0)</f>
-        <v>-0.01690833</v>
+        <v>0.5030612</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C24" s="32">
         <f>C21</f>
-        <v>-159931.05983267</v>
-      </c>
-      <c r="D24" s="33">
+        <v>837568.94016733</v>
+      </c>
+      <c r="D24" s="32">
         <f>C24+D21</f>
-        <v>-198173.45299868</v>
-      </c>
-      <c r="E24" s="33">
+        <v>2134979.04700132</v>
+      </c>
+      <c r="E24" s="32">
         <f>D24+E21</f>
-        <v>-182619.77016469</v>
-      </c>
-      <c r="F24" s="33">
+        <v>3843729.12983531</v>
+      </c>
+      <c r="F24" s="32">
         <f>E24+F21</f>
-        <v>-131135.05862743</v>
-      </c>
-      <c r="G24" s="33">
+        <v>5911704.92899757</v>
+      </c>
+      <c r="G24" s="32">
         <f>F24+G21</f>
-        <v>-167419.25485698</v>
+        <v>8120810.80871802</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C25" s="34" t="s">
-        <v>7</v>
+      <c r="C25" s="33" t="s">
+        <v>130</v>
       </c>
       <c r="D25" s="34" t="s">
         <v>7</v>
@@ -4146,7 +4136,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4174,57 +4164,57 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="33">
+        <v>132</v>
+      </c>
+      <c r="C4" s="32">
         <f>Assumptions!D57</f>
         <v>75000</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="32">
         <f>C16</f>
-        <v>-84931.05983267</v>
-      </c>
-      <c r="E4" s="33">
+        <v>912568.94016733</v>
+      </c>
+      <c r="E4" s="32">
         <f>D16</f>
-        <v>-123173.45299868</v>
-      </c>
-      <c r="F4" s="33">
+        <v>2209979.04700132</v>
+      </c>
+      <c r="F4" s="32">
         <f>E16</f>
-        <v>-107619.77016469</v>
-      </c>
-      <c r="G4" s="33">
+        <v>3918729.12983531</v>
+      </c>
+      <c r="G4" s="32">
         <f>F16</f>
-        <v>-56135.05862743</v>
+        <v>5986704.92899757</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C5" s="27">
         <f>'5-Year P&amp;L'!C16</f>
-        <v>-100866.66666667</v>
+        <v>896633.33333333</v>
       </c>
       <c r="D5" s="27">
         <f>'5-Year P&amp;L'!D16</f>
-        <v>20822</v>
+        <v>1356474.5</v>
       </c>
       <c r="E5" s="27">
         <f>'5-Year P&amp;L'!E16</f>
-        <v>74618.076</v>
+        <v>1767814.476</v>
       </c>
       <c r="F5" s="27">
         <f>'5-Year P&amp;L'!F16</f>
-        <v>110549.10470327</v>
+        <v>2127040.19232827</v>
       </c>
       <c r="G5" s="27">
         <f>'5-Year P&amp;L'!G16</f>
-        <v>22780.19693646</v>
+        <v>2268170.27288646</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C7" s="27">
         <f>Assumptions!D58</f>
@@ -4249,7 +4239,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C8" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -4274,7 +4264,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C9" s="29">
         <f>C7+C8</f>
@@ -4299,102 +4289,102 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C11" s="35">
         <f>IF(C9&gt;0,C5/C9,IF(C5&gt;0,99.9,0))</f>
-        <v>-1.70774068</v>
+        <v>15.18060688</v>
       </c>
       <c r="D11" s="35">
         <f>IF(D9&gt;0,D5/D9,IF(D5&gt;0,99.9,0))</f>
-        <v>0.3525305</v>
-      </c>
-      <c r="E11" s="36">
+        <v>22.96602788</v>
+      </c>
+      <c r="E11" s="35">
         <f>IF(E9&gt;0,E5/E9,IF(E5&gt;0,99.9,0))</f>
-        <v>1.26333434</v>
-      </c>
-      <c r="F11" s="36">
+        <v>29.93029101</v>
+      </c>
+      <c r="F11" s="35">
         <f>IF(F9&gt;0,F5/F9,IF(F5&gt;0,99.9,0))</f>
-        <v>1.87167088</v>
+        <v>36.0122246</v>
       </c>
       <c r="G11" s="35">
         <f>IF(G9&gt;0,G5/G9,IF(G5&gt;0,99.9,0))</f>
-        <v>0.38568409</v>
+        <v>38.40165202</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="25" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C13" s="27">
         <f>C5-C9</f>
-        <v>-159931.05983267</v>
+        <v>837568.94016733</v>
       </c>
       <c r="D13" s="27">
         <f>D5-D9</f>
-        <v>-38242.39316601</v>
+        <v>1297410.10683399</v>
       </c>
       <c r="E13" s="27">
         <f>E5-E9</f>
-        <v>15553.68283399</v>
+        <v>1708750.08283399</v>
       </c>
       <c r="F13" s="27">
         <f>F5-F9</f>
-        <v>51484.71153726</v>
+        <v>2067975.79916226</v>
       </c>
       <c r="G13" s="27">
         <f>G5-G9</f>
-        <v>-36284.19622955</v>
+        <v>2209105.87972045</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="C14" s="33">
+        <v>139</v>
+      </c>
+      <c r="C14" s="32">
         <f>C5-C9</f>
-        <v>-159931.05983267</v>
-      </c>
-      <c r="D14" s="33">
+        <v>837568.94016733</v>
+      </c>
+      <c r="D14" s="32">
         <f>D5-D9</f>
-        <v>-38242.39316601</v>
-      </c>
-      <c r="E14" s="33">
+        <v>1297410.10683399</v>
+      </c>
+      <c r="E14" s="32">
         <f>E5-E9</f>
-        <v>15553.68283399</v>
-      </c>
-      <c r="F14" s="33">
+        <v>1708750.08283399</v>
+      </c>
+      <c r="F14" s="32">
         <f>F5-F9</f>
-        <v>51484.71153726</v>
-      </c>
-      <c r="G14" s="33">
+        <v>2067975.79916226</v>
+      </c>
+      <c r="G14" s="32">
         <f>G5-G9</f>
-        <v>-36284.19622955</v>
+        <v>2209105.87972045</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="30">
         <f>C4+C14</f>
-        <v>-84931.05983267</v>
+        <v>912568.94016733</v>
       </c>
       <c r="D16" s="30">
         <f>D4+D14</f>
-        <v>-123173.45299868</v>
+        <v>2209979.04700132</v>
       </c>
       <c r="E16" s="30">
         <f>E4+E14</f>
-        <v>-107619.77016469</v>
+        <v>3918729.12983531</v>
       </c>
       <c r="F16" s="30">
         <f>F4+F14</f>
-        <v>-56135.05862743</v>
+        <v>5986704.92899757</v>
       </c>
       <c r="G16" s="30">
         <f>G4+G14</f>
-        <v>-92419.25485698</v>
+        <v>8195810.80871802</v>
       </c>
     </row>
   </sheetData>
@@ -4425,7 +4415,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4453,7 +4443,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C4" s="26">
         <f>Drivers!C12</f>
@@ -4478,7 +4468,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C5" s="26">
         <f>Assumptions!D35</f>
@@ -4503,25 +4493,25 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="37">
+        <v>144</v>
+      </c>
+      <c r="C6" s="36">
         <f>C4+C5</f>
         <v>14</v>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="36">
         <f>D4+D5</f>
         <v>16</v>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="36">
         <f>E4+E5</f>
         <v>19</v>
       </c>
-      <c r="F6" s="37">
+      <c r="F6" s="36">
         <f>F4+F5</f>
         <v>21</v>
       </c>
-      <c r="G6" s="37">
+      <c r="G6" s="36">
         <f>G4+G5</f>
         <v>23</v>
       </c>
@@ -4554,13 +4544,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C3" s="27">
         <f>Assumptions!D59</f>
@@ -4569,9 +4559,9 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="C4" s="32">
+        <v>147</v>
+      </c>
+      <c r="C4" s="31">
         <f>Assumptions!D60</f>
         <v>0.065</v>
       </c>
@@ -4587,20 +4577,20 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="33">
+        <v>148</v>
+      </c>
+      <c r="C6" s="32">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>34064.39316601</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C8" s="35">
         <f>'Cash Flow &amp; DSCR'!C11</f>
-        <v>-1.70774068</v>
+        <v>15.18060688</v>
       </c>
     </row>
   </sheetData>
@@ -4631,7 +4621,7 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C1" s="13"/>
     </row>
@@ -4664,7 +4654,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C6" s="25">
         <f>Assumptions!D8</f>
@@ -4682,58 +4672,58 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C9" s="27">
         <f>Drivers!G10</f>
-        <v>2145936.2104</v>
+        <v>4391326.28635</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="C10" s="38">
+        <v>153</v>
+      </c>
+      <c r="C10" s="37">
         <f>'5-Year P&amp;L'!G16</f>
-        <v>22780.19693646</v>
+        <v>2268170.27288646</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="39" t="s">
-        <v>153</v>
+      <c r="B12" s="38" t="s">
+        <v>154</v>
       </c>
       <c r="C12" s="23"/>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" s="40">
+        <v>155</v>
+      </c>
+      <c r="C13" s="39">
         <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
-        <v>-0.01690833</v>
+        <v>0.5030612</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="32">
+        <v>156</v>
+      </c>
+      <c r="C14" s="31">
         <f>IF(Drivers!G10&gt;0,Drivers!G16/Drivers!G10,0)</f>
-        <v>0.66686369</v>
+        <v>0.32588035</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="25" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C15" s="27">
         <f>IF(Assumptions!D16&gt;0,Drivers!G10/Assumptions!D16,0)</f>
-        <v>10730</v>
+        <v>21957</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C16" s="27">
         <f>IF(Assumptions!D16&gt;0,('5-Year P&amp;L'!G12+'5-Year P&amp;L'!G13)/Assumptions!D16,0)</f>
@@ -4742,33 +4732,33 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="25" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C17" s="35">
         <f>'Cash Flow &amp; DSCR'!C11</f>
-        <v>-1.70774068</v>
+        <v>15.18060688</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C18" s="35">
         <f>'Cash Flow &amp; DSCR'!G11</f>
-        <v>0.38568409</v>
+        <v>38.40165202</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="C19" s="41">
-        <v>0</v>
+        <v>161</v>
+      </c>
+      <c r="C19" s="40">
+        <v>304</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C21" s="12"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Private_School_+_ESA.xlsx
@@ -10,18 +10,20 @@
     <sheet sheetId="4" name="Drivers" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="5-Year P&amp;L" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Cash Flow &amp; DSCR" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Staffing" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Loan Snapshot" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Summary" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Decision History" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Financial Health" state="visible" r:id="rId14"/>
+    <sheet sheetId="7" name="AR &amp; Restricted Recon" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Staffing" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Loan Snapshot" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Summary" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Stress Tests" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Decision History" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Financial Health" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="259">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -29,7 +31,7 @@
     <t>Heritage Academy</t>
   </si>
   <si>
-    <t>Generated May 7, 2026 · nonprofit_501c3</t>
+    <t>Generated May 9, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -143,7 +145,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -398,7 +400,10 @@
     <t>Operating Margin</t>
   </si>
   <si>
-    <t>Capital &amp; Debt Service</t>
+    <t>Interest Expense</t>
+  </si>
+  <si>
+    <t>Principal &amp; Capital Outlays</t>
   </si>
   <si>
     <t>Net Income</t>
@@ -446,6 +451,42 @@
     <t>Ending Cash</t>
   </si>
   <si>
+    <t>AR Schedule &amp; Restricted-vs-Unrestricted Cash Recon</t>
+  </si>
+  <si>
+    <t>AR = year's collected tuition × 30-day weighted delay ÷ 365. Bad debt = contracted − collected.</t>
+  </si>
+  <si>
+    <t>Accounts Receivable Schedule</t>
+  </si>
+  <si>
+    <t>Contracted Tuition (gross)</t>
+  </si>
+  <si>
+    <t>Collected Tuition (cash-basis)</t>
+  </si>
+  <si>
+    <t>Bad Debt (contracted − collected)</t>
+  </si>
+  <si>
+    <t>Year-end AR Balance (30-day delay)</t>
+  </si>
+  <si>
+    <t>Restricted vs Unrestricted Cash</t>
+  </si>
+  <si>
+    <t>Total Cash Position (accrual)</t>
+  </si>
+  <si>
+    <t>Restricted Cash (capital/program-restricted)</t>
+  </si>
+  <si>
+    <t>Unrestricted Cash (DSCR/runway basis)</t>
+  </si>
+  <si>
+    <t>Note: DSCR and cash-runway covenants in this packet are computed off Unrestricted Cash (row 14). Restricted gifts cannot legally service debt and are excluded from coverage tests.</t>
+  </si>
+  <si>
     <t>Staffing Detail</t>
   </si>
   <si>
@@ -512,6 +553,75 @@
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
+    <t>Standard Lender Stress Tests</t>
+  </si>
+  <si>
+    <t>Five fixed downside scenarios re-run on the canonical engine. Identical figures appear on the founder dashboard, consultant view, and lender packet PDF.</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Δ vs Base (Y1)</t>
+  </si>
+  <si>
+    <t>Base Case</t>
+  </si>
+  <si>
+    <t>Canonical engine output. All scenarios below are deltas vs this row.</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
+    <t>Break-Even Students</t>
+  </si>
+  <si>
+    <t>Cash Runway (mo)</t>
+  </si>
+  <si>
+    <t>Break-Even Year</t>
+  </si>
+  <si>
+    <t>Enrollment -10%</t>
+  </si>
+  <si>
+    <t>All five enrollment years scaled down by 10% — the standard lender enrollment-miss sensitivity.</t>
+  </si>
+  <si>
+    <t>0y</t>
+  </si>
+  <si>
+    <t>Enrollment -20%</t>
+  </si>
+  <si>
+    <t>All five enrollment years scaled down by 20% — the stretch downside lenders use to confirm the school can survive a soft-launch.</t>
+  </si>
+  <si>
+    <t>ESA / Public Funding Delayed 3 Months</t>
+  </si>
+  <si>
+    <t>Year-1 ESA, school-choice, and public-funding receipts reduced by 25% (≈ 3 months delayed) to simulate a slow first disbursement.</t>
+  </si>
+  <si>
+    <t>Rent Shock +25%</t>
+  </si>
+  <si>
+    <t>Occupancy &amp; facility expense rows escalated by 25% — covers a lease renewal, market-rate reset, or unbudgeted CAM/utilities surprise.</t>
+  </si>
+  <si>
+    <t>Founder Comp Normalized to Market</t>
+  </si>
+  <si>
+    <t>Founder compensation re-cast at the market-rate benchmark (with benefits + payroll tax). The lender / board view of true operating cost.</t>
+  </si>
+  <si>
     <t>Decision History</t>
   </si>
   <si>
@@ -533,9 +643,6 @@
     <t>○ Red = action needed</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
     <t>Benchmark</t>
   </si>
   <si>
@@ -591,9 +698,6 @@
   </si>
   <si>
     <t>≥ 3 sources</t>
-  </si>
-  <si>
-    <t>DSCR</t>
   </si>
   <si>
     <t>≥ 1.25x</t>
@@ -708,7 +812,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -810,6 +914,18 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFD97706"/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -861,12 +977,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4EC"/>
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF8E1"/>
+        <fgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -939,7 +1055,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1006,6 +1122,13 @@
     <xf numFmtId="167" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="16" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1019,15 +1142,43 @@
     <xf numFmtId="3" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1048,10 +1199,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1061,7 +1212,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1773,6 +1924,1345 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B1:C21"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="25" t="str">
+        <f>Assumptions!D5</f>
+        <v>Heritage Academy</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="25" t="str">
+        <f>Assumptions!D7</f>
+        <v>Private School</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="25" t="str">
+        <f>Assumptions!D6</f>
+        <v>FL</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="25">
+        <f>Assumptions!D8</f>
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="26">
+        <f>Assumptions!D16</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C9" s="27">
+        <f>Drivers!G10</f>
+        <v>4391326.28635</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="C10" s="40">
+        <f>'5-Year P&amp;L'!G16</f>
+        <v>2268170.27288646</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="41" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="23"/>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="42">
+        <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
+        <v>0.5030612</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C14" s="31">
+        <f>IF(Drivers!G10&gt;0,Drivers!G16/Drivers!G10,0)</f>
+        <v>0.32588035</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="27">
+        <f>IF(Assumptions!D16&gt;0,Drivers!G10/Assumptions!D16,0)</f>
+        <v>21957</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="27">
+        <f>IF(Assumptions!D16&gt;0,('5-Year P&amp;L'!G12+'5-Year P&amp;L'!G13)/Assumptions!D16,0)</f>
+        <v>10616</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C17" s="35">
+        <f>'Cash Flow &amp; DSCR'!C11</f>
+        <v>15.18060688</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="35">
+        <f>'Cash Flow &amp; DSCR'!G11</f>
+        <v>38.40165202</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" s="43">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C21" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B21:C21"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFD97706"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H57"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="8" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="45" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="G4" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="48" t="s">
+        <v>181</v>
+      </c>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="49" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="27">
+        <v>737263.6068339921</v>
+      </c>
+      <c r="D7" s="27">
+        <v>1333094.106833992</v>
+      </c>
+      <c r="E7" s="27">
+        <v>1947205.806833992</v>
+      </c>
+      <c r="F7" s="27">
+        <v>2505582.952833992</v>
+      </c>
+      <c r="G7" s="27">
+        <v>2893078.708213992</v>
+      </c>
+      <c r="H7" s="50" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8" s="51">
+        <v>22.64</v>
+      </c>
+      <c r="D8" s="26">
+        <v>40.13</v>
+      </c>
+      <c r="E8" s="26">
+        <v>58.16</v>
+      </c>
+      <c r="F8" s="26">
+        <v>74.55</v>
+      </c>
+      <c r="G8" s="26">
+        <v>85.93</v>
+      </c>
+      <c r="H8" s="50" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" s="27">
+        <v>812263.6068339921</v>
+      </c>
+      <c r="D9" s="27">
+        <v>2145357.713667984</v>
+      </c>
+      <c r="E9" s="27">
+        <v>4092563.520501976</v>
+      </c>
+      <c r="F9" s="27">
+        <v>6598146.473335968</v>
+      </c>
+      <c r="G9" s="27">
+        <v>9491225.18154996</v>
+      </c>
+      <c r="H9" s="50" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="26">
+        <v>59</v>
+      </c>
+      <c r="D10" s="26">
+        <v>58</v>
+      </c>
+      <c r="E10" s="26">
+        <v>57</v>
+      </c>
+      <c r="F10" s="26">
+        <v>56</v>
+      </c>
+      <c r="G10" s="26">
+        <v>55</v>
+      </c>
+      <c r="H10" s="50" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="26">
+        <v>60</v>
+      </c>
+      <c r="D11" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="53" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="50" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="27">
+        <v>562513.6068339921</v>
+      </c>
+      <c r="D16" s="27">
+        <v>1099246.856833992</v>
+      </c>
+      <c r="E16" s="27">
+        <v>1650917.806833992</v>
+      </c>
+      <c r="F16" s="27">
+        <v>2162443.5528339916</v>
+      </c>
+      <c r="G16" s="27">
+        <v>2500596.708213992</v>
+      </c>
+      <c r="H16" s="32">
+        <v>-174750</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C17" s="51">
+        <v>17.51</v>
+      </c>
+      <c r="D17" s="26">
+        <v>33.27</v>
+      </c>
+      <c r="E17" s="26">
+        <v>49.46</v>
+      </c>
+      <c r="F17" s="26">
+        <v>64.48</v>
+      </c>
+      <c r="G17" s="26">
+        <v>74.41</v>
+      </c>
+      <c r="H17" s="53">
+        <v>-5.129999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="27">
+        <v>637513.6068339921</v>
+      </c>
+      <c r="D18" s="27">
+        <v>1736760.4636679841</v>
+      </c>
+      <c r="E18" s="27">
+        <v>3387678.270501976</v>
+      </c>
+      <c r="F18" s="27">
+        <v>5550121.823335968</v>
+      </c>
+      <c r="G18" s="27">
+        <v>8050718.53154996</v>
+      </c>
+      <c r="H18" s="32">
+        <v>-174750</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C19" s="26">
+        <v>58</v>
+      </c>
+      <c r="D19" s="26">
+        <v>58</v>
+      </c>
+      <c r="E19" s="26">
+        <v>57</v>
+      </c>
+      <c r="F19" s="26">
+        <v>56</v>
+      </c>
+      <c r="G19" s="26">
+        <v>55</v>
+      </c>
+      <c r="H19" s="53">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C20" s="26">
+        <v>60</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H20" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="50" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="48" t="s">
+        <v>191</v>
+      </c>
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="49"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="27">
+        <v>387763.60683399206</v>
+      </c>
+      <c r="D25" s="27">
+        <v>865399.6068339921</v>
+      </c>
+      <c r="E25" s="27">
+        <v>1354629.806833992</v>
+      </c>
+      <c r="F25" s="27">
+        <v>1800240.8528339919</v>
+      </c>
+      <c r="G25" s="27">
+        <v>2108114.708213992</v>
+      </c>
+      <c r="H25" s="32">
+        <v>-349500</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C26" s="51">
+        <v>12.38</v>
+      </c>
+      <c r="D26" s="26">
+        <v>26.4</v>
+      </c>
+      <c r="E26" s="26">
+        <v>40.77</v>
+      </c>
+      <c r="F26" s="26">
+        <v>53.85</v>
+      </c>
+      <c r="G26" s="26">
+        <v>62.89</v>
+      </c>
+      <c r="H26" s="53">
+        <v>-10.26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" s="27">
+        <v>462763.60683399206</v>
+      </c>
+      <c r="D27" s="27">
+        <v>1328163.2136679841</v>
+      </c>
+      <c r="E27" s="27">
+        <v>2682793.020501976</v>
+      </c>
+      <c r="F27" s="27">
+        <v>4483033.873335968</v>
+      </c>
+      <c r="G27" s="27">
+        <v>6591148.581549959</v>
+      </c>
+      <c r="H27" s="32">
+        <v>-349500</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="26">
+        <v>58</v>
+      </c>
+      <c r="D28" s="26">
+        <v>58</v>
+      </c>
+      <c r="E28" s="26">
+        <v>57</v>
+      </c>
+      <c r="F28" s="26">
+        <v>56</v>
+      </c>
+      <c r="G28" s="26">
+        <v>55</v>
+      </c>
+      <c r="H28" s="53">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="26">
+        <v>60</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H29" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="D30" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H30" s="50" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="48"/>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="B33" s="49"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="27">
+        <v>519763.60683399206</v>
+      </c>
+      <c r="D34" s="27">
+        <v>1333094.106833992</v>
+      </c>
+      <c r="E34" s="27">
+        <v>1947205.806833992</v>
+      </c>
+      <c r="F34" s="27">
+        <v>2505582.952833992</v>
+      </c>
+      <c r="G34" s="27">
+        <v>2893078.708213992</v>
+      </c>
+      <c r="H34" s="32">
+        <v>-217500</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C35" s="51">
+        <v>16.26</v>
+      </c>
+      <c r="D35" s="26">
+        <v>40.13</v>
+      </c>
+      <c r="E35" s="26">
+        <v>58.16</v>
+      </c>
+      <c r="F35" s="26">
+        <v>74.55</v>
+      </c>
+      <c r="G35" s="26">
+        <v>85.93</v>
+      </c>
+      <c r="H35" s="53">
+        <v>-6.379999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" s="27">
+        <v>594763.6068339921</v>
+      </c>
+      <c r="D36" s="27">
+        <v>1927857.7136679841</v>
+      </c>
+      <c r="E36" s="27">
+        <v>3875063.520501976</v>
+      </c>
+      <c r="F36" s="27">
+        <v>6380646.473335968</v>
+      </c>
+      <c r="G36" s="27">
+        <v>9273725.18154996</v>
+      </c>
+      <c r="H36" s="32">
+        <v>-217500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" s="26">
+        <v>67</v>
+      </c>
+      <c r="D37" s="26">
+        <v>58</v>
+      </c>
+      <c r="E37" s="26">
+        <v>57</v>
+      </c>
+      <c r="F37" s="26">
+        <v>56</v>
+      </c>
+      <c r="G37" s="26">
+        <v>55</v>
+      </c>
+      <c r="H37" s="53">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C38" s="26">
+        <v>60</v>
+      </c>
+      <c r="D38" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H38" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="C39" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H39" s="50" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="B41" s="48"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="B42" s="49"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="49"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="27">
+        <v>703163.6068339921</v>
+      </c>
+      <c r="D43" s="27">
+        <v>1297971.106833992</v>
+      </c>
+      <c r="E43" s="27">
+        <v>1911029.356833992</v>
+      </c>
+      <c r="F43" s="27">
+        <v>2468321.664333992</v>
+      </c>
+      <c r="G43" s="27">
+        <v>2854700.733558992</v>
+      </c>
+      <c r="H43" s="32">
+        <v>-34100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C44" s="51">
+        <v>21.64</v>
+      </c>
+      <c r="D44" s="26">
+        <v>39.1</v>
+      </c>
+      <c r="E44" s="26">
+        <v>57.1</v>
+      </c>
+      <c r="F44" s="26">
+        <v>73.46</v>
+      </c>
+      <c r="G44" s="26">
+        <v>84.8</v>
+      </c>
+      <c r="H44" s="53">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" s="27">
+        <v>778163.6068339921</v>
+      </c>
+      <c r="D45" s="27">
+        <v>2076134.7136679841</v>
+      </c>
+      <c r="E45" s="27">
+        <v>3987164.070501976</v>
+      </c>
+      <c r="F45" s="27">
+        <v>6455485.734835968</v>
+      </c>
+      <c r="G45" s="27">
+        <v>9310186.468394961</v>
+      </c>
+      <c r="H45" s="32">
+        <v>-34100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C46" s="26">
+        <v>61</v>
+      </c>
+      <c r="D46" s="26">
+        <v>60</v>
+      </c>
+      <c r="E46" s="26">
+        <v>59</v>
+      </c>
+      <c r="F46" s="26">
+        <v>58</v>
+      </c>
+      <c r="G46" s="26">
+        <v>57</v>
+      </c>
+      <c r="H46" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C47" s="26">
+        <v>60</v>
+      </c>
+      <c r="D47" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H47" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="C48" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="D48" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H48" s="50" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="B50" s="48"/>
+      <c r="C50" s="48"/>
+      <c r="D50" s="48"/>
+      <c r="E50" s="48"/>
+      <c r="F50" s="48"/>
+      <c r="G50" s="48"/>
+      <c r="H50" s="48"/>
+    </row>
+    <row r="51" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="B51" s="49"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="49"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
+      <c r="G51" s="49"/>
+      <c r="H51" s="49"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" s="27">
+        <v>677571.1068339921</v>
+      </c>
+      <c r="D52" s="27">
+        <v>1273401.606833992</v>
+      </c>
+      <c r="E52" s="27">
+        <v>1834453.306833992</v>
+      </c>
+      <c r="F52" s="27">
+        <v>2392830.452833992</v>
+      </c>
+      <c r="G52" s="27">
+        <v>2780326.208213992</v>
+      </c>
+      <c r="H52" s="32">
+        <v>-59692.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C53" s="51">
+        <v>20.89</v>
+      </c>
+      <c r="D53" s="26">
+        <v>38.38</v>
+      </c>
+      <c r="E53" s="26">
+        <v>54.85</v>
+      </c>
+      <c r="F53" s="26">
+        <v>71.24</v>
+      </c>
+      <c r="G53" s="26">
+        <v>82.62</v>
+      </c>
+      <c r="H53" s="53">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C54" s="27">
+        <v>812263.6068339921</v>
+      </c>
+      <c r="D54" s="27">
+        <v>2145357.713667984</v>
+      </c>
+      <c r="E54" s="27">
+        <v>4092563.520501976</v>
+      </c>
+      <c r="F54" s="27">
+        <v>6598146.473335968</v>
+      </c>
+      <c r="G54" s="27">
+        <v>9491225.18154996</v>
+      </c>
+      <c r="H54" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C55" s="26">
+        <v>59</v>
+      </c>
+      <c r="D55" s="26">
+        <v>58</v>
+      </c>
+      <c r="E55" s="26">
+        <v>57</v>
+      </c>
+      <c r="F55" s="26">
+        <v>56</v>
+      </c>
+      <c r="G55" s="26">
+        <v>55</v>
+      </c>
+      <c r="H55" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C56" s="26">
+        <v>60</v>
+      </c>
+      <c r="D56" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H56" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="C57" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="D57" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F57" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="G57" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H57" s="50" t="s">
+        <v>190</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A51:H51"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1788,7 +3278,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -1798,26 +3288,26 @@
       <c r="H1" s="13"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
+      <c r="B2" s="55" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="42" t="s">
-        <v>165</v>
-      </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
+      <c r="B4" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1833,7 +3323,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF328555"/>
@@ -1851,7 +3341,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1874,37 +3364,37 @@
       <c r="I3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D4" s="44" t="s">
-        <v>168</v>
-      </c>
-      <c r="F4" s="45" t="s">
-        <v>169</v>
+      <c r="B4" s="56" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="F4" s="58" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="C6" s="47" t="s">
+      <c r="B6" s="59" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="60" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="47" t="s">
+      <c r="E6" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="47" t="s">
+      <c r="F6" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="47" t="s">
+      <c r="G6" s="60" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="47" t="s">
-        <v>171</v>
+      <c r="H6" s="60" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1929,7 +3419,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="C8" s="27">
         <v>1992500</v>
@@ -1949,7 +3439,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="C9" s="27">
         <v>824466.6666666666</v>
@@ -1969,7 +3459,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="C10" s="27">
         <v>271400</v>
@@ -1989,7 +3479,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="C11" s="27">
         <v>59064.39316600799</v>
@@ -2009,7 +3499,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C12" s="30">
         <v>837568.9401673255</v>
@@ -2029,7 +3519,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C13" s="30">
         <v>912568.9401673255</v>
@@ -2049,50 +3539,50 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="48">
+        <v>128</v>
+      </c>
+      <c r="C14" s="61">
         <v>0.42036082317055234</v>
       </c>
-      <c r="D14" s="48">
+      <c r="D14" s="61">
         <v>0.49097224228424513</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="61">
         <v>0.5131626345526604</v>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="61">
         <v>0.523364282048977</v>
       </c>
-      <c r="G14" s="48">
+      <c r="G14" s="61">
         <v>0.5030612019396584</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
-        <v>176</v>
-      </c>
-      <c r="C15" s="49">
+        <v>211</v>
+      </c>
+      <c r="C15" s="62">
         <v>19925</v>
       </c>
-      <c r="D15" s="49">
+      <c r="D15" s="62">
         <v>20327.173076923078</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="62">
         <v>20811.5075</v>
       </c>
-      <c r="F15" s="49">
+      <c r="F15" s="62">
         <v>21358.445630405404</v>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="62">
         <v>21956.63143175</v>
       </c>
-      <c r="H15" s="50" t="s">
-        <v>177</v>
+      <c r="H15" s="63" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="C16" s="32">
         <v>11549.310598326745</v>
@@ -2112,7 +3602,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="25" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="C17" s="27">
         <v>600</v>
@@ -2132,402 +3622,402 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="C18" s="49">
+        <v>215</v>
+      </c>
+      <c r="C18" s="62">
         <v>1364</v>
       </c>
-      <c r="D18" s="49">
+      <c r="D18" s="62">
         <v>1080.7076923076922</v>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="62">
         <v>904.4172499999999</v>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="62">
         <v>805.6646637837837</v>
       </c>
-      <c r="G18" s="49">
+      <c r="G18" s="62">
         <v>767.5970084200001</v>
       </c>
-      <c r="H18" s="50" t="s">
-        <v>181</v>
+      <c r="H18" s="63" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="C19" s="37">
+        <v>217</v>
+      </c>
+      <c r="C19" s="40">
         <v>8375.689401673255</v>
       </c>
-      <c r="D19" s="37">
+      <c r="D19" s="40">
         <v>9980.077744876862</v>
       </c>
-      <c r="E19" s="37">
+      <c r="E19" s="40">
         <v>10679.688017712451</v>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="40">
         <v>11178.247563039235</v>
       </c>
-      <c r="G19" s="37">
+      <c r="G19" s="40">
         <v>11045.529398602237</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="C20" s="48">
+        <v>218</v>
+      </c>
+      <c r="C20" s="61">
         <v>0.4137850271852781</v>
       </c>
-      <c r="D20" s="48">
+      <c r="D20" s="61">
         <v>0.3600765553498396</v>
       </c>
-      <c r="E20" s="48">
+      <c r="E20" s="61">
         <v>0.34179813740066645</v>
       </c>
-      <c r="F20" s="48">
+      <c r="F20" s="61">
         <v>0.32415096499091023</v>
       </c>
-      <c r="G20" s="48">
+      <c r="G20" s="61">
         <v>0.3258803472205957</v>
       </c>
-      <c r="H20" s="50" t="s">
-        <v>184</v>
+      <c r="H20" s="63" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="C21" s="48">
+        <v>220</v>
+      </c>
+      <c r="C21" s="61">
         <v>0.06845671267252196</v>
       </c>
-      <c r="D21" s="48">
+      <c r="D21" s="61">
         <v>0.05316566589058034</v>
       </c>
-      <c r="E21" s="48">
+      <c r="E21" s="61">
         <v>0.04345755587383566</v>
       </c>
-      <c r="F21" s="48">
+      <c r="F21" s="61">
         <v>0.03772112810666604</v>
       </c>
-      <c r="G21" s="48">
+      <c r="G21" s="61">
         <v>0.034959689094659116</v>
       </c>
-      <c r="H21" s="50" t="s">
-        <v>186</v>
+      <c r="H21" s="63" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="48">
+      <c r="C22" s="61">
         <v>0.45000418235048106</v>
       </c>
-      <c r="D22" s="48">
+      <c r="D22" s="61">
         <v>0.5133236771922389</v>
       </c>
-      <c r="E22" s="48">
+      <c r="E22" s="61">
         <v>0.5309005354369452</v>
       </c>
-      <c r="F22" s="48">
+      <c r="F22" s="61">
         <v>0.538312326284557</v>
       </c>
-      <c r="G22" s="48">
+      <c r="G22" s="61">
         <v>0.5165114420982191</v>
       </c>
-      <c r="H22" s="50" t="s">
-        <v>187</v>
+      <c r="H22" s="63" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="C23" s="51">
+        <v>223</v>
+      </c>
+      <c r="C23" s="64">
         <v>4</v>
       </c>
-      <c r="D23" s="51">
+      <c r="D23" s="64">
         <v>4</v>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="64">
         <v>4</v>
       </c>
-      <c r="F23" s="51">
+      <c r="F23" s="64">
         <v>4</v>
       </c>
-      <c r="G23" s="51">
+      <c r="G23" s="64">
         <v>4</v>
       </c>
-      <c r="H23" s="50" t="s">
-        <v>189</v>
+      <c r="H23" s="63" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="C24" s="52">
+        <v>184</v>
+      </c>
+      <c r="C24" s="65">
         <v>15.18060688125977</v>
       </c>
-      <c r="D24" s="52">
+      <c r="D24" s="65">
         <v>22.966027877192538</v>
       </c>
-      <c r="E24" s="52">
+      <c r="E24" s="65">
         <v>29.930291013594818</v>
       </c>
-      <c r="F24" s="52">
+      <c r="F24" s="65">
         <v>36.012224596127645</v>
       </c>
-      <c r="G24" s="52">
+      <c r="G24" s="65">
         <v>38.401652015817284</v>
       </c>
-      <c r="H24" s="50" t="s">
-        <v>191</v>
+      <c r="H24" s="63" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="28" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="C25" s="33" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D25" s="53" t="str">
+      <c r="D25" s="66" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="53" t="str">
+      <c r="E25" s="66" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="53" t="str">
+      <c r="F25" s="66" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="53" t="str">
+      <c r="G25" s="66" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="50" t="s">
+      <c r="H25" s="63" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="C26" s="54">
+        <v>227</v>
+      </c>
+      <c r="C26" s="67">
         <v>9</v>
       </c>
-      <c r="D26" s="55">
+      <c r="D26" s="68">
         <v>20</v>
       </c>
-      <c r="E26" s="51">
+      <c r="E26" s="64">
         <v>29</v>
       </c>
-      <c r="F26" s="51">
+      <c r="F26" s="64">
         <v>38</v>
       </c>
-      <c r="G26" s="51">
+      <c r="G26" s="64">
         <v>45</v>
       </c>
-      <c r="H26" s="50" t="s">
-        <v>194</v>
+      <c r="H26" s="63" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="C27" s="51">
+        <v>229</v>
+      </c>
+      <c r="C27" s="64">
         <v>288</v>
       </c>
-      <c r="D27" s="51">
+      <c r="D27" s="64">
         <v>600</v>
       </c>
-      <c r="E27" s="51">
+      <c r="E27" s="64">
         <v>882</v>
       </c>
-      <c r="F27" s="51">
+      <c r="F27" s="64">
         <v>1160</v>
       </c>
-      <c r="G27" s="51">
+      <c r="G27" s="64">
         <v>1371</v>
       </c>
-      <c r="H27" s="50" t="s">
-        <v>196</v>
+      <c r="H27" s="63" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="C29" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="D29" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46" t="s">
-        <v>200</v>
-      </c>
-      <c r="G29" s="46"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="46"/>
+      <c r="B29" s="59" t="s">
+        <v>231</v>
+      </c>
+      <c r="C29" s="59" t="s">
+        <v>232</v>
+      </c>
+      <c r="D29" s="59" t="s">
+        <v>233</v>
+      </c>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59" t="s">
+        <v>234</v>
+      </c>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="59"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="56" t="s">
-        <v>201</v>
+      <c r="B30" s="69" t="s">
+        <v>235</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="D30" s="57" t="s">
-        <v>203</v>
-      </c>
-      <c r="E30" s="57"/>
-      <c r="F30" s="58" t="s">
-        <v>204</v>
-      </c>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="58"/>
+        <v>236</v>
+      </c>
+      <c r="D30" s="70" t="s">
+        <v>237</v>
+      </c>
+      <c r="E30" s="70"/>
+      <c r="F30" s="71" t="s">
+        <v>238</v>
+      </c>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="56" t="s">
-        <v>205</v>
+      <c r="B31" s="69" t="s">
+        <v>239</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="D31" s="57" t="s">
-        <v>206</v>
-      </c>
-      <c r="E31" s="57"/>
-      <c r="F31" s="58" t="s">
-        <v>207</v>
-      </c>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
+        <v>236</v>
+      </c>
+      <c r="D31" s="70" t="s">
+        <v>240</v>
+      </c>
+      <c r="E31" s="70"/>
+      <c r="F31" s="71" t="s">
+        <v>241</v>
+      </c>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="56" t="s">
-        <v>208</v>
+      <c r="B32" s="69" t="s">
+        <v>242</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="D32" s="57" t="s">
-        <v>209</v>
-      </c>
-      <c r="E32" s="57"/>
-      <c r="F32" s="58" t="s">
-        <v>210</v>
-      </c>
-      <c r="G32" s="58"/>
-      <c r="H32" s="58"/>
-      <c r="I32" s="58"/>
+        <v>236</v>
+      </c>
+      <c r="D32" s="70" t="s">
+        <v>243</v>
+      </c>
+      <c r="E32" s="70"/>
+      <c r="F32" s="71" t="s">
+        <v>244</v>
+      </c>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="56" t="s">
-        <v>211</v>
+      <c r="B33" s="69" t="s">
+        <v>245</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="D33" s="57" t="s">
-        <v>212</v>
-      </c>
-      <c r="E33" s="57"/>
-      <c r="F33" s="58" t="s">
-        <v>213</v>
-      </c>
-      <c r="G33" s="58"/>
-      <c r="H33" s="58"/>
-      <c r="I33" s="58"/>
+        <v>236</v>
+      </c>
+      <c r="D33" s="70" t="s">
+        <v>246</v>
+      </c>
+      <c r="E33" s="70"/>
+      <c r="F33" s="71" t="s">
+        <v>247</v>
+      </c>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="56" t="s">
-        <v>214</v>
+      <c r="B34" s="69" t="s">
+        <v>248</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="D34" s="57" t="s">
-        <v>215</v>
-      </c>
-      <c r="E34" s="57"/>
-      <c r="F34" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="G34" s="58"/>
-      <c r="H34" s="58"/>
-      <c r="I34" s="58"/>
+        <v>236</v>
+      </c>
+      <c r="D34" s="70" t="s">
+        <v>249</v>
+      </c>
+      <c r="E34" s="70"/>
+      <c r="F34" s="71" t="s">
+        <v>250</v>
+      </c>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="56" t="s">
-        <v>217</v>
+      <c r="B35" s="69" t="s">
+        <v>251</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="D35" s="57" t="s">
-        <v>218</v>
-      </c>
-      <c r="E35" s="57"/>
-      <c r="F35" s="58" t="s">
-        <v>219</v>
-      </c>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
+        <v>236</v>
+      </c>
+      <c r="D35" s="70" t="s">
+        <v>252</v>
+      </c>
+      <c r="E35" s="70"/>
+      <c r="F35" s="71" t="s">
+        <v>253</v>
+      </c>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="56" t="s">
-        <v>220</v>
+      <c r="B36" s="69" t="s">
+        <v>254</v>
       </c>
       <c r="C36" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="D36" s="57" t="s">
-        <v>221</v>
-      </c>
-      <c r="E36" s="57"/>
-      <c r="F36" s="58" t="s">
-        <v>222</v>
-      </c>
-      <c r="G36" s="58"/>
-      <c r="H36" s="58"/>
-      <c r="I36" s="58"/>
+        <v>236</v>
+      </c>
+      <c r="D36" s="70" t="s">
+        <v>255</v>
+      </c>
+      <c r="E36" s="70"/>
+      <c r="F36" s="71" t="s">
+        <v>256</v>
+      </c>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="56" t="s">
+      <c r="B38" s="69" t="s">
         <v>39</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>223</v>
+        <v>257</v>
       </c>
       <c r="D38" s="28"/>
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="59" t="s">
-        <v>224</v>
-      </c>
-      <c r="C40" s="59"/>
-      <c r="D40" s="59"/>
-      <c r="E40" s="59"/>
-      <c r="F40" s="59"/>
-      <c r="G40" s="59"/>
-      <c r="H40" s="59"/>
-      <c r="I40" s="59"/>
+      <c r="B40" s="72" t="s">
+        <v>258</v>
+      </c>
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="72"/>
+      <c r="G40" s="72"/>
+      <c r="H40" s="72"/>
+      <c r="I40" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -3677,7 +5167,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G25"/>
+  <dimension ref="B1:G26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -3993,118 +5483,138 @@
         <v>125</v>
       </c>
       <c r="C19" s="27">
-        <f>'Cash Flow &amp; DSCR'!C9</f>
-        <v>59064.39316601</v>
+        <v>15710</v>
       </c>
       <c r="D19" s="27">
-        <f>'Cash Flow &amp; DSCR'!D9</f>
-        <v>59064.39316601</v>
+        <v>14480</v>
       </c>
       <c r="E19" s="27">
-        <f>'Cash Flow &amp; DSCR'!E9</f>
-        <v>59064.39316601</v>
+        <v>13169</v>
       </c>
       <c r="F19" s="27">
-        <f>'Cash Flow &amp; DSCR'!F9</f>
-        <v>59064.39316601</v>
+        <v>11769</v>
       </c>
       <c r="G19" s="27">
-        <f>'Cash Flow &amp; DSCR'!G9</f>
-        <v>59064.39316601</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="28" t="s">
+        <v>10276</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="C21" s="30">
-        <f>C16-C19</f>
+      <c r="C20" s="27">
+        <f>'Cash Flow &amp; DSCR'!C9-C19</f>
+        <v>43354.8138866</v>
+      </c>
+      <c r="D20" s="27">
+        <f>'Cash Flow &amp; DSCR'!D9-D19</f>
+        <v>44584.06976575</v>
+      </c>
+      <c r="E20" s="27">
+        <f>'Cash Flow &amp; DSCR'!E9-E19</f>
+        <v>45895.65118771</v>
+      </c>
+      <c r="F20" s="27">
+        <f>'Cash Flow &amp; DSCR'!F9-F19</f>
+        <v>47295.07164655</v>
+      </c>
+      <c r="G20" s="27">
+        <f>'Cash Flow &amp; DSCR'!G9-G19</f>
+        <v>48788.21388525</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="30">
+        <f>C16-C19-C20</f>
         <v>837568.94016733</v>
       </c>
-      <c r="D21" s="30">
-        <f>D16-D19</f>
+      <c r="D22" s="30">
+        <f>D16-D19-D20</f>
         <v>1297410.10683399</v>
       </c>
-      <c r="E21" s="30">
-        <f>E16-E19</f>
+      <c r="E22" s="30">
+        <f>E16-E19-E20</f>
         <v>1708750.08283399</v>
       </c>
-      <c r="F21" s="30">
-        <f>F16-F19</f>
+      <c r="F22" s="30">
+        <f>F16-F19-F20</f>
         <v>2067975.79916226</v>
       </c>
-      <c r="G21" s="30">
-        <f>G16-G19</f>
+      <c r="G22" s="30">
+        <f>G16-G19-G20</f>
         <v>2209105.87972045</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C22" s="31">
-        <f>IF(C10&gt;0,C21/C10,0)</f>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="31">
+        <f>IF(C10&gt;0,C22/C10,0)</f>
         <v>0.42036082</v>
       </c>
-      <c r="D22" s="31">
-        <f>IF(D10&gt;0,D21/D10,0)</f>
+      <c r="D23" s="31">
+        <f>IF(D10&gt;0,D22/D10,0)</f>
         <v>0.49097224</v>
       </c>
-      <c r="E22" s="31">
-        <f>IF(E10&gt;0,E21/E10,0)</f>
+      <c r="E23" s="31">
+        <f>IF(E10&gt;0,E22/E10,0)</f>
         <v>0.51316263</v>
       </c>
-      <c r="F22" s="31">
-        <f>IF(F10&gt;0,F21/F10,0)</f>
+      <c r="F23" s="31">
+        <f>IF(F10&gt;0,F22/F10,0)</f>
         <v>0.52336428</v>
       </c>
-      <c r="G22" s="31">
-        <f>IF(G10&gt;0,G21/G10,0)</f>
+      <c r="G23" s="31">
+        <f>IF(G10&gt;0,G22/G10,0)</f>
         <v>0.5030612</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="32">
-        <f>C21</f>
-        <v>837568.94016733</v>
-      </c>
-      <c r="D24" s="32">
-        <f>C24+D21</f>
-        <v>2134979.04700132</v>
-      </c>
-      <c r="E24" s="32">
-        <f>D24+E21</f>
-        <v>3843729.12983531</v>
-      </c>
-      <c r="F24" s="32">
-        <f>E24+F21</f>
-        <v>5911704.92899757</v>
-      </c>
-      <c r="G24" s="32">
-        <f>F24+G21</f>
-        <v>8120810.80871802</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="32">
+        <f>C22</f>
+        <v>837568.94016733</v>
+      </c>
+      <c r="D25" s="32">
+        <f>C25+D22</f>
+        <v>2134979.04700132</v>
+      </c>
+      <c r="E25" s="32">
+        <f>D25+E22</f>
+        <v>3843729.12983531</v>
+      </c>
+      <c r="F25" s="32">
+        <f>E25+F22</f>
+        <v>5911704.92899757</v>
+      </c>
+      <c r="G25" s="32">
+        <f>F25+G22</f>
+        <v>8120810.80871802</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="D25" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" s="34" t="s">
+      <c r="C26" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" s="34" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4136,7 +5646,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4164,7 +5674,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C4" s="32">
         <f>Assumptions!D57</f>
@@ -4189,7 +5699,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C5" s="27">
         <f>'5-Year P&amp;L'!C16</f>
@@ -4214,7 +5724,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C7" s="27">
         <f>Assumptions!D58</f>
@@ -4239,7 +5749,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C8" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -4264,7 +5774,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C9" s="29">
         <f>C7+C8</f>
@@ -4289,7 +5799,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="28" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C11" s="35">
         <f>IF(C9&gt;0,C5/C9,IF(C5&gt;0,99.9,0))</f>
@@ -4314,7 +5824,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C13" s="27">
         <f>C5-C9</f>
@@ -4339,7 +5849,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C14" s="32">
         <f>C5-C9</f>
@@ -4364,7 +5874,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C16" s="30">
         <f>C4+C14</f>
@@ -4402,6 +5912,267 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF7C3AED"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:G17"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="23"/>
+      <c r="C4" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="27">
+        <v>1050000</v>
+      </c>
+      <c r="D6" s="27">
+        <v>1405950</v>
+      </c>
+      <c r="E6" s="27">
+        <v>1782312</v>
+      </c>
+      <c r="F6" s="27">
+        <v>2122622.1975</v>
+      </c>
+      <c r="G6" s="27">
+        <v>2363568.501</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="27">
+        <v>997500</v>
+      </c>
+      <c r="D7" s="27">
+        <v>1335652.5</v>
+      </c>
+      <c r="E7" s="27">
+        <v>1693196.4</v>
+      </c>
+      <c r="F7" s="27">
+        <v>2016491.0876249997</v>
+      </c>
+      <c r="G7" s="27">
+        <v>2245390.07595</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="37">
+        <f>C6-C7</f>
+        <v>52500</v>
+      </c>
+      <c r="D8" s="37">
+        <f>D6-D7</f>
+        <v>70297.5</v>
+      </c>
+      <c r="E8" s="37">
+        <f>E6-E7</f>
+        <v>89115.6</v>
+      </c>
+      <c r="F8" s="37">
+        <f>F6-F7</f>
+        <v>106131.109875</v>
+      </c>
+      <c r="G8" s="37">
+        <f>G6-G7</f>
+        <v>118178.42505</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="29">
+        <f>C7*30/365</f>
+        <v>81986.30136986</v>
+      </c>
+      <c r="D9" s="29">
+        <f>D7*30/365</f>
+        <v>109779.65753425</v>
+      </c>
+      <c r="E9" s="29">
+        <f>E7*30/365</f>
+        <v>139166.82739726</v>
+      </c>
+      <c r="F9" s="29">
+        <f>F7*30/365</f>
+        <v>165738.99350342</v>
+      </c>
+      <c r="G9" s="29">
+        <f>G7*30/365</f>
+        <v>184552.60898219</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="27">
+        <v>912568.9401673255</v>
+      </c>
+      <c r="D12" s="27">
+        <v>2209979.0470013176</v>
+      </c>
+      <c r="E12" s="27">
+        <v>3918729.12983531</v>
+      </c>
+      <c r="F12" s="27">
+        <v>5986704.928997569</v>
+      </c>
+      <c r="G12" s="27">
+        <v>8195810.808718016</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" s="27">
+        <v>0</v>
+      </c>
+      <c r="D13" s="27">
+        <v>0</v>
+      </c>
+      <c r="E13" s="27">
+        <v>0</v>
+      </c>
+      <c r="F13" s="27">
+        <v>0</v>
+      </c>
+      <c r="G13" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" s="30">
+        <f>C12-C13</f>
+        <v>912568.94016733</v>
+      </c>
+      <c r="D14" s="30">
+        <f>D12-D13</f>
+        <v>2209979.04700132</v>
+      </c>
+      <c r="E14" s="30">
+        <f>E12-E13</f>
+        <v>3918729.12983531</v>
+      </c>
+      <c r="F14" s="30">
+        <f>F12-F13</f>
+        <v>5986704.92899757</v>
+      </c>
+      <c r="G14" s="30">
+        <f>G12-G13</f>
+        <v>8195810.80871802</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B16:G17"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor rgb="FF0D9488"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4415,7 +6186,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4443,7 +6214,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C4" s="26">
         <f>Drivers!C12</f>
@@ -4468,7 +6239,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="25" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="C5" s="26">
         <f>Assumptions!D35</f>
@@ -4493,25 +6264,25 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="36">
+        <v>157</v>
+      </c>
+      <c r="C6" s="39">
         <f>C4+C5</f>
         <v>14</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="39">
         <f>D4+D5</f>
         <v>16</v>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="39">
         <f>E4+E5</f>
         <v>19</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="39">
         <f>F4+F5</f>
         <v>21</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="39">
         <f>G4+G5</f>
         <v>23</v>
       </c>
@@ -4528,7 +6299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFD97706"/>
@@ -4544,13 +6315,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="25" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="C3" s="27">
         <f>Assumptions!D59</f>
@@ -4559,7 +6330,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C4" s="31">
         <f>Assumptions!D60</f>
@@ -4577,7 +6348,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C6" s="32">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -4586,7 +6357,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="C8" s="35">
         <f>'Cash Flow &amp; DSCR'!C11</f>
@@ -4603,174 +6374,4 @@
     <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF328555"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:C21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C1" s="13"/>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="25" t="str">
-        <f>Assumptions!D5</f>
-        <v>Heritage Academy</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="25" t="str">
-        <f>Assumptions!D7</f>
-        <v>Private School</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="25" t="str">
-        <f>Assumptions!D6</f>
-        <v>FL</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="25">
-        <f>Assumptions!D8</f>
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="26">
-        <f>Assumptions!D16</f>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="C9" s="27">
-        <f>Drivers!G10</f>
-        <v>4391326.28635</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="C10" s="37">
-        <f>'5-Year P&amp;L'!G16</f>
-        <v>2268170.27288646</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="C12" s="23"/>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="39">
-        <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
-        <v>0.5030612</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="C14" s="31">
-        <f>IF(Drivers!G10&gt;0,Drivers!G16/Drivers!G10,0)</f>
-        <v>0.32588035</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="C15" s="27">
-        <f>IF(Assumptions!D16&gt;0,Drivers!G10/Assumptions!D16,0)</f>
-        <v>21957</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="C16" s="27">
-        <f>IF(Assumptions!D16&gt;0,('5-Year P&amp;L'!G12+'5-Year P&amp;L'!G13)/Assumptions!D16,0)</f>
-        <v>10616</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="C17" s="35">
-        <f>'Cash Flow &amp; DSCR'!C11</f>
-        <v>15.18060688</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="C18" s="35">
-        <f>'Cash Flow &amp; DSCR'!G11</f>
-        <v>38.40165202</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="C19" s="40">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="C21" s="12"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B21:C21"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>